--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -15562,7 +15562,7 @@
       </c>
       <c r="E131" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F131" s="41" t="inlineStr">
@@ -15598,21 +15598,60 @@
       <c r="N131" s="45" t="n"/>
       <c r="O131" s="46" t="n"/>
       <c r="P131" s="46" t="n"/>
-      <c r="Q131" s="47" t="n"/>
+      <c r="Q131" s="47" t="n">
+        <v>100</v>
+      </c>
       <c r="R131" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="S131" s="48" t="n"/>
+      <c r="S131" s="48" t="inlineStr">
+        <is>
+          <t>As a trader, I want the system to know exactly what it is holding - opened only from a real fill, protected before it counts as held, and priced continuously - so that every other safety mechanism in the system is reasoning about the actual book rather than the one it intended to have.</t>
+        </is>
+      </c>
       <c r="T131" s="48" t="inlineStr">
         <is>
-          <t>1. Track open positions with live P&amp;L
-2. MFE/MAE tracking for the journal
-3. R-multiple computation
-4. Position state in Redis for fast reads</t>
-        </is>
-      </c>
-      <c r="U131" s="48" t="n"/>
-      <c r="V131" s="48" t="n"/>
+          <t>1. Confirm a fill: how much actually filled, at what price, and refuse to call anything else a fill
+2. THE FILL-CONFIRMATION TRIGGER that calls ProtectiveStop.attach (inherited from E15-S04; was absent from this task list)
+3. Track open positions with live P&amp;L
+4. MFE/MAE tracking for the journal - including PERSISTING them, which nothing does today
+5. R-multiple computation (largely delivered by E14-S07 on the model; this story exposes it on the book)
+6. Position state in Redis for fast reads
+7. Confirm the FILL of an emergency exit (inherited from E15-S04: attach proves the exit is live, not that it filled)</t>
+        </is>
+      </c>
+      <c r="U131" s="48" t="inlineStr">
+        <is>
+          <t>AC1 (RED) A position is opened for the quantity that FILLED at the price it filled, never the quantity ordered. An entry of 100 that fills 40 opens a position of 40; an entry that fills 0 opens nothing. Falsifiable: assert quantity and entry_price against filled_quantity and average_price.
+AC2 (RED) Nothing enters the book as protected without a verified live stop. When attach raises, no protected position exists and no Redis mirror is written. Falsifiable: the protected variant is constructible ONLY from an EstablishedPosition.
+AC3 (RED) A position whose stop could not be established stays tracked until its emergency exit is confirmed FILLED. Falsifiable: after StopNotEstablishedError the book holds it as EXITING naming the exit order; a FILLED exit closes it with realised P&amp;L and clears Redis.
+AC4 MFE and MAE are the running extremes of unrealised P&amp;L and never move the wrong way. Falsifiable: property test over generated price sequences - MFE equals the max and MAE the min of unrealised P&amp;L over the sequence - and both survive a round trip through Redis and through Postgres.
+AC5 (RED) A position rebuilt from the database is NEVER presumed protected. Falsifiable: restore() yields positions in an UNVERIFIED state and there is no code path from a database row to the protected variant.</t>
+        </is>
+      </c>
+      <c r="V131" s="48" t="inlineStr">
+        <is>
+          <t>BUSINESS ANALYSIS, 22 Sep 2026. The story arrived with four tasks, no user story and NO ACCEPTANCE CRITERIA at all - on a 'Safety-critical' item. Nothing falsifiable means nothing to sign off against, so Phase 1 wrote them rather than proceeding. The task list was also incomplete against this story's own Build Concerns: the fill-confirmation trigger, which E15-S04 recorded as belonging here and is the single most important thing the story delivers, was not among the four tasks.
+WHAT BREAKS IF THIS IS WRONG, which is what set the test depth:
+- A fill that never becomes a tracked position is a real position with no stop and no deadline - the naked position E15-S04 exists to prevent, arriving through the front door instead.
+- A position built from ORDERED quantity after a partial fill places a stop for more shares than are held. When that stop triggers it sells what is not there, which is a naked SHORT created by the protective mechanism.
+- Wrong live P&amp;L makes the daily-loss halt fire late or not at all.
+- MFE/MAE only misinform the journal: no money path today, so they are tested as properties rather than as safety.
+OUT OF SCOPE, named with owners so the boundary is not re-litigated:
+- The 30s reconciliation POLL LOOP - E15-S09. This story delivers mechanisms and predicates; the loop that calls them is that story, exactly as E15-S04 delivered attach and left the loop to S09.
+- The square-off TIMER loop and exiting at the deadline - E15-S06. This story COMPUTES and stores squareoff_deadline because the column is NOT NULL and the position cannot be constructed without it; it does not act on it.
+- Exit precedence - E15-S07. Trailing stops and partial exits - E15-S08. Simulated broker - E15-S10.
+FOUND WHILE READING, and it makes task 4 real work rather than a field assignment: PositionRepository._position_to_dict does not return max_favourable_excursion or max_adverse_excursion, and close_position does not write them. The columns have existed since the first migration. So MFE/MAE are today written by nothing and read by nothing - the same shape as the two exposure caps that sat in system.yaml binding on nothing, and as SUBMIT_FAILED being modelled and unreachable. A story that just computed them in memory would have looked complete and persisted nothing.
+DELIVERED 22 Sep 2026. execution/positions.py.
+THE THREE STATES ARE TYPES, NOT A FLAG. ProtectedPosition holds an EstablishedPosition, ExitingPosition holds a live market exit awaiting its fill, UnverifiedPosition is what a restart produces. A boolean would have read identically and permitted the one state this module exists to prevent: a position called protected because a field said so. A flag can be set; an EstablishedPosition can only be obtained, and only from the good end of ProtectiveStop.attach.
+THE TRIGGER E15-S04 RECORDED NOW EXISTS. open_from_fill is the fill-confirmation path that calls attach; until this story nothing did, and the protective stop was built and unwired.
+FILLED_QUANTITY, NEVER STATUS. Kite reports OPEN for a partially filled order and PARTIAL -&gt; CANCELLED is legal and real (a partly filled order cancelled at square-off). A status-driven implementation opens nothing for the cancelled case and a FULL-SIZE position for the partial - and a full-size position gets a full-size stop, which sells shares that do not exist when it triggers. That is a protective mechanism creating a naked short, and it is why AC1 is the first criterion.
+A FILL CAN LAND THROUGH ITS OWN STOP, and nothing had modelled it. A long that fills at or below its approved stop cannot be expressed as a Position at all - the model refuses it - so a naive version meets a Pydantic ValidationError while holding live stock. It is now exited at market through ProtectiveStop.exit_now, which is why gateway.Closable exists: build_exit only ever read four fields, and widening to them lets the dangerous holding be exited instead of raising.
+NOTHING IS PERSISTED FOR THAT CASE, deliberately: a positions row claiming a stop that is not on the protective side of entry would be a false record. The exit ORDER row carries the same correlation_id.
+ORDER OF OPERATIONS: the row is written BEFORE the stop is attached. Die after the insert and reconciliation finds a position with no stop and exits one position; die after attaching with no row and the broker holds a position we have no record of, which 8.3 says trips the kill switch. Losing a trade beats losing the day.
+43 unit (2 property-based) + 13 integration (real Postgres, real Redis). Mutation: 24 injected, 24 killed.</t>
+        </is>
+      </c>
       <c r="W131" s="49" t="n"/>
       <c r="X131" t="inlineStr">
         <is>
@@ -15710,7 +15749,11 @@
       <c r="W132" s="49" t="n"/>
       <c r="X132" s="75" t="inlineStr">
         <is>
-          <t>TWO issues. (1) A single polling loop for all positions is a single point of failure at the most time-critical moment of the day — if it dies at 14:00, nothing notices until the broker squares off. Monitor its liveness independently. (2) The market order at the deadline MUST carry market_protection (C9) or Zerodha rejects it — exactly when you cannot afford a rejection.</t>
+          <t>TWO issues. (1) A single polling loop for all positions is a single point of failure at the most time-critical moment of the day — if it dies at 14:00, nothing notices until the broker squares off. Monitor its liveness independently. (2) The market order at the deadline MUST carry market_protection (C9) or Zerodha rejects it — exactly when you cannot afford a rejection.
+CONSTRAINT INHERITED FROM E15-S05 (22 Sep 2026).
+1. THE DEADLINE IS ALREADY COMPUTED AND STORED at position open, because positions.squareoff_deadline is NOT NULL and the position cannot be constructed without it. This story owns the TIMER LOOP that acts on it, not the computation - do not compute it a second time, and if the two ever disagree the stored one is what the position was opened under.
+2. AN EXIT IS NOT DONE WHEN IT IS PLACED. Reuse PositionManager.confirm_exit: it gates on filled_quantity, leaves a partially filled exit open for the remainder, and is the only thing that writes the close. A timer that treated submission as closure would drop positions out of the book while they were still held.
+3. PASS YOUR OWN ExitReason (TIME). confirm_exit defaults to UNPROTECTED because E15-S05's only caller is the failed-stop path.</t>
         </is>
       </c>
     </row>
@@ -15956,7 +15999,11 @@
 5. AN UNPROTECTED POSITION FOUND BY THE LOOP TAKES THE SAME PATH AS ONE FOUND AT ATTACH TIME: exit at market, and halt if the exit fails. Do not invent a second policy for it.
 CONSTRAINT INHERITED FROM SIT-003 (11 Sep 2026).
 6. SUBMIT_FAILED IS MODELLED AND NOTHING WRITES IT. order_state.py gives it a legal incoming edge from SUBMITTING and an outgoing edge to RECONCILE_REQUIRED, and no code path in src/ has ever produced it. It belongs to THIS story: a submission that failed in a way the broker did not refuse is exactly what reconciliation has to resolve. SIT-003 fixed the sibling case (an outright rejection now writes REJECTED); do not assume this one was fixed with it.
-7. A ROW IN SUBMITTING MEANS WE DO NOT KNOW, AND THAT IS NOW LOAD-BEARING. Since SIT-003 a refusal writes REJECTED, so a SUBMITTING row no longer conflates the refused case with the unknown one. Query it; do not treat it as failed.</t>
+7. A ROW IN SUBMITTING MEANS WE DO NOT KNOW, AND THAT IS NOW LOAD-BEARING. Since SIT-003 a refusal writes REJECTED, so a SUBMITTING row no longer conflates the refused case with the unknown one. Query it; do not treat it as failed.
+CONSTRAINT INHERITED FROM E15-S05 (22 Sep 2026), in addition to the E15-S03 and E15-S04 constraints above.
+6. RESTORE PRODUCES UnverifiedPosition, NEVER ProtectedPosition, and there is deliberately no code path from a row to the protected type. Your loop is what resolves it: call ProtectiveStop.is_protected and act on the answer. A restart currently ends with a book whose protection is entirely unknown, which is honest and is not safe until this loop exists.
+7. THE REDIS MIRROR IS A CACHE, NOT AN AUTHORITY. PositionSnapshot.protection records what a process believed when it wrote the key. Anything with Redis access can write that key and the value can be stale by a tick. Trusting it is the same defect as reading stop_price off a row, one store along - it launders 'we thought so a moment ago' into 'the broker confirms a live stop'.
+8. SUBMIT_FAILED IS STILL MODELLED AND UNREACHABLE (carried forward from SIT-003, which made REJECTED reachable). It belongs to this story's path.</t>
         </is>
       </c>
     </row>
@@ -21899,7 +21946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J134"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -26879,6 +26926,154 @@
       <c r="G134" s="76" t="inlineStr">
         <is>
           <t>tests/unit/test_gateway.py::TestARefusedOrderIsRecordedAsRefused::test_a_refused_order_is_terminal_and_is_never_resubmitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="150" customHeight="1" s="59">
+      <c r="A135" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-15</t>
+        </is>
+      </c>
+      <c r="B135" s="76" t="inlineStr">
+        <is>
+          <t>E15-S05</t>
+        </is>
+      </c>
+      <c r="C135" s="76" t="inlineStr">
+        <is>
+          <t>A safety guarantee that was only a type annotation</t>
+        </is>
+      </c>
+      <c r="D135" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E135" s="76" t="inlineStr">
+        <is>
+          <t>ProtectedPosition is the type that proves a position is protected: it holds an EstablishedPosition, which only ProtectiveStop.attach can produce. As a plain frozen dataclass it accepted anything. ProtectedPosition(a_position_row) constructed happily and produced exactly the object the class exists to make impossible.</t>
+        </is>
+      </c>
+      <c r="F135" s="76" t="inlineStr">
+        <is>
+          <t>Found by writing the test that asserts the guarantee rather than assuming the annotation was one - the test failed with DID NOT RAISE. Dataclasses do not check types at runtime, so the only enforcement was mypy, which sees src/ and nothing else: any dynamic or test-side construction was unguarded. On the verification ladder this was 'a type checker complains', one rung below 'the dangerous state cannot be represented'. A __post_init__ now refuses, with the message explaining that a position is protected because the broker confirmed a live stop, never because a field said so.</t>
+        </is>
+      </c>
+      <c r="G135" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_positions.py::test_the_protected_type_cannot_be_built_from_a_position. Mutation M8 (remove the guard) killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="150" customHeight="1" s="59">
+      <c r="A136" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-16</t>
+        </is>
+      </c>
+      <c r="B136" s="76" t="inlineStr">
+        <is>
+          <t>E15-S05</t>
+        </is>
+      </c>
+      <c r="C136" s="76" t="inlineStr">
+        <is>
+          <t>MFE/MAE: columns since the first migration, written by nothing, read by nothing</t>
+        </is>
+      </c>
+      <c r="D136" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E136" s="76" t="inlineStr">
+        <is>
+          <t>positions.max_favourable_excursion and max_adverse_excursion have existed since the first migration. PositionRepository.close_position did not write them and _position_to_dict did not return them - and open_positions() is how the book is rebuilt after a restart, so a restart silently reset every position's excursions to zero while the columns held the real values.</t>
+        </is>
+      </c>
+      <c r="F136" s="76" t="inlineStr">
+        <is>
+          <t>The same shape as the two exposure caps that sat in system.yaml binding on nothing, and as SUBMIT_FAILED being modelled and unreachable: the artefact exists, looks complete, and is connected at neither end. Found in Phase 1 by reading the repository before designing against it, which is also what made the story's task 4 real work rather than a field assignment - a version that computed the excursions in memory would have looked finished and persisted nothing. Both directions are now wired and proved against real Postgres rather than a double that echoes back whatever it was handed.</t>
+        </is>
+      </c>
+      <c r="G136" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_position_manager_wiring.py::test_the_excursions_survive_the_database and ::test_restored_positions_carry_their_excursions. Mutations M15, M22, M23, M24 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="150" customHeight="1" s="59">
+      <c r="A137" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-17</t>
+        </is>
+      </c>
+      <c r="B137" s="76" t="inlineStr">
+        <is>
+          <t>E15-S05</t>
+        </is>
+      </c>
+      <c r="C137" s="76" t="inlineStr">
+        <is>
+          <t>Three Redis keys documented as HASH that are JSON strings</t>
+        </is>
+      </c>
+      <c r="D137" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E137" s="76" t="inlineStr">
+        <is>
+          <t>keys.py described state:quote, state:bar:current and state:position as HASH, matching LOW_LEVEL_ARCHITECTURE 4.3. ingest/quotes.py writes the quote key with state.set_state, which does client.set of model_dump_json - a string. HGETALL against it raises WRONGTYPE.</t>
+        </is>
+      </c>
+      <c r="F137" s="76" t="inlineStr">
+        <is>
+          <t>Caught while deciding how to store the position mirror: the docstring said HASH and the only implemented example said otherwise. The code is right and the docs were corrected, because JSON round-trips Decimal exactly and a hash of stringified decimals would re-introduce parsing at every read - and money is never a float here. state:bar:current was left describing the SPEC's intent and explicitly marked unverified, because nothing writes it yet and claiming a storage type for an unimplemented key would have been the same mistake in the other direction.</t>
+        </is>
+      </c>
+      <c r="G137" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_position_manager_wiring.py::test_the_snapshot_round_trips_with_exact_decimals - reads the key back through state.get_state against real Redis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="150" customHeight="1" s="59">
+      <c r="A138" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-18</t>
+        </is>
+      </c>
+      <c r="B138" s="76" t="inlineStr">
+        <is>
+          <t>E15-S05</t>
+        </is>
+      </c>
+      <c r="C138" s="76" t="inlineStr">
+        <is>
+          <t>A source edit silently moved a decorator off the class it belonged to</t>
+        </is>
+      </c>
+      <c r="D138" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E138" s="76" t="inlineStr">
+        <is>
+          <t>Inserting the new Closable protocol anchored on the text 'class GatewayPolicy:' placed it between @dataclass(frozen=True) and GatewayPolicy. Closable became a frozen dataclass and GatewayPolicy silently lost its decorator - meaning no generated __init__, and __post_init__ (which refuses market_protection of 0) never called.</t>
+        </is>
+      </c>
+      <c r="F138" s="76" t="inlineStr">
+        <is>
+          <t>Caught by mypy before a single test ran, via a __match_args__ conflict that made no sense until the file was read. Worth recording because the failure mode is general and invisible: anchoring an edit on a 'class X:' line attaches the new text to whatever decorator sits above it, and the result is syntactically valid. Every gate would eventually have caught this one because GatewayPolicy is constructed everywhere - but a decorator on a rarely constructed class would have survived to production. The lesson is to anchor on the decorator when one is present, not on the class line.</t>
+        </is>
+      </c>
+      <c r="G138" s="76" t="inlineStr">
+        <is>
+          <t>Not a test - mypy src/ is the gate that caught it, and the full suite (2,223) confirms GatewayPolicy still validates market_protection.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -15649,7 +15649,8 @@
 A FILL CAN LAND THROUGH ITS OWN STOP, and nothing had modelled it. A long that fills at or below its approved stop cannot be expressed as a Position at all - the model refuses it - so a naive version meets a Pydantic ValidationError while holding live stock. It is now exited at market through ProtectiveStop.exit_now, which is why gateway.Closable exists: build_exit only ever read four fields, and widening to them lets the dangerous holding be exited instead of raising.
 NOTHING IS PERSISTED FOR THAT CASE, deliberately: a positions row claiming a stop that is not on the protective side of entry would be a false record. The exit ORDER row carries the same correlation_id.
 ORDER OF OPERATIONS: the row is written BEFORE the stop is attached. Die after the insert and reconciliation finds a position with no stop and exits one position; die after attaching with no row and the broker holds a position we have no record of, which 8.3 says trips the kill switch. Losing a trade beats losing the day.
-43 unit (2 property-based) + 13 integration (real Postgres, real Redis). Mutation: 24 injected, 24 killed.</t>
+43 unit (2 property-based) + 13 integration (real Postgres, real Redis). Mutation: 24 injected, 24 killed.
+SIT-004 (MEDIUM, fixed same session): replaying a day's fills after a restart was refused by the uq_open_symbol index and by nothing else, so a normal restart outcome reached the caller as a database integrity error. Positions now get the same three-layer treatment orders already had - cheap check, unique index, reconciliation - and the cheap check answers with PositionAlreadyHeldError. Final mutation score includes M25/M26.</t>
         </is>
       </c>
       <c r="W131" s="49" t="n"/>
@@ -29106,7 +29107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -29380,6 +29381,68 @@
         </is>
       </c>
       <c r="L7" s="76" t="inlineStr">
+        <is>
+          <t>None - fixed in the same session</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="170" customHeight="1" s="59">
+      <c r="A8" s="76" t="inlineStr">
+        <is>
+          <t>SIT-004</t>
+        </is>
+      </c>
+      <c r="B8" s="76" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C8" s="76" t="inlineStr">
+        <is>
+          <t>E15-S05</t>
+        </is>
+      </c>
+      <c r="D8" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E8" s="76" t="inlineStr">
+        <is>
+          <t>execution/positions.py</t>
+        </is>
+      </c>
+      <c r="F8" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G8" s="76" t="inlineStr">
+        <is>
+          <t>Replaying a day's fills after a restart - 40 positions opened, the book restored from rows, then the same 40 fills presented again, which is exactly what happens because the broker keeps reporting yesterday's entries as FILLED. No second position was created and no second stop was placed, so the system was SAFE. But all 40 replays surfaced as a raw unique-index violation escaping open_from_fill: the caller is told the insert failed, with no way to tell 'this is already open and protected' from 'opening this failed'.</t>
+        </is>
+      </c>
+      <c r="H8" s="76" t="inlineStr">
+        <is>
+          <t>The unit store is a dictionary that accepts every insert, and the integration tests each open one position. Neither shape can produce a replay: it needs the SAME fills presented twice to a store that carries state across both passes, which is a session-scale setup. The defect also hides behind a correct outcome - nothing duplicates, because the partial unique index refuses it - so only the TYPE of the failure is wrong, and only a test that asserts on the failure type would see it. The first version of this SIT test asserted merely that the replay failed, and passed.</t>
+        </is>
+      </c>
+      <c r="I8" s="76" t="inlineStr">
+        <is>
+          <t>Only layer 2 of EPIC01 8.4's three-layer pattern existed for positions. The gateway applies all three to ORDERS (cheap check, uq_client_order, reconciliation) and E15-S05 inherited none of it for POSITIONS: there was no cheap check before the insert, so the database constraint was doing work it is meant to back up rather than perform. PositionRepository.open_position even documents this - 'a normal, expected outcome under concurrency, not an error to surface; callers must catch it and treat it as slot taken' - and the new caller did not. The instruction was in the docstring of the function being called, which is the easiest kind of instruction to not read.</t>
+        </is>
+      </c>
+      <c r="J8" s="76" t="inlineStr">
+        <is>
+          <t>open_from_fill now checks the in-memory book first and raises PositionAlreadyHeldError, a typed, actionable answer. Deliberately AFTER confirm_fill, because 'nothing filled' is the more specific truth. The cheap check is only as good as the book - empty until restore() runs - so the partial unique indexes remain the guarantee rather than the optimisation, and E15-S09's reconciliation is the third layer behind both.</t>
+        </is>
+      </c>
+      <c r="K8" s="76" t="inlineStr">
+        <is>
+          <t>tests/sit/test_e14_trading_session.py::TestSit18...::test_replaying_the_days_fills_after_a_restart (asserts the failure TYPE, not merely that it failed) plus tests/unit/test_positions.py::TestReplayingAFill (4 tests, including the control that a different symbol still opens). Mutations M25 and M26 killed.</t>
+        </is>
+      </c>
+      <c r="L8" s="76" t="inlineStr">
         <is>
           <t>None - fixed in the same session</t>
         </is>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4530,7 +4530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X203"/>
+  <dimension ref="A1:X204"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -15650,7 +15650,10 @@
 NOTHING IS PERSISTED FOR THAT CASE, deliberately: a positions row claiming a stop that is not on the protective side of entry would be a false record. The exit ORDER row carries the same correlation_id.
 ORDER OF OPERATIONS: the row is written BEFORE the stop is attached. Die after the insert and reconciliation finds a position with no stop and exits one position; die after attaching with no row and the broker holds a position we have no record of, which 8.3 says trips the kill switch. Losing a trade beats losing the day.
 43 unit (2 property-based) + 13 integration (real Postgres, real Redis). Mutation: 24 injected, 24 killed.
-SIT-004 (MEDIUM, fixed same session): replaying a day's fills after a restart was refused by the uq_open_symbol index and by nothing else, so a normal restart outcome reached the caller as a database integrity error. Positions now get the same three-layer treatment orders already had - cheap check, unique index, reconciliation - and the cheap check answers with PositionAlreadyHeldError. Final mutation score includes M25/M26.</t>
+SIT-004 (MEDIUM, fixed same session): replaying a day's fills after a restart was refused by the uq_open_symbol index and by nothing else, so a normal restart outcome reached the caller as a database integrity error. Positions now get the same three-layer treatment orders already had - cheap check, unique index, reconciliation - and the cheap check answers with PositionAlreadyHeldError. Final mutation score includes M25/M26.
+SIT AGAINST THE PROMOTED QA TREE, 24 Sep 2026: QA f7caa6f (DEV ec32630), CI green on both. 163 passed, 0 failed, including all 12 SIT-18 scenarios. Documents/, scripts/tracker and .claude confirmed absent from the QA tree.
+THE FIRST TWO RUNS STALLED, and the cause was the harness, not the code: the previous session's stopped SIT run had left two orphaned pytest processes alive for two days in the SAME worktree, and a second pytest writing that worktree's __pycache__ blocked on them - CPU flat, no output. Found by reading the process table instead of re-running, confirmed by the next run passing once they were terminated. Worth knowing because 'the suite hangs in the QA worktree' looked like a defect in the promoted code and was not one.
+CORRECTION, 24 Sep 2026 (SIT-007): the stall above was NOT caused by the orphaned processes. It is a hang inside CPython's Windows socketpair emulation, reached when a process creates thousands of event loops, and it recurred in the full suite with no orphans present. The run that passed after the orphans were killed passed by chance. The two stale processes were real and were rightly removed; they were not the cause. Recorded rather than rewritten, because a confirmed-looking wrong diagnosis is the more useful thing to keep.</t>
         </is>
       </c>
       <c r="W131" s="49" t="n"/>
@@ -15754,7 +15757,9 @@
 CONSTRAINT INHERITED FROM E15-S05 (22 Sep 2026).
 1. THE DEADLINE IS ALREADY COMPUTED AND STORED at position open, because positions.squareoff_deadline is NOT NULL and the position cannot be constructed without it. This story owns the TIMER LOOP that acts on it, not the computation - do not compute it a second time, and if the two ever disagree the stored one is what the position was opened under.
 2. AN EXIT IS NOT DONE WHEN IT IS PLACED. Reuse PositionManager.confirm_exit: it gates on filled_quantity, leaves a partially filled exit open for the remainder, and is the only thing that writes the close. A timer that treated submission as closure would drop positions out of the book while they were still held.
-3. PASS YOUR OWN ExitReason (TIME). confirm_exit defaults to UNPROTECTED because E15-S05's only caller is the failed-stop path.</t>
+3. PASS YOUR OWN ExitReason (TIME). confirm_exit defaults to UNPROTECTED because E15-S05's only caller is the failed-stop path.
+CONSTRAINT INHERITED FROM E15-S09 (24 Sep 2026).
+4. THE SQUARE-OFF EXIT SHARES ITS KEY WITH THE RECONCILER'S EMERGENCY EXIT. Both are intent=SQUAREOFF on the same correlation, so the gateway treats a second one as a replay of the first and resumes it rather than placing a new order. That is right while the first is working and wrong once it has been CANCELLED part-filled: the remainder cannot be exited under that key, and the exit path halts instead. Decide whether the timer needs its own intent (ExitReason TIME exists; OrderIntent has no TIME member).</t>
         </is>
       </c>
     </row>
@@ -15927,7 +15932,7 @@
       </c>
       <c r="E135" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F135" s="41" t="inlineStr">
@@ -15963,7 +15968,9 @@
       <c r="N135" s="45" t="n"/>
       <c r="O135" s="46" t="n"/>
       <c r="P135" s="46" t="n"/>
-      <c r="Q135" s="47" t="n"/>
+      <c r="Q135" s="47" t="n">
+        <v>100</v>
+      </c>
       <c r="R135" s="39" t="n">
         <v>5</v>
       </c>
@@ -15976,17 +15983,51 @@
         <is>
           <t>1. Every 30s during market hours, plus on every reconnect
 2. Diff orders and positions
-3. Broker state wins — it is the legal record
-4. `RECONCILIATION_DRIFT` audit event per difference
-5. Unknown position → kill switch + P0 alert immediately</t>
+3. Broker state wins - through the state machine, consulting filled_quantity
+4. RECONCILIATION_DRIFT audit event per difference
+5. Unknown position -&gt; kill switch + P0 alert immediately
+6. (constraints 4, 5, 8) Every booked position checked for a live stop every cycle; unprotected -&gt; exit at market; UnverifiedPosition resolved from the broker
+7. (constraints 6, 7, 10) SUBMITTING rows queried; absent past a grace window -&gt; SUBMIT_FAILED
+8. Give fetch_positions an honest type: the protocol promised Position, the Kite adapter returns raw dicts, and nothing noticed</t>
         </is>
       </c>
       <c r="U135" s="48" t="inlineStr">
         <is>
-          <t>• 🔴 An unknown position halts the system within one reconciliation cycle</t>
-        </is>
-      </c>
-      <c r="V135" s="48" t="n"/>
+          <t>AC1 (RED) An unknown position - broker MIS quantity that our own orders do not explain - arms the kill switch in the cycle that first observes it.
+AC2 (RED) A fill racing the two broker reads never produces a false halt. Positions are read BEFORE the orderbook, so a race can only make our orders explain more than the broker shows, never less.
+AC3 (RED) Every booked position is checked for a live stop every cycle. One that is not protected is exited at market, and a failed exit halts - the same path as attach. Protection is never read from the mirror or from a row.
+AC4 (RED) An UnverifiedPosition whose stop the broker confirms live becomes ProtectedPosition; one whose stop is absent or dead is exited.
+AC5 (RED) Broker status is applied through the state machine: an OPEN report with a partial fill records PARTIAL, and a refused transition records RECONCILE_REQUIRED once - not once per cycle.
+AC6 A SUBMITTING order absent at the broker past a grace window becomes SUBMIT_FAILED; inside the window it is left alone; present, it is adopted.
+AC7 (RED) A holding our orders explain but the book does not hold is unprotected by definition and is exited. Until E15-S12 books fills, this is every fill - fail closed, and said plainly.
+AC8 Every difference emits exactly one RECONCILIATION_DRIFT event whose stage and outcome fit decision_log's columns (String(28), String(12)), proved against the real table; a clean cycle emits none.
+AC9 A broker read that fails is never acted on as a partial view. Consecutive failures halt (BROKER_DISCONNECTED) rather than leave open positions unwatched.</t>
+        </is>
+      </c>
+      <c r="V135" s="48" t="inlineStr">
+        <is>
+          <t>BUSINESS ANALYSIS, 24 Sep 2026.
+WHY THIS STORY AND NOT E15-S06: S06 is next by id but depends on E04-S05 (CAS classification), which is New. S09 is the first P0 in sequence with every dependency met, and it closes the gaps S04 and S05 left open on purpose: E15-S04's acceptance criterion is 'only half met' without this loop, and E15-S05 ends a restart with a book whose protection is 'entirely unknown, which is honest and is not safe until this loop exists'.
+THE STORY HAD ONE ACCEPTANCE CRITERION and ten recorded constraints. A constraint that is not a criterion cannot be signed off, so Phase 1 wrote nine falsifiable criteria. The constraint list also had two blocks both numbered from 6; renumbered 1-10.
+WHAT BREAKS IF THIS IS WRONG: an order placed outside this system - a bug, or someone else - runs unwatched; a stop rejected a second after it was verified leaves a position naked until square-off; a restart leaves every position's protection unknown indefinitely.
+OUT OF SCOPE, with owners:
+- BOOKING FILLS (entry filled -&gt; open_from_fill; stop or exit filled -&gt; confirm_exit): E15-S12, raised here. open_from_fill needs the approved sizing, slot and CAS flag, and the orders table carries none of them - that is its own design problem. Until it lands, AC7 means the system exits every fill. That is the honest behaviour of a half-built pipeline, not a defect.
+- ACTING ON AN UNKNOWN POSITION. It is not ours; it may be the owner's own manual trade. The loop halts and alerts; it does not trade a position it did not open. Deliberate.
+- Alert TRANSPORT: E14-S12, needs credentials. End-of-day reconciliation and journal: E15-S11.
+FOUND WHILE READING:
+- TradingAdapter.fetch_positions is declared '-&gt; list[Position]'. The Kite adapter returns raw dicts, and its own docstring says why that is right: mapping would invent a stop price, correlation id and slot the broker does not have. The protocol and the implementation disagree and no check noticed, so the first consumer - this loop - would have been typed against fields that do not exist.
+- decision_log.outcome is String(12). The obvious outcome label, 'UNKNOWN_POSITION', is 16 characters and would fail the audit insert at the exact moment it matters - the decision_log.stage lesson, one column along.
+- OrderRepository can write SUBMITTING, SUBMITTED and REJECTED and nothing else. A reconciler needs to write any legal transition.
+- open_orders() hardcodes the terminal set as three strings rather than asking OrderStatus.is_terminal: two definitions of one fact.
+DELIVERED 24 Sep 2026. execution/reconciliation.py.
+READ EVERYTHING, THEN ACT, and never act on a partial view: a failed read does nothing and counts; three in a row halt (BROKER_DISCONNECTED).
+UNKNOWN POSITIONS ARE FOUND PER SIDE, NOT BY NET. The two broker reads are separate calls. Read positions first and an ENTRY fill in the gap is harmless, but an EXIT fill makes the broker look like it holds shares nobody ordered, and a net comparison halts the day on its own square-off. Cumulative bought and sold each only grow, so positions-first plus a per-side comparison is race-free in both directions without a second read.
+POLICY, STATED SO IT IS A CHOICE: MIS only (CNC/NRML/MTF are the owner's and never halt). ANY unexplained MIS fill halts - including a foreign sale netting against our long, which leaves our stop selling shares that are gone. The owner trading MIS by hand on the same account WILL halt the system. The loop never trades an unknown position, and alerts separately from the halt.
+FOUND IN THE CODE BEFORE WRITING ANY: the adapter protocol, the Kite adapter and the design doc gave fetch_positions three different return types; subscribe was declared a coroutine while every implementation is an async iterator. Nothing checked conformance - @runtime_checkable checks names, not signatures. Now type-checked (_conforms in broker/kite/trading.py).
+FOUND BY THE PRIMARY SOURCE: Kite keeps positions closed during the day in the net list at quantity 0, and quantity is signed. A reader treating every row as open sees a book full of positions that are not there.
+TESTS: 2,239 -&gt; 2,361; coverage 92% -&gt; 93%; 86 reconciler unit + 16 integration (real Postgres, Redis, Kite mapping) + 9 ProtectiveStop unit + 11 SIT-19. Mutation: 38 injected, 38 killed (32/35 on the first run; 3 test gaps closed, then M36-M38 added for SIT-005/006).</t>
+        </is>
+      </c>
       <c r="W135" s="49" t="n"/>
       <c r="X135" s="75" t="inlineStr">
         <is>
@@ -16002,9 +16043,9 @@
 6. SUBMIT_FAILED IS MODELLED AND NOTHING WRITES IT. order_state.py gives it a legal incoming edge from SUBMITTING and an outgoing edge to RECONCILE_REQUIRED, and no code path in src/ has ever produced it. It belongs to THIS story: a submission that failed in a way the broker did not refuse is exactly what reconciliation has to resolve. SIT-003 fixed the sibling case (an outright rejection now writes REJECTED); do not assume this one was fixed with it.
 7. A ROW IN SUBMITTING MEANS WE DO NOT KNOW, AND THAT IS NOW LOAD-BEARING. Since SIT-003 a refusal writes REJECTED, so a SUBMITTING row no longer conflates the refused case with the unknown one. Query it; do not treat it as failed.
 CONSTRAINT INHERITED FROM E15-S05 (22 Sep 2026), in addition to the E15-S03 and E15-S04 constraints above.
-6. RESTORE PRODUCES UnverifiedPosition, NEVER ProtectedPosition, and there is deliberately no code path from a row to the protected type. Your loop is what resolves it: call ProtectiveStop.is_protected and act on the answer. A restart currently ends with a book whose protection is entirely unknown, which is honest and is not safe until this loop exists.
-7. THE REDIS MIRROR IS A CACHE, NOT AN AUTHORITY. PositionSnapshot.protection records what a process believed when it wrote the key. Anything with Redis access can write that key and the value can be stale by a tick. Trusting it is the same defect as reading stop_price off a row, one store along - it launders 'we thought so a moment ago' into 'the broker confirms a live stop'.
-8. SUBMIT_FAILED IS STILL MODELLED AND UNREACHABLE (carried forward from SIT-003, which made REJECTED reachable). It belongs to this story's path.</t>
+8. RESTORE PRODUCES UnverifiedPosition, NEVER ProtectedPosition, and there is deliberately no code path from a row to the protected type. Your loop is what resolves it: call ProtectiveStop.is_protected and act on the answer. A restart currently ends with a book whose protection is entirely unknown, which is honest and is not safe until this loop exists.
+9. THE REDIS MIRROR IS A CACHE, NOT AN AUTHORITY. PositionSnapshot.protection records what a process believed when it wrote the key. Anything with Redis access can write that key and the value can be stale by a tick. Trusting it is the same defect as reading stop_price off a row, one store along - it launders 'we thought so a moment ago' into 'the broker confirms a live stop'.
+10. SUBMIT_FAILED IS STILL MODELLED AND UNREACHABLE (carried forward from SIT-003, which made REJECTED reachable). It belongs to this story's path.</t>
         </is>
       </c>
     </row>
@@ -21178,6 +21219,105 @@
       </c>
       <c r="W203" s="49" t="n"/>
       <c r="X203" s="75" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="38" t="inlineStr">
+        <is>
+          <t>E15-S12</t>
+        </is>
+      </c>
+      <c r="B204" s="39" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="C204" s="40" t="inlineStr">
+        <is>
+          <t>EXECUTION &amp; POSITIONS</t>
+        </is>
+      </c>
+      <c r="D204" s="40" t="inlineStr">
+        <is>
+          <t>Book fills from reconciliation</t>
+        </is>
+      </c>
+      <c r="E204" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F204" s="41" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G204" s="39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H204" s="50" t="inlineStr">
+        <is>
+          <t>Safety-critical</t>
+        </is>
+      </c>
+      <c r="I204" s="39" t="inlineStr">
+        <is>
+          <t>FEAT</t>
+        </is>
+      </c>
+      <c r="J204" s="39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K204" s="40" t="inlineStr">
+        <is>
+          <t>E15-S09, E15-S05</t>
+        </is>
+      </c>
+      <c r="L204" s="40" t="n"/>
+      <c r="M204" s="44" t="n"/>
+      <c r="N204" s="45" t="n"/>
+      <c r="O204" s="44" t="n"/>
+      <c r="P204" s="44" t="n"/>
+      <c r="Q204" s="44" t="n"/>
+      <c r="R204" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="S204" s="48" t="inlineStr">
+        <is>
+          <t>As a trader, I want a fill the reconciliation loop observes to become a protected position in the book, so that the system can hold a position at all - until this exists, every fill is exited as unprotected.</t>
+        </is>
+      </c>
+      <c r="T204" s="48" t="inlineStr">
+        <is>
+          <t>1. Carry the approved sizing, slot and CAS flag from submission to fill (the orders table has none of them)
+2. Entry observed FILLED or PARTIAL -&gt; PositionManager.open_from_fill
+3. Stop observed FILLED -&gt; confirm_exit(reason=STOP); square-off exit FILLED -&gt; confirm_exit(reason=UNPROTECTED or TIME)
+4. After a restart, a fill with no recorded sizing cannot be booked correctly and is exited, not guessed</t>
+        </is>
+      </c>
+      <c r="U204" s="48" t="inlineStr">
+        <is>
+          <t>AC1 (RED) An entry fill observed by reconciliation becomes a ProtectedPosition within the same cycle.
+AC2 (RED) A stopped-out position leaves the book with exit_reason STOP and its realised P&amp;L.
+AC3 (RED) A fill whose sizing is unknown is exited rather than booked with a guessed stop.</t>
+        </is>
+      </c>
+      <c r="V204" s="48" t="inlineStr">
+        <is>
+          <t>RAISED 24 Sep 2026 by E15-S09's business analysis. Split out because open_from_fill needs data the orders table does not carry, which is a design problem of its own and would have doubled S09.</t>
+        </is>
+      </c>
+      <c r="W204" s="49" t="n"/>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>CONSTRAINT INHERITED FROM E15-S09 (24 Sep 2026).
+1. BOOKING MUST RUN BEFORE S09's UNBOOKED-HOLDING CHECK IN THE SAME CYCLE. That check exits anything our orders explain but the book does not hold. Run it first and a fresh fill is exited thirty seconds before it could have been protected.
+2. open_from_fill raises PositionAlreadyHeldError on a replay (SIT-004). That is the normal outcome of a restart, not a failure to handle.
+3. A KEY ON MORE THAN ONE BROKER ORDER IS NOT BOOKABLE (REC-001). The reconciler halts on it and marks the correlation doubted; do not book a fill for a doubted correlation - some of those shares may not be ours.
+4. confirm_exit's default reason is UNPROTECTED. A stop fill is STOP; pass it.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:W197"/>
@@ -21947,7 +22087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -27075,6 +27215,154 @@
       <c r="G138" s="76" t="inlineStr">
         <is>
           <t>Not a test - mypy src/ is the gate that caught it, and the full suite (2,223) confirms GatewayPolicy still validates market_protection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="150" customHeight="1" s="59">
+      <c r="A139" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-19</t>
+        </is>
+      </c>
+      <c r="B139" s="76" t="inlineStr">
+        <is>
+          <t>E15-S09</t>
+        </is>
+      </c>
+      <c r="C139" s="76" t="inlineStr">
+        <is>
+          <t>An adapter and its protocol disagreed on two methods, and nothing checked</t>
+        </is>
+      </c>
+      <c r="D139" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E139" s="76" t="inlineStr">
+        <is>
+          <t>TradingAdapter.fetch_positions was declared -&gt; list[Position]; the Kite adapter returned list[dict]; LOW_LEVEL_ARCHITECTURE 5.1 said list[BrokerPosition]. MarketDataAdapter.subscribe was declared async def (a coroutine) while every implementation returns an async iterator, which cannot be awaited.</t>
+        </is>
+      </c>
+      <c r="F139" s="76" t="inlineStr">
+        <is>
+          <t>Found by the capability check before designing: the reconciler would have been the first consumer of fetch_positions, typed against a stop price, correlation id and slot the broker never supplies. Confirmed by a mypy probe assigning the Kite adapter to the protocol, which reported BOTH drifts. @runtime_checkable checks that attribute names exist, never signatures, so the protocol could say anything. The spec was right; the protocol drifted from it; the implementation drifted from both. BrokerPosition now exists and mypy enforces conformance.</t>
+        </is>
+      </c>
+      <c r="G139" s="76" t="inlineStr">
+        <is>
+          <t>src/algotrader/broker/kite/trading.py::_conforms (type-checked, never called); tests/integration/test_reconciliation_wiring.py exercises the real mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="150" customHeight="1" s="59">
+      <c r="A140" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-20</t>
+        </is>
+      </c>
+      <c r="B140" s="76" t="inlineStr">
+        <is>
+          <t>E15-S09</t>
+        </is>
+      </c>
+      <c r="C140" s="76" t="inlineStr">
+        <is>
+          <t>A net-quantity unknown-position check halts the day on its own exits</t>
+        </is>
+      </c>
+      <c r="D140" s="76" t="inlineStr">
+        <is>
+          <t>Design finding -&gt; designed out</t>
+        </is>
+      </c>
+      <c r="E140" s="76" t="inlineStr">
+        <is>
+          <t>The obvious check - broker net quantity equals what our orders net to - is not race-free across two separate broker reads. An exit fill landing between them shows in the orderbook but not yet in positions, so the broker appears to hold 40 shares nobody ordered.</t>
+        </is>
+      </c>
+      <c r="F140" s="76" t="inlineStr">
+        <is>
+          <t>Found while designing, before code, by walking the race in both directions: reading positions first protects against entry fills and INVERTS for exits. Net quantity is not monotone; cumulative bought and sold each are. The check compares each side separately against an orderbook read AFTER positions. Mutation M2 substitutes the net rule and the exit-race test fails.</t>
+        </is>
+      </c>
+      <c r="G140" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_reconciliation.py::TestAc2NoFalseHaltFromARace::test_an_exit_fill_between_the_reads_is_not_unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="150" customHeight="1" s="59">
+      <c r="A141" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-21</t>
+        </is>
+      </c>
+      <c r="B141" s="76" t="inlineStr">
+        <is>
+          <t>E15-S09</t>
+        </is>
+      </c>
+      <c r="C141" s="76" t="inlineStr">
+        <is>
+          <t>A closed position and a product this system never trades would each have halted</t>
+        </is>
+      </c>
+      <c r="D141" s="76" t="inlineStr">
+        <is>
+          <t>Design finding -&gt; designed out</t>
+        </is>
+      </c>
+      <c r="E141" s="76" t="inlineStr">
+        <is>
+          <t>Kite's positions list keeps rows for positions closed during the day at quantity 0, and includes products this system never trades. Mapping product through the closed Product enum would make one MTF holding - a real Zerodha product - fail every read, which is a halt after three cycles.</t>
+        </is>
+      </c>
+      <c r="F141" s="76" t="inlineStr">
+        <is>
+          <t>Found by reading Kite's own portfolio documentation rather than recalling the shape: the example payload shows a closed row at 0 and a signed -3 short. BrokerPosition keeps product and exchange as strings; the reconciler scopes to MIS on NSE and judges activity, not row presence.</t>
+        </is>
+      </c>
+      <c r="G141" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_reconciliation_wiring.py::TestAnUnknownPositionHaltsForReal (CNC/NRML/MTF parametrised; closed row).</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="150" customHeight="1" s="59">
+      <c r="A142" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-22</t>
+        </is>
+      </c>
+      <c r="B142" s="76" t="inlineStr">
+        <is>
+          <t>E15-S09</t>
+        </is>
+      </c>
+      <c r="C142" s="76" t="inlineStr">
+        <is>
+          <t>The decorator mistake QA-E15-18 recorded, repeated two days later</t>
+        </is>
+      </c>
+      <c r="D142" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E142" s="76" t="inlineStr">
+        <is>
+          <t>Inserting BrokerPosition above class MarketDataAdapter moved its @runtime_checkable decorator onto the new dataclass, and left the protocol without it.</t>
+        </is>
+      </c>
+      <c r="F142" s="76" t="inlineStr">
+        <is>
+          <t>Caught by mypy before any test ran, exactly as QA-E15-18 was. Recorded because the lesson had been written down - in CLAUDE.md, under things that turned out false - and did not prevent the repeat. The type checker prevented both. The useful conclusion is about where the defence lives, not about remembering harder.</t>
+        </is>
+      </c>
+      <c r="G142" s="76" t="inlineStr">
+        <is>
+          <t>mypy src/ (the gate that caught it); git diff confirms both @runtime_checkable decorators are where they were.</t>
         </is>
       </c>
     </row>
@@ -27095,7 +27383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -29087,6 +29375,90 @@
       <c r="H48" s="76" t="inlineStr">
         <is>
           <t>tests/integration/test_redis_layer.py::test_every_builder_is_declared, which fails today against the pre-fix tuple.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="76" t="inlineStr">
+        <is>
+          <t>REC-001</t>
+        </is>
+      </c>
+      <c r="B49" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C49" s="76" t="inlineStr">
+        <is>
+          <t>execution/reconciliation.py - order attribution</t>
+        </is>
+      </c>
+      <c r="D49" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E49" s="76" t="inlineStr">
+        <is>
+          <t>Attribution by tag can be spoofed. A broker order carrying our 20-character tag is counted as ours, and a tag is readable by anyone with access to the account. Faced with our FILLED entry and a foreign order with the same tag, the first version raised no halt, never examined the duplicate (terminal rows skip order reconciliation), and exited all 140 shares.</t>
+        </is>
+      </c>
+      <c r="F49" s="76" t="inlineStr">
+        <is>
+          <t>An unknown position hidden from the one check that exists to find it, and the reconciler trading 100 shares that were not ours - the one thing its design says it must never do. The non-malicious path is the same shape: a real duplicate from failed idempotency raised no halt when the row was terminal.</t>
+        </is>
+      </c>
+      <c r="G49" s="76" t="inlineStr">
+        <is>
+          <t>A cycle-level duplicate check that sees every key regardless of row status, halts with its own reason (HaltReason.DUPLICATE_ORDER - not UNKNOWN_POSITION, because the shares carry our key), reports once, and marks the correlation doubted so the unbooked-exit step never trades it. Found by the STRIDE pass against the story's own attribution rule; probed and confirmed failing first.</t>
+        </is>
+      </c>
+      <c r="H49" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_reconciliation.py::TestACopiedTagIsNotOurs (6 tests, incl. control). Mutations M22, M23 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="76" t="inlineStr">
+        <is>
+          <t>REC-002</t>
+        </is>
+      </c>
+      <c r="B50" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C50" s="76" t="inlineStr">
+        <is>
+          <t>execution/reconciliation.py - halt record</t>
+        </is>
+      </c>
+      <c r="D50" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E50" s="76" t="inlineStr">
+        <is>
+          <t>The BROKER_DISCONNECTED halt detail embedded the broker exception's message. The halt record is written to Redis, a sink the logging layer's redaction (RedactingFilter) never sees.</t>
+        </is>
+      </c>
+      <c r="F50" s="76" t="inlineStr">
+        <is>
+          <t>Any credential-shaped text in a broker exception would be stored unredacted in Redis for the rest of the day. Not demonstrated with a real Kite message - its errors name fields, not values - so graded MEDIUM rather than as a disclosure.</t>
+        </is>
+      </c>
+      <c r="G50" s="76" t="inlineStr">
+        <is>
+          <t>Structural rather than a scrub: the halt records the exception TYPE and the failure count, never its text. The full message still reaches the ERROR log line, which is redacted. One rung above scrubbing text on its way into a sink.</t>
+        </is>
+      </c>
+      <c r="H50" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_reconciliation.py::TestNothingSecretReachesTheHaltRecord. Mutation M30 killed.</t>
         </is>
       </c>
     </row>
@@ -29107,7 +29479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -29443,6 +29815,192 @@
         </is>
       </c>
       <c r="L8" s="76" t="inlineStr">
+        <is>
+          <t>None - fixed in the same session</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="190" customHeight="1" s="59">
+      <c r="A9" s="76" t="inlineStr">
+        <is>
+          <t>SIT-005</t>
+        </is>
+      </c>
+      <c r="B9" s="76" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C9" s="76" t="inlineStr">
+        <is>
+          <t>E15-S09</t>
+        </is>
+      </c>
+      <c r="D9" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E9" s="76" t="inlineStr">
+        <is>
+          <t>execution/reconciliation.py</t>
+        </is>
+      </c>
+      <c r="F9" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G9" s="76" t="inlineStr">
+        <is>
+          <t>One stranger's position on the account, seen by 30 consecutive cycles, produced 30 UNKNOWN_POS audit rows, 30 CRITICAL 'UNKNOWN POSITION' log lines and unknown_positions_total = 30. The counter's own help text says it counts positions; it was counting cycles.</t>
+        </is>
+      </c>
+      <c r="H9" s="76" t="inlineStr">
+        <is>
+          <t>Every unit test of the unknown path runs ONE cycle. Repetition is a property of a session - the stranger's position stays at the broker, so every later cycle sees it again - and only a test that runs the loop after every fill of a day can see what the alert does on the thirtieth look.</t>
+        </is>
+      </c>
+      <c r="I9" s="76" t="inlineStr">
+        <is>
+          <t>Detection and alerting were the same step. Refusals and duplicates had already been made report-once in this story; the unknown path - the one that matters most - had not, and the asymmetry went unnoticed until a session exercised it.</t>
+        </is>
+      </c>
+      <c r="J9" s="76" t="inlineStr">
+        <is>
+          <t>Detection still runs every cycle (report.unknown). The alert - log, counter, audit row - runs when a stranger is new or its size changes. The HALT is re-armed every cycle regardless, so an operator who clears the latch while an unknown position remains is halted again by the next cycle.</t>
+        </is>
+      </c>
+      <c r="K9" s="76" t="inlineStr">
+        <is>
+          <t>tests/sit/...::TestSit19...::test_a_stranger_is_alerted_once_not_every_cycle; tests/unit/test_reconciliation.py::TestAStrangerIsAlertedOnce (3). Mutations M37, M38.</t>
+        </is>
+      </c>
+      <c r="L9" s="76" t="inlineStr">
+        <is>
+          <t>None - fixed in the same session</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="190" customHeight="1" s="59">
+      <c r="A10" s="76" t="inlineStr">
+        <is>
+          <t>SIT-006</t>
+        </is>
+      </c>
+      <c r="B10" s="76" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C10" s="76" t="inlineStr">
+        <is>
+          <t>E15-S09</t>
+        </is>
+      </c>
+      <c r="D10" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E10" s="76" t="inlineStr">
+        <is>
+          <t>execution/reconciliation.py + execution/positions.py</t>
+        </is>
+      </c>
+      <c r="F10" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G10" s="76" t="inlineStr">
+        <is>
+          <t>A restart restored four positions; one had its stop rejected. The loop exited it correctly - and left it in the book as UnverifiedPosition. A ProtectedPosition whose stop died was likewise exited and still labelled ProtectedPosition. The next cycle ran the exit path again: a CRITICAL 'NAKED POSITION ... Closing at market' line and a stop_attach_failures_total increment every 30 seconds for the rest of the day.</t>
+        </is>
+      </c>
+      <c r="H10" s="76" t="inlineStr">
+        <is>
+          <t>The unit test for this exact path asserted the defect. test_a_restored_position_with_no_stop_is_exited ended with 'assert isinstance(manager.tracked(INFY), UnverifiedPosition)' - the test wrote the stale label down as correct behaviour, so it could not fail. The SIT assertion was about the END state of a restart ('nothing may still be unknown'), which is a question about the book rather than about the call.</t>
+        </is>
+      </c>
+      <c r="I10" s="76" t="inlineStr">
+        <is>
+          <t>open_from_fill records ExitingPosition when attach fails; the reconciler exited through the same path and recorded nothing. The book then claimed a protection the broker had just disproved - the one state E15-S05's three types exist to make impossible. Graded HIGH because it is a silent wrong answer in the book, and because the repeated CRITICAL line degrades the one alert channel naked positions have.</t>
+        </is>
+      </c>
+      <c r="J10" s="76" t="inlineStr">
+        <is>
+          <t>PositionManager.mark_exiting, called after exit_now succeeds (exit_now verifies the exit is live and raises having halted if not). A FAILED exit leaves the label alone: there is no live exit, and calling it EXITING would be the same false claim in the other direction.</t>
+        </is>
+      </c>
+      <c r="K10" s="76" t="inlineStr">
+        <is>
+          <t>tests/sit/...::TestSit19...::test_a_restart_resolves_every_restored_position_in_one_cycle; tests/unit/test_reconciliation.py::TestAnExitedPositionSaysSo (5). Mutation M36.</t>
+        </is>
+      </c>
+      <c r="L10" s="76" t="inlineStr">
+        <is>
+          <t>None - fixed in the same session</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="190" customHeight="1" s="59">
+      <c r="A11" s="76" t="inlineStr">
+        <is>
+          <t>SIT-007</t>
+        </is>
+      </c>
+      <c r="B11" s="76" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C11" s="76" t="inlineStr">
+        <is>
+          <t>E15-S09</t>
+        </is>
+      </c>
+      <c r="D11" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="E11" s="76" t="inlineStr">
+        <is>
+          <t>tests/sit (test infrastructure, Windows only)</t>
+        </is>
+      </c>
+      <c r="F11" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G11" s="76" t="inlineStr">
+        <is>
+          <t>The full suite hung - zero CPU, no output - inside SIT, in a test that passes in 2.7 s alone. Three runs hung this way across two days, including the E15-S05 SIT runs against the QA worktree.</t>
+        </is>
+      </c>
+      <c r="H11" s="76" t="inlineStr">
+        <is>
+          <t>Linux CI cannot see it: Linux has a native socketpair syscall. On Windows it needs enough event loops in ONE process for a rare loopback failure to happen, which is why it passed alone and hung in the suite.</t>
+        </is>
+      </c>
+      <c r="I11" s="76" t="inlineStr">
+        <is>
+          <t>Every asyncio.run builds a new event loop; on Windows each loop's self-pipe is socket.socketpair(), which CPython emulates with a real loopback TCP connection and then waits for in accept() with NO timeout. The SIT module walks sessions minute by minute and created thousands of loops per test. The pytest faulthandler dump showed the test blocked in socketpair -&gt; accept, and the process's socket table showed a 127.0.0.1 listener in LISTEN with no peer ever connected. THE EARLIER DIAGNOSIS WAS WRONG: on 24 Sep the E15-S05 QA stall was attributed to orphaned pytest processes, 'confirmed' by the next run passing after they were killed. The pass was coincidence - a probabilistic hang that did not recur on that run.</t>
+        </is>
+      </c>
+      <c r="J11" s="76" t="inlineStr">
+        <is>
+          <t>One event loop per SIT module via asyncio.Runner (closer to production, which runs one long-lived loop): SIT went from 49-78 s to 17 s with no hang. faulthandler_timeout = 300 in pytest config, so any future hang dumps every thread's stack instead of waiting in silence. Production is unaffected.</t>
+        </is>
+      </c>
+      <c r="K11" s="76" t="inlineStr">
+        <is>
+          <t>No test can prove a probabilistic hang absent. The structural change removes the thousands of loop creations that made it likely, and faulthandler_timeout turns any recurrence into a named stack rather than a silent stall.</t>
+        </is>
+      </c>
+      <c r="L11" s="76" t="inlineStr">
         <is>
           <t>None - fixed in the same session</t>
         </is>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4530,7 +4530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X204"/>
+  <dimension ref="A1:X205"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -15759,7 +15759,8 @@
 2. AN EXIT IS NOT DONE WHEN IT IS PLACED. Reuse PositionManager.confirm_exit: it gates on filled_quantity, leaves a partially filled exit open for the remainder, and is the only thing that writes the close. A timer that treated submission as closure would drop positions out of the book while they were still held.
 3. PASS YOUR OWN ExitReason (TIME). confirm_exit defaults to UNPROTECTED because E15-S05's only caller is the failed-stop path.
 CONSTRAINT INHERITED FROM E15-S09 (24 Sep 2026).
-4. THE SQUARE-OFF EXIT SHARES ITS KEY WITH THE RECONCILER'S EMERGENCY EXIT. Both are intent=SQUAREOFF on the same correlation, so the gateway treats a second one as a replay of the first and resumes it rather than placing a new order. That is right while the first is working and wrong once it has been CANCELLED part-filled: the remainder cannot be exited under that key, and the exit path halts instead. Decide whether the timer needs its own intent (ExitReason TIME exists; OrderIntent has no TIME member).</t>
+4. THE SQUARE-OFF EXIT SHARES ITS KEY WITH THE RECONCILER'S EMERGENCY EXIT. Both are intent=SQUAREOFF on the same correlation, so the gateway treats a second one as a replay of the first and resumes it rather than placing a new order. That is right while the first is working and wrong once it has been CANCELLED part-filled: the remainder cannot be exited under that key, and the exit path halts instead. Decide whether the timer needs its own intent (ExitReason TIME exists; OrderIntent has no TIME member).
+5. CANCEL THE PROTECTIVE STOP BEFORE THE SQUARE-OFF EXIT (E15-S12). A timer exit placed while the stop is still working means two exits for one position; if both fill, our sells outrun our buys and the OVER_EXITED guard halts the day. OrderGateway.cancel now exists for exactly this.</t>
         </is>
       </c>
     </row>
@@ -15908,6 +15909,13 @@
         </is>
       </c>
       <c r="W134" s="49" t="n"/>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>CONSTRAINT INHERITED FROM E15-S12 (30 Sep 2026).
+1. A PARTIAL stop or exit fill leaves the position HELD at its original quantity - confirm_exit does not reduce it. Reducing the book on a partial exit is this story's.
+2. Only FINISHED entries are booked, so a booked position cannot grow today. If this story ever books a working entry, the stop must be resized as it grows, or the later shares have no stop.</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="30" customHeight="1" s="59">
       <c r="A135" s="38" t="inlineStr">
@@ -16025,7 +16033,9 @@
 POLICY, STATED SO IT IS A CHOICE: MIS only (CNC/NRML/MTF are the owner's and never halt). ANY unexplained MIS fill halts - including a foreign sale netting against our long, which leaves our stop selling shares that are gone. The owner trading MIS by hand on the same account WILL halt the system. The loop never trades an unknown position, and alerts separately from the halt.
 FOUND IN THE CODE BEFORE WRITING ANY: the adapter protocol, the Kite adapter and the design doc gave fetch_positions three different return types; subscribe was declared a coroutine while every implementation is an async iterator. Nothing checked conformance - @runtime_checkable checks names, not signatures. Now type-checked (_conforms in broker/kite/trading.py).
 FOUND BY THE PRIMARY SOURCE: Kite keeps positions closed during the day in the net list at quantity 0, and quantity is signed. A reader treating every row as open sees a book full of positions that are not there.
-TESTS: 2,239 -&gt; 2,361; coverage 92% -&gt; 93%; 86 reconciler unit + 16 integration (real Postgres, Redis, Kite mapping) + 9 ProtectiveStop unit + 11 SIT-19. Mutation: 38 injected, 38 killed (32/35 on the first run; 3 test gaps closed, then M36-M38 added for SIT-005/006).</t>
+TESTS: 2,239 -&gt; 2,361; coverage 92% -&gt; 93%; 86 reconciler unit + 16 integration (real Postgres, Redis, Kite mapping) + 9 ProtectiveStop unit + 11 SIT-19. Mutation: 38 injected, 38 killed (32/35 on the first run; 3 test gaps closed, then M36-M38 added for SIT-005/006).
+SIT AGAINST THE PROMOTED QA TREE, 24 Sep 2026: QA e12a708 (DEV 2f1bc6e), CI green on both. 174 passed, 0 failed, 34 s.
+QA-E15-23 (30 Sep 2026, found during E15-S12): a working partial entry that keeps filling after the loop exits it leaves the new shares naked - CRITICAL, fixed in E15-S12. This story's AC7 was met for a fill that no longer changes and missed the one that does.</t>
         </is>
       </c>
       <c r="W135" s="49" t="n"/>
@@ -21243,7 +21253,7 @@
       </c>
       <c r="E204" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F204" s="41" t="inlineStr">
@@ -21279,9 +21289,11 @@
       <c r="N204" s="45" t="n"/>
       <c r="O204" s="44" t="n"/>
       <c r="P204" s="44" t="n"/>
-      <c r="Q204" s="44" t="n"/>
+      <c r="Q204" s="44" t="n">
+        <v>100</v>
+      </c>
       <c r="R204" s="39" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S204" s="48" t="inlineStr">
         <is>
@@ -21290,22 +21302,40 @@
       </c>
       <c r="T204" s="48" t="inlineStr">
         <is>
-          <t>1. Carry the approved sizing, slot and CAS flag from submission to fill (the orders table has none of them)
-2. Entry observed FILLED or PARTIAL -&gt; PositionManager.open_from_fill
-3. Stop observed FILLED -&gt; confirm_exit(reason=STOP); square-off exit FILLED -&gt; confirm_exit(reason=UNPROTECTED or TIME)
-4. After a restart, a fill with no recorded sizing cannot be booked correctly and is exited, not guessed</t>
+          <t>1. Carry the approved sizing, slot and CAS flag from submission to fill (the orders table has none of them) - an EntryPlan registered with the position manager
+2. Entry observed FILLED (terminal) -&gt; PositionManager.open_from_fill, BEFORE the unbooked-exit step
+3. Stop observed FILLED -&gt; confirm_exit(reason=STOP); emergency exit FILLED -&gt; confirm_exit(reason=UNPROTECTED)
+4. A fill with no plan (e.g. after a restart) is exited, never booked on a guess
+5. ADDED: a still-working entry with a partial fill is FROZEN (remainder cancelled through the gateway) before it is booked or exited
+6. ADDED: a holding that can no longer be exited under the day's exit key halts instead of being left silently (QA-E15-23, CRITICAL, found in E15-S09)
+7. ADDED: OrderGateway.cancel - the only path to cancelling an order, as placing is</t>
         </is>
       </c>
       <c r="U204" s="48" t="inlineStr">
         <is>
-          <t>AC1 (RED) An entry fill observed by reconciliation becomes a ProtectedPosition within the same cycle.
-AC2 (RED) A stopped-out position leaves the book with exit_reason STOP and its realised P&amp;L.
-AC3 (RED) A fill whose sizing is unknown is exited rather than booked with a guessed stop.</t>
+          <t>AC1 (RED) A terminal entry fill with an approved plan becomes a ProtectedPosition in the same cycle, before the unbooked-exit step runs.
+AC2 (RED) A position whose stop fills leaves the book with exit_reason STOP and its realised P&amp;L; one whose emergency exit fills leaves with UNPROTECTED.
+AC3 (RED) A fill with no plan is exited, never booked with a guessed stop.
+AC4 (RED) A working entry with a partial fill is frozen - its remainder cancelled - before it is booked or exited; one that cannot be frozen within three cycles halts (NAKED_POSITION).
+AC5 (RED) A holding that cannot be exited under the day's exit key (key already spent, or our exits exceeding our entries) halts rather than being left silently.
+AC6 A doubted correlation is never booked; a replayed booking (PositionAlreadyHeldError) is a normal outcome, not a failure.</t>
         </is>
       </c>
       <c r="V204" s="48" t="inlineStr">
         <is>
-          <t>RAISED 24 Sep 2026 by E15-S09's business analysis. Split out because open_from_fill needs data the orders table does not carry, which is a design problem of its own and would have doubled S09.</t>
+          <t>RAISED 24 Sep 2026 by E15-S09's business analysis. Split out because open_from_fill needs data the orders table does not carry, which is a design problem of its own and would have doubled S09.
+BUSINESS ANALYSIS, 30 Sep 2026.
+RESEARCH (primary source, fetched 30 Sep 2026): Zerodha's market-price-protection article says the exchange 'will either convert your order to a limit order, or cancel your order'. A secondary summary says the unexecuted remainder stays open as a limit order at the protection price. Both agree a remainder CAN stay working - which of the two happens when does not change the design: build for the worse one.
+THAT MAKES A PARTIAL ENTRY A MOVING TARGET. Book it and protect it, and its remainder can fill afterwards with no stop. Exit it, and the remainder can fill after the exit under a key that can only be used once. So a working partial entry is frozen first, and acted on once its quantity can no longer change.
+FOUND WHILE PROBING THAT, IN SHIPPED E15-S09 CODE (QA-E15-23, CRITICAL): an entry filling 40, then 30 more after the loop exited the 40, leaves 30 shares long with no stop, no exit, no halt and no alert - forever. The day's SQUAREOFF key is spent and exit_is_live counts the FILLED exit as live. Confirmed with the real gateway, real ProtectiveStop and real Reconciler, not by reasoning.
+DESIGN DECISION - PLANS ARE IN MEMORY, NOT DURABLE. The window between submission and booking is one cycle; a restart inside it exits the fill (AC3), which is safe and costs one trade. A durable plan table would book it instead, at the cost of a migration. Wrong if restarts during trading become common, or booking lags.
+OUT OF SCOPE, with owners: resizing a stop when a booked position grows, and reducing the book's quantity on a PARTIAL stop or exit fill - both E15-S08 (partial exits). Registering plans at submission - the pipeline wiring, which does not exist yet; this story delivers the registry and its consumer, as S04 and S05 delivered mechanisms before their callers.
+DELIVERED 30 Sep 2026. Step 3b of the reconciliation cycle, EntryPlan, OrderGateway.cancel.
+CLOSE, FREEZE, BOOK - in that order, and BEFORE the protection check and the unbooked-exit step. A stop that filled closes with STOP; an emergency exit with UNPROTECTED. A working partial entry is frozen - its remainder cancelled through the gateway, the only path to a cancel - and acted on once its quantity cannot change. A finished entry with a plan is booked; one without is exited, never booked on a guess.
+BOOKED UNDER OUR IDENTITY. The Kite adapter derives an order's correlation id from its truncated tag; booked from that, the stop key is wrong and the next step exits the position just protected. Proved against the real adapter.
+QA-E15-23 (CRITICAL, in E15-S09's shipped code) FIXED HERE: only a WORKING exit covers a holding. Anything uncovered once the day's exit key is spent (EXIT_SPENT), or our exits outrunning our entries (OVER_EXITED), halts once and re-arms every cycle.
+FOUND DURING THE STORY: two E15-S09 tests asserted what the fake allowed and the real key rule forbids (QA-E15-24); PositionManager accepted no calendar and failed at its first booking (QA-E15-25); an integration helper committed its session and leaked rows into the next file (QA-E15-26); a mutation survivor's test passed for the wrong reason (QA-E15-27); a booking failure's broker text reached the audit table (REC-003).
+TESTS: 2,361 -&gt; 2,419; coverage 93% flat; 30 reconciler unit + 8 position-manager unit + 9 gateway-cancel unit + 4 integration (real Postgres, Redis, Kite mapping) + 7 SIT-20. Mutation: 21 injected, 21 killed (19/21 first run; both survivors verified benign - second layers - and now held directly).</t>
         </is>
       </c>
       <c r="W204" s="49" t="n"/>
@@ -21316,6 +21346,104 @@
 2. open_from_fill raises PositionAlreadyHeldError on a replay (SIT-004). That is the normal outcome of a restart, not a failure to handle.
 3. A KEY ON MORE THAN ONE BROKER ORDER IS NOT BOOKABLE (REC-001). The reconciler halts on it and marks the correlation doubted; do not book a fill for a doubted correlation - some of those shares may not be ours.
 4. confirm_exit's default reason is UNPROTECTED. A stop fill is STOP; pass it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="38" t="inlineStr">
+        <is>
+          <t>E15-S13</t>
+        </is>
+      </c>
+      <c r="B205" s="39" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="C205" s="40" t="inlineStr">
+        <is>
+          <t>EXECUTION &amp; POSITIONS</t>
+        </is>
+      </c>
+      <c r="D205" s="40" t="inlineStr">
+        <is>
+          <t>Execution service: from signal to protected position</t>
+        </is>
+      </c>
+      <c r="E205" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F205" s="41" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G205" s="39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H205" s="50" t="inlineStr">
+        <is>
+          <t>Safety-critical</t>
+        </is>
+      </c>
+      <c r="I205" s="39" t="inlineStr">
+        <is>
+          <t>FEAT</t>
+        </is>
+      </c>
+      <c r="J205" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K205" s="40" t="inlineStr">
+        <is>
+          <t>E15-S12, E15-S09, E14-S07</t>
+        </is>
+      </c>
+      <c r="L205" s="40" t="n"/>
+      <c r="M205" s="44" t="n"/>
+      <c r="N205" s="45" t="n"/>
+      <c r="O205" s="44" t="n"/>
+      <c r="P205" s="44" t="n"/>
+      <c r="Q205" s="44" t="n"/>
+      <c r="R205" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="S205" s="48" t="inlineStr">
+        <is>
+          <t>As a trader, I want the execution service to take an approved signal all the way to a protected position and keep watching it, so that the mechanisms built separately in E15 actually run together.</t>
+        </is>
+      </c>
+      <c r="T205" s="48" t="inlineStr">
+        <is>
+          <t>1. Consume Recommendations from stream:signals; evaluate them with the real risk engine
+2. Allocate the slot, submit the entry, and register its EntryPlan with the position manager AS it is sent
+3. Run the reconciliation loop on its 30s schedule and on reconnect
+4. Restore the book on start-up before the first cycle
+5. Supply the CAS flag from instrument_daily_status (E04-S05 populates it)</t>
+        </is>
+      </c>
+      <c r="U205" s="48" t="inlineStr">
+        <is>
+          <t>AC1 (RED) An approved signal becomes a ProtectedPosition through the running service, end to end.
+AC2 (RED) A signal the risk engine rejects places nothing.
+AC3 (RED) A restart restores the book before the first cycle, so nothing held is mistaken for unbooked.</t>
+        </is>
+      </c>
+      <c r="V205" s="48" t="inlineStr">
+        <is>
+          <t>RAISED 30 Sep 2026 by E15-S12. S04, S05, S09 and S12 each delivered a mechanism and deliberately left its caller; this story is the caller. Until it exists nothing registers an EntryPlan when an entry is sent, so in production every fill is still exited as unprotected.</t>
+        </is>
+      </c>
+      <c r="W205" s="49" t="n"/>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>CONSTRAINT INHERITED FROM E15-S12 (30 Sep 2026).
+1. REGISTER THE PLAN BEFORE THE FIRST CYCLE CAN SEE THE FILL. A MARKET entry can fill before submit returns; a cycle that sees the fill with no plan exits it.
+2. RESTORE BEFORE RECONCILING. A cycle run on an empty book treats every held position as an unbooked fill and exits it.</t>
         </is>
       </c>
     </row>
@@ -22087,7 +22215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J142"/>
+  <dimension ref="A1:J148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -27363,6 +27491,228 @@
       <c r="G142" s="76" t="inlineStr">
         <is>
           <t>mypy src/ (the gate that caught it); git diff confirms both @runtime_checkable decorators are where they were.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="150" customHeight="1" s="59">
+      <c r="A143" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-23</t>
+        </is>
+      </c>
+      <c r="B143" s="76" t="inlineStr">
+        <is>
+          <t>E15-S09</t>
+        </is>
+      </c>
+      <c r="C143" s="76" t="inlineStr">
+        <is>
+          <t>A working partial entry that kept filling left shares naked, silently, forever</t>
+        </is>
+      </c>
+      <c r="D143" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed in E15-S12</t>
+        </is>
+      </c>
+      <c r="E143" s="76" t="inlineStr">
+        <is>
+          <t>Found during E15-S12's research, in code already on QA. Entry for 100 fills 40 and stays working; the loop exits the 40 as unbooked (correct); 30 more fill. Every later cycle: open quantity 30, exit_is_live(holding) -&gt; the SQUAREOFF key's order is FILLED, which is_live counts as live -&gt; skip. Result: net 30 long, no stop, no exit, no halt, no alert, for the rest of the day.</t>
+        </is>
+      </c>
+      <c r="F143" s="76" t="inlineStr">
+        <is>
+          <t>CRITICAL by the bug bar - a fail-open unprotected position. Two defects compound: the day's exit key can be used once, and 'is an exit live' was answering 'did an exit ever exist'. A FILLED exit covers the shares it sold, not shares bought after it. Probed with the real gateway, ProtectiveStop and Reconciler before any fix was written; the component tests could not see it because no double ever let an entry keep filling after it had been acted on.</t>
+        </is>
+      </c>
+      <c r="G143" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_reconciliation.py (E15-S12 additions) and SIT-20; see E15-S12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="150" customHeight="1" s="59">
+      <c r="A144" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-24</t>
+        </is>
+      </c>
+      <c r="B144" s="76" t="inlineStr">
+        <is>
+          <t>E15-S09</t>
+        </is>
+      </c>
+      <c r="C144" s="76" t="inlineStr">
+        <is>
+          <t>Two tests asserted what a fake allowed and the real system forbids</t>
+        </is>
+      </c>
+      <c r="D144" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E144" s="76" t="inlineStr">
+        <is>
+          <t>test_a_holding_whose_exit_is_already_working_is_not_exited_again modelled 'an exit is working' by telling the fake protector exit_is_live=True. test_only_the_open_remainder_is_exited asserted an exit for the 25 left after a cancelled partial exit.</t>
+        </is>
+      </c>
+      <c r="F144" s="76" t="inlineStr">
+        <is>
+          <t>The second asserted a capability the system does not have: the day's SQUAREOFF key was spent, so the real gateway would have resumed the cancelled exit rather than place a new one, and ended in a halt. It passed only because the fake exit_now accepted any call. A double more capable than the real thing proves things that are not true - QA-E15-12's family, from the other side. Rewritten to assert what reality allows (a halt, EXIT_SPENT) and to model a working exit as a real order in the snapshot.</t>
+        </is>
+      </c>
+      <c r="G144" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_reconciliation.py::TestAc7UnbookedHoldings</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="150" customHeight="1" s="59">
+      <c r="A145" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-25</t>
+        </is>
+      </c>
+      <c r="B145" s="76" t="inlineStr">
+        <is>
+          <t>E15-S12</t>
+        </is>
+      </c>
+      <c r="C145" s="76" t="inlineStr">
+        <is>
+          <t>A position manager with no calendar constructed fine and failed at its first booking</t>
+        </is>
+      </c>
+      <c r="D145" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E145" s="76" t="inlineStr">
+        <is>
+          <t>PositionManager took calendar: Any and used it only inside open_from_fill. Built with None, it failed at the first booking - inside a reconciliation cycle, as an error the cycle recorded and moved past.</t>
+        </is>
+      </c>
+      <c r="F145" s="76" t="inlineStr">
+        <is>
+          <t>Found by the integration tests, whose wiring had passed None since E15-S09 when nothing booked. Mis-wired in production, every fill would quietly have become an exit. Now refused at construction - the same rule the manager's store follows: an absent capability must not read as a satisfied one.</t>
+        </is>
+      </c>
+      <c r="G145" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_positions.py::TestTheCalendarIsRequiredUpFront. Mutation M20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="150" customHeight="1" s="59">
+      <c r="A146" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-26</t>
+        </is>
+      </c>
+      <c r="B146" s="76" t="inlineStr">
+        <is>
+          <t>E15-S09</t>
+        </is>
+      </c>
+      <c r="C146" s="76" t="inlineStr">
+        <is>
+          <t>An integration helper committed its session and leaked rows into later files</t>
+        </is>
+      </c>
+      <c r="D146" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E146" s="76" t="inlineStr">
+        <is>
+          <t>_drift_rows called session.commit() to see the audit writer's rows. That persisted the test's orders and positions past its rollback. test_position_manager_wiring's exactly-one-row assertions then failed - but only when the reconciliation file ran first.</t>
+        </is>
+      </c>
+      <c r="F146" s="76" t="inlineStr">
+        <is>
+          <t>The commit was never needed: under READ COMMITTED a new statement already sees rows another session committed. Order-dependent failures are findings, not flakes; this one was invisible in the suite's normal alphabetical order.</t>
+        </is>
+      </c>
+      <c r="G146" s="76" t="inlineStr">
+        <is>
+          <t>Both files, run in the adverse order: 33 passed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="150" customHeight="1" s="59">
+      <c r="A147" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-27</t>
+        </is>
+      </c>
+      <c r="B147" s="76" t="inlineStr">
+        <is>
+          <t>E15-S12</t>
+        </is>
+      </c>
+      <c r="C147" s="76" t="inlineStr">
+        <is>
+          <t>A test written to kill a mutation survivor passed for the wrong reason</t>
+        </is>
+      </c>
+      <c r="D147" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E147" s="76" t="inlineStr">
+        <is>
+          <t>The direct test for mutation M15 (booking a doubted correlation) passed with the mutation applied. Its broker fill had no average price, so confirm_fill refused it as contradictory and booking failed on THAT, whatever the doubted check did.</t>
+        </is>
+      </c>
+      <c r="F147" s="76" t="inlineStr">
+        <is>
+          <t>Found only because the survivor was re-run after the test was added, rather than the test being trusted. Each of these tests now asserts the cycle recorded no errors, and the booking test has a control that books.</t>
+        </is>
+      </c>
+      <c r="G147" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_reconciliation.py::TestS12TheSecondLayersHoldOnTheirOwn. M4 and M15 killed on re-run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="150" customHeight="1" s="59">
+      <c r="A148" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-28</t>
+        </is>
+      </c>
+      <c r="B148" s="76" t="inlineStr">
+        <is>
+          <t>E15-S09</t>
+        </is>
+      </c>
+      <c r="C148" s="76" t="inlineStr">
+        <is>
+          <t>The reconciliation integration file left audit rows for whichever file ran next</t>
+        </is>
+      </c>
+      <c r="D148" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E148" s="76" t="inlineStr">
+        <is>
+          <t>The full gate failed test_repositories::test_max_seq_starts_at_zero - an empty chain expected, 4 rows found. The reconciliation wiring tests write through the real AuditWriter, which commits in its own session; their fixture cleared decision_log at the START of each test but not the end.</t>
+        </is>
+      </c>
+      <c r="F148" s="76" t="inlineStr">
+        <is>
+          <t>The leak existed since E15-S09 and was masked by test order: the file's last test then wrote nothing. E15-S12's booking tests, now last, write BOOKED and CLOSED rows. Second order-dependent leak from the same file in one story (QA-E15-26 was the first) - a fixture that shares a table must leave it as it found it, at both ends. Found by the full gate, not by running the new tests.</t>
+        </is>
+      </c>
+      <c r="G148" s="76" t="inlineStr">
+        <is>
+          <t>The three files in suite order: 77 passed; full gate re-run.</t>
         </is>
       </c>
     </row>
@@ -27383,7 +27733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -29459,6 +29809,48 @@
       <c r="H50" s="76" t="inlineStr">
         <is>
           <t>tests/unit/test_reconciliation.py::TestNothingSecretReachesTheHaltRecord. Mutation M30 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="76" t="inlineStr">
+        <is>
+          <t>REC-003</t>
+        </is>
+      </c>
+      <c r="B51" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C51" s="76" t="inlineStr">
+        <is>
+          <t>execution/reconciliation.py - booking drift</t>
+        </is>
+      </c>
+      <c r="D51" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E51" s="76" t="inlineStr">
+        <is>
+          <t>When booking failed with StopNotEstablishedError, the UNPROTECTED drift detail carried that exception's message - which embeds the broker's own error text - into decision_log, a sink the logging layer's redaction never sees.</t>
+        </is>
+      </c>
+      <c r="F51" s="76" t="inlineStr">
+        <is>
+          <t>Broker error text stored unredacted in the audit table. Same class as REC-002, one sink along. Not demonstrated with a real Kite message, so MEDIUM.</t>
+        </is>
+      </c>
+      <c r="G51" s="76" t="inlineStr">
+        <is>
+          <t>The detail records the exception TYPE only. Found by the STRIDE pass against E15-S12's own diff.</t>
+        </is>
+      </c>
+      <c r="H51" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_reconciliation.py::TestS12NothingSecretReachesTheAuditTable. Mutation M17 killed.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -21335,7 +21335,8 @@
 BOOKED UNDER OUR IDENTITY. The Kite adapter derives an order's correlation id from its truncated tag; booked from that, the stop key is wrong and the next step exits the position just protected. Proved against the real adapter.
 QA-E15-23 (CRITICAL, in E15-S09's shipped code) FIXED HERE: only a WORKING exit covers a holding. Anything uncovered once the day's exit key is spent (EXIT_SPENT), or our exits outrunning our entries (OVER_EXITED), halts once and re-arms every cycle.
 FOUND DURING THE STORY: two E15-S09 tests asserted what the fake allowed and the real key rule forbids (QA-E15-24); PositionManager accepted no calendar and failed at its first booking (QA-E15-25); an integration helper committed its session and leaked rows into the next file (QA-E15-26); a mutation survivor's test passed for the wrong reason (QA-E15-27); a booking failure's broker text reached the audit table (REC-003).
-TESTS: 2,361 -&gt; 2,419; coverage 93% flat; 30 reconciler unit + 8 position-manager unit + 9 gateway-cancel unit + 4 integration (real Postgres, Redis, Kite mapping) + 7 SIT-20. Mutation: 21 injected, 21 killed (19/21 first run; both survivors verified benign - second layers - and now held directly).</t>
+TESTS: 2,361 -&gt; 2,419; coverage 93% flat; 30 reconciler unit + 8 position-manager unit + 9 gateway-cancel unit + 4 integration (real Postgres, Redis, Kite mapping) + 7 SIT-20. Mutation: 21 injected, 21 killed (19/21 first run; both survivors verified benign - second layers - and now held directly).
+SIT AGAINST THE PROMOTED QA TREE, 15 Oct 2026: QA 4426069 (DEV 21c042c, CI green on DEV). 181 passed, 0 failed, including all 7 SIT-20 scenarios; Documents/, scripts/tracker and .claude absent from the QA tree.</t>
         </is>
       </c>
       <c r="W204" s="49" t="n"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -27734,7 +27734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -29813,7 +29813,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" s="59">
       <c r="A51" s="76" t="inlineStr">
         <is>
           <t>REC-003</t>
@@ -29852,6 +29852,132 @@
       <c r="H51" s="76" t="inlineStr">
         <is>
           <t>tests/unit/test_reconciliation.py::TestS12NothingSecretReachesTheAuditTable. Mutation M17 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="76" t="inlineStr">
+        <is>
+          <t>DEP-001</t>
+        </is>
+      </c>
+      <c r="B52" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C52" s="76" t="inlineStr">
+        <is>
+          <t>Dependency supply chain - urllib3 (via requests/kiteconnect, docker, testcontainers)</t>
+        </is>
+      </c>
+      <c r="D52" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E52" s="76" t="inlineStr">
+        <is>
+          <t>QA CI on the E15-S12 promotion (4426069) failed the dependency audit: urllib3 2.7.0 carries PYSEC-2026-4175 (CVE-2026-97687, HTTPS-proxy TLS settings not separated from the target's - CERT_NONE for a target could disable proxy certificate verification in place), PYSEC-2026-4176 (CVE-2026-97688, infinite loop streaming a chunked deflate response with trailing bytes) and PYSEC-2026-4177 (CVE-2026-97689, unbounded buffering of a chunk-size line). All fixed in 2.8.0. Published after the DEV audit passed on 30 Sep; no dependency changed between the two runs.</t>
+        </is>
+      </c>
+      <c r="F52" s="76" t="inlineStr">
+        <is>
+          <t>urllib3 is the transport under requests, which kiteconnect uses for every broker REST call - orders, positions, the order book. The streaming bugs need a malicious server and the proxy bug needs an HTTPS forwarding proxy, neither configured today, but the broker channel is the one path where a degraded or impersonated peer reaches money.</t>
+        </is>
+      </c>
+      <c r="G52" s="76" t="inlineStr">
+        <is>
+          <t>constraints.txt urllib3==2.7.0 -&gt; 2.8.0 (pure Python; requests bounds &lt;3, docker &gt;=1.26, testcontainers unbounded - resolution unchanged otherwise). pip check clean apart from the known, intended autobahn override (B7).</t>
+        </is>
+      </c>
+      <c r="H52" s="76" t="inlineStr">
+        <is>
+          <t>pip-audit --skip-editable --ignore-vuln CVE-2026-106454 exits 0; full gate green on the bump; CI's audit step is the regression check and now also prints the urllib3 version it audited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="76" t="inlineStr">
+        <is>
+          <t>DEP-002</t>
+        </is>
+      </c>
+      <c r="B53" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C53" s="76" t="inlineStr">
+        <is>
+          <t>Dependency supply chain - Twisted (via kiteconnect -&gt; autobahn[twisted])</t>
+        </is>
+      </c>
+      <c r="D53" s="76" t="inlineStr">
+        <is>
+          <t>Accepted risk</t>
+        </is>
+      </c>
+      <c r="E53" s="76" t="inlineStr">
+        <is>
+          <t>Twisted 26.4.0 carries CVE-2026-106454 / GHSA-8pqf-f4m5-798g (CVSS 4.3, published to GitHub 15 Aug 2026, to NVD 6 Oct): wildcardToRegexp() in twisted/mail/imap4.py compiles an IMAP LIST/LSUB pattern without escaping it, so an authenticated IMAP client can send a catastrophic-backtracking regex and stall a Twisted IMAP SERVER's reactor. Affected &lt;= 26.4.0, patched: none (advisory checked 15 Oct 2026). The vulnerable source was confirmed present on disk in the installed package.</t>
+        </is>
+      </c>
+      <c r="F53" s="76" t="inlineStr">
+        <is>
+          <t>None reachable. Exploitation needs a Twisted IMAP4 server accepting logins. This system runs no IMAP server, never runs the Twisted reactor, and never imports twisted.mail: importing kiteconnect plus every algotrader module in a clean interpreter loads 90 Twisted modules and none under twisted.mail. Twisted cannot be removed (kiteconnect/__init__ imports .ticker, which imports twisted.internet) or upgraded past the finding (no fixed release). Rated LOW for this system: present, unreachable, availability-only.</t>
+        </is>
+      </c>
+      <c r="G53" s="76" t="inlineStr">
+        <is>
+          <t>The audit ignores exactly this ID (--ignore-vuln CVE-2026-106454) in both CI commands and make audit - never the package, so any OTHER Twisted advisory still fails the gate. The ignore is an executable claim: ACCEPTED_ADVISORIES records the ID with the package and the version it was assessed against.</t>
+        </is>
+      </c>
+      <c r="H53" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_dependency_hygiene.py::TestTheAcceptedTwistedAdvisory (8 tests): the clean-interpreter load probe never reaches twisted.mail, with a control proving the probe sees it when it IS imported; no src file imports twisted/autobahn, with a control on the scanner; every audit site ignores exactly the accepted set; the installed and constrained Twisted equal the assessed version, so a Twisted upgrade fails the build until the ignore is removed or re-assessed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="76" t="inlineStr">
+        <is>
+          <t>DEP-003</t>
+        </is>
+      </c>
+      <c r="B54" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C54" s="76" t="inlineStr">
+        <is>
+          <t>Build tooling - Makefile audit target</t>
+        </is>
+      </c>
+      <c r="D54" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E54" s="76" t="inlineStr">
+        <is>
+          <t>make audit ran bare `pip-audit` while CI ran `pip-audit --skip-editable`. The two audits were not the same check, and the local one was the one the sdlc skill did not point at.</t>
+        </is>
+      </c>
+      <c r="F54" s="76" t="inlineStr">
+        <is>
+          <t>A developer's audit and CI's could disagree about whether the tree was clean. Found by the new audit-site test on its first run, before any wiring - the probe failed for a reason nobody had written down.</t>
+        </is>
+      </c>
+      <c r="G54" s="76" t="inlineStr">
+        <is>
+          <t>make audit now runs the CI command verbatim, including the accepted advisory; the sdlc skill's Phase 7 command is `make audit`.</t>
+        </is>
+      </c>
+      <c r="H54" s="76" t="inlineStr">
+        <is>
+          <t>TestTheAcceptedTwistedAdvisory::test_every_audit_is_skip_editable_and_not_strict and ::test_every_audit_ignores_exactly_the_accepted_set cover both sites.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -21336,7 +21336,9 @@
 QA-E15-23 (CRITICAL, in E15-S09's shipped code) FIXED HERE: only a WORKING exit covers a holding. Anything uncovered once the day's exit key is spent (EXIT_SPENT), or our exits outrunning our entries (OVER_EXITED), halts once and re-arms every cycle.
 FOUND DURING THE STORY: two E15-S09 tests asserted what the fake allowed and the real key rule forbids (QA-E15-24); PositionManager accepted no calendar and failed at its first booking (QA-E15-25); an integration helper committed its session and leaked rows into the next file (QA-E15-26); a mutation survivor's test passed for the wrong reason (QA-E15-27); a booking failure's broker text reached the audit table (REC-003).
 TESTS: 2,361 -&gt; 2,419; coverage 93% flat; 30 reconciler unit + 8 position-manager unit + 9 gateway-cancel unit + 4 integration (real Postgres, Redis, Kite mapping) + 7 SIT-20. Mutation: 21 injected, 21 killed (19/21 first run; both survivors verified benign - second layers - and now held directly).
-SIT AGAINST THE PROMOTED QA TREE, 15 Oct 2026: QA 4426069 (DEV 21c042c, CI green on DEV). 181 passed, 0 failed, including all 7 SIT-20 scenarios; Documents/, scripts/tracker and .claude absent from the QA tree.</t>
+SIT AGAINST THE PROMOTED QA TREE, 15 Oct 2026: QA 4426069 (DEV 21c042c, CI green on DEV). 181 passed, 0 failed, including all 7 SIT-20 scenarios; Documents/, scripts/tracker and .claude absent from the QA tree.
+QA CI ON 4426069 WAS RED, 15 Oct 2026 - not this story's code. The Tests job passed; the Security job's dependency audit failed on four advisories published between the DEV run (30 Sep) and the QA run: three in urllib3 2.7.0 and one in Twisted 26.4.0 (DEP-001, DEP-002, DEP-003). Fixed in DEV 2125817 - urllib3 2.8.0; the Twisted IMAP-server advisory, which has no patched release and is unreachable here, is ignored by ID and the ignore is held by TestTheAcceptedTwistedAdvisory. Full gate 2,427 passed, 0 skipped, coverage 93%.
+RE-PROMOTED AND SIT RE-RUN, 15 Oct 2026: QA e28427e (DEV 2125817), CI green on DEV and QA. 201 passed, 0 failed - all 181 SIT scenarios including the 7 SIT-20 ones, plus the 20 dependency-hygiene tests - run from a worktree of the QA branch with algotrader confirmed loaded from that tree. Documents/, scripts/tracker and .claude absent from QA. No new SIT defects.</t>
         </is>
       </c>
       <c r="W204" s="49" t="n"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -8201,7 +8201,11 @@
 • Every holiday in the circular is excluded by `is_trading_day`</t>
         </is>
       </c>
-      <c r="V44" s="48" t="n"/>
+      <c r="V44" s="48" t="inlineStr">
+        <is>
+          <t>DATED, 27 Oct 2026: config/nse_holidays.yaml covers 2026 only. MarketCalendar fails CLOSED on an uncovered year (HolidayDataError), so from 1 Jan 2027 the system refuses to trade until the 2027 list is added. NSE publishes it in December; add it, triangulated against two publications as the 2026 list was, before the last trading day of 2026.</t>
+        </is>
+      </c>
       <c r="W44" s="49" t="n"/>
       <c r="X44" s="75" t="inlineStr">
         <is>
@@ -21446,7 +21450,12 @@
         <is>
           <t>CONSTRAINT INHERITED FROM E15-S12 (30 Sep 2026).
 1. REGISTER THE PLAN BEFORE THE FIRST CYCLE CAN SEE THE FILL. A MARKET entry can fill before submit returns; a cycle that sees the fill with no plan exits it.
-2. RESTORE BEFORE RECONCILING. A cycle run on an empty book treats every held position as an unbooked fill and exits it.</t>
+2. RESTORE BEFORE RECONCILING. A cycle run on an empty book treats every held position as an unbooked fill and exits it.
+CONSTRAINTS FROM THE 27 OCT 2026 VERIFICATION (QA-VER-01).
+1. BUILD THE RISK ENGINE THROUGH ONE FACTORY that registers all fourteen checks in canonical order and asserts the id list equals all_check_ids(). RiskEngine(checks=[], sizer=...) approves everything - a legitimate test affordance, and a total bypass if production ever constructs one by hand.
+2. EvalContext.entries_today MUST come from the order book (entries this strategy made in this symbol today). None refuses to fire - max_entries_per_day defaults to 1 and is now enforced (AUDIT-012). EvalContext.sector likewise, for strategies restricted to sectors.
+3. PAIR EVERY DECISION WITH THE RECOMMENDATION IT WAS EVALUATED WITH. The gateway now refuses a mismatch (AUDIT-006); the SIT harness had it wrong for weeks (SIT-008).
+4. RECONCILIATION READS SHARE THE DATA TOKEN BUCKET WITH BACKFILL. A backfill draining the bucket makes the 30-second reads fail, and three consecutive failures arm BROKER_DISCONNECTED. Either keep backfill out of the session or give reconciliation its own budget.</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J148"/>
+  <dimension ref="A1:J149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -22246,6 +22255,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="82" t="inlineStr">
         <is>
@@ -27716,6 +27726,43 @@
       <c r="G148" s="76" t="inlineStr">
         <is>
           <t>The three files in suite order: 77 passed; full gate re-run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="76" t="inlineStr">
+        <is>
+          <t>QA-VER-01</t>
+        </is>
+      </c>
+      <c r="B149" s="76" t="inlineStr">
+        <is>
+          <t>Whole system</t>
+        </is>
+      </c>
+      <c r="C149" s="76" t="inlineStr">
+        <is>
+          <t>Verification of everything built, 27 Oct 2026: every built package read for edge cases and security, probes for each suspicion, fixes with tests.</t>
+        </is>
+      </c>
+      <c r="D149" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E149" s="76" t="inlineStr">
+        <is>
+          <t>16 findings in built code (AUDIT-006..021: 1 CRITICAL latent, 6 HIGH, 4 MEDIUM, 5 LOW), 4 dependency findings (DEP-004..007), 1 SIT harness defect (SIT-008). See Security Findings / SIT Defects for each.</t>
+        </is>
+      </c>
+      <c r="F149" s="76" t="inlineStr">
+        <is>
+          <t>Recurring shapes, each now covered structurally: a denylist where an allowlist was needed (is_live); a declaration enforced by nothing (strategy constraints, three indexes); 'unknown' reading as a safe value (slots, entries_today); a filter whose baseline could lock (outlier); a credential in a plain str (KiteFeed); two objects passed separately with nothing tying them (decision/recommendation).</t>
+        </is>
+      </c>
+      <c r="G149" s="76" t="inlineStr">
+        <is>
+          <t>Full gate: 2,427 -&gt; 2,581 passed, 0 skipped, coverage 93% (flat); ruff, format, mypy, bandit clean; pip-audit clean with 6 assessed ignores. Mutation testing on the fixes: 33/33 mutations killed (32/33 first run; M32 survivor verified benign - anchors refused first - and closed with an alias-only test).</t>
         </is>
       </c>
     </row>
@@ -27736,7 +27783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -27765,6 +27812,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -29980,6 +30028,846 @@
       <c r="H54" s="76" t="inlineStr">
         <is>
           <t>TestTheAcceptedTwistedAdvisory::test_every_audit_is_skip_editable_and_not_strict and ::test_every_audit_ignores_exactly_the_accepted_set cover both sites.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-006</t>
+        </is>
+      </c>
+      <c r="B55" s="76" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C55" s="76" t="inlineStr">
+        <is>
+          <t>execution/gateway.py + common/models/trading.py - decision binding</t>
+        </is>
+      </c>
+      <c r="D55" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E55" s="76" t="inlineStr">
+        <is>
+          <t>RiskDecision carried no identity of the recommendation it decided - approved, sizing and checks_passed only - and OrderGateway.build_entry took the decision and the recommendation as two separate arguments. Nothing tied them together.</t>
+        </is>
+      </c>
+      <c r="F55" s="76" t="inlineStr">
+        <is>
+          <t>Latent today (no production caller yet; E15-S13 wires it), real the moment it is wired: an approval for one candidate handed in beside another's recommendation built an order for the second at the first one's size - another symbol, or the opposite direction - and every object involved validated on its own. Demonstrated in-repo: the SIT harness had done exactly this in every gateway submission for weeks (SIT-008).</t>
+        </is>
+      </c>
+      <c r="G55" s="76" t="inlineStr">
+        <is>
+          <t>RiskDecision gained correlation_id, symbol and direction, stamped by approve()/reject() from the recommendation; the engine passes it on all five exits. build_entry refuses a pair that is not is_for() each other with DecisionMismatchError, BEFORE the approval check, so crossed wiring is named rather than hidden behind 'not approved'.</t>
+        </is>
+      </c>
+      <c r="H55" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_gateway.py::TestADecisionIsOnlyEverSentForWhatItDecided (crossed symbol / direction / signal, nothing sent and no row written; control); tests/unit/test_risk_framework.py::TestEveryDecisionSaysWhatItDecided (all 7 engine exits; is_for control). Mutations M1-M4 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-007</t>
+        </is>
+      </c>
+      <c r="B56" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C56" s="76" t="inlineStr">
+        <is>
+          <t>ingest/kite_ws.py, broker/kite/session.py - credential holding</t>
+        </is>
+      </c>
+      <c r="D56" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E56" s="76" t="inlineStr">
+        <is>
+          <t>KiteFeed held the broker access token as a plain `str` field on a dataclass, whose generated __repr__ prints every field. exchange_request_token returned the raw token as a str, contradicting its own module's 'revealed in exactly two places'.</t>
+        </is>
+      </c>
+      <c r="F56" s="76" t="inlineStr">
+        <is>
+          <t>Invariant 4 violated in shipped code: any log line or traceback rendering the feed wrote the bearer credential in clear. It survived every audit because the only structural check looked at BrokerSession alone.</t>
+        </is>
+      </c>
+      <c r="G56" s="76" t="inlineStr">
+        <is>
+          <t>KiteFeed.access_token is a SecretString (a plain str is refused with TypeError) and is revealed only where the URL is built. exchange_request_token returns None; callers use build_client. A new structural invariant scans EVERY class in src for credential-named fields typed str, with an assessed allowlist (broker_token, instrument_token are public ids).</t>
+        </is>
+      </c>
+      <c r="H56" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_safety_invariants.py::TestCredentialsAreHeldAsSecrets (whole-src scan; control proves it flags the pre-fix KiteFeed); tests/unit/test_ingest_feed.py::TestTheFeedNeverHoldsThePlainToken. Mutation M18 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-008</t>
+        </is>
+      </c>
+      <c r="B57" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C57" s="76" t="inlineStr">
+        <is>
+          <t>common/logging.py + common/secrets.py - redaction</t>
+        </is>
+      </c>
+      <c r="D57" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E57" s="76" t="inlineStr">
+        <is>
+          <t>Probed with kiteconnect's own debug formats: the redactor let api_key, request_token, checksum and access_token through in JSON ('"api_key": "..."') and in Python dict repr, and had no pattern for Kite's 'token key:secret' Authorization header. register_secret_values was never called anywhere, so the value-scrubbing layer the module calls 'the real work' was empty. websockets/kiteconnect/requests were not pinned at WARNING. Found while fixing: the layers interfered - value-scrubbing first turned 'token key:secret' into 'token key:***', which the header pattern no longer matched, leaking the key (a test that passed alone and failed in the suite).</t>
+        </is>
+      </c>
+      <c r="F57" s="76" t="inlineStr">
+        <is>
+          <t>No live leak with default configuration (kiteconnect's debug output is gated on its own flag, which nothing sets), but a defence that silently did not cover what it claimed: one log.info of a session payload, or root logging at DEBUG, would have written broker credentials to disk.</t>
+        </is>
+      </c>
+      <c r="G57" s="76" t="inlineStr">
+        <is>
+          <t>Quoted-key pattern (keeps the key, masks the value); Kite header pattern; every SecretString registers its own value at construction (&gt;= 8 chars) and the redactor scrubs registered values longest-first; patterns now run BEFORE value-scrubbing; NOISY_LIBRARIES adds websockets, kiteconnect, requests.</t>
+        </is>
+      </c>
+      <c r="H57" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_log_redaction.py::TestTheShapesTheBrokerSdkActuallyLogs (6 real shapes + deterministic layer-interference case + no-false-positive control), ::TestASecretStringScrubsItsOwnValue, ::TestNoisyLibrariesStayQuietAtDebug. Mutations M20-M22, M33 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-009</t>
+        </is>
+      </c>
+      <c r="B58" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C58" s="76" t="inlineStr">
+        <is>
+          <t>execution/protective_stop.py + broker/kite/mapping.py - stop liveness</t>
+        </is>
+      </c>
+      <c r="D58" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E58" s="76" t="inlineStr">
+        <is>
+          <t>is_live() was a denylist - live meant 'not REJECTED or CANCELLED'. mapping.status_in sends every unrecognised Kite status to RECONCILE_REQUIRED, which therefore counted as a protecting stop. Kite documents three interim statuses the table did not map (CANCEL PENDING, MODIFY VALIDATION PENDING, AMO REQ RECEIVED; kite.trade/docs/connect/v3/orders fetched 27 Oct 2026) and says 'there may be other values as well'.</t>
+        </is>
+      </c>
+      <c r="F58" s="76" t="inlineStr">
+        <is>
+          <t>A stop in a status nobody could interpret produced an EstablishedPosition - a type whose whole meaning is 'the broker confirmed a live stop' - and the reconciliation predicate kept reporting the position as protected.</t>
+        </is>
+      </c>
+      <c r="G58" s="76" t="inlineStr">
+        <is>
+          <t>is_live is an allowlist: SUBMITTED, OPEN, PARTIAL, FILLED. The documented statuses are mapped explicitly so ordinary broker behaviour stays off the fail-closed path; an undocumented one now exits the position (and an exit in an unknown state halts).</t>
+        </is>
+      </c>
+      <c r="H58" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_protective_stop.py::...test_live_is_an_allowlist_over_every_status (every OrderStatus member), ::test_a_stop_in_a_status_nobody_modelled_is_exited_not_trusted; tests/unit/test_broker_kite.py::...test_every_documented_status_is_modelled. Mutations M8, M9 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-010</t>
+        </is>
+      </c>
+      <c r="B59" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C59" s="76" t="inlineStr">
+        <is>
+          <t>execution/risk/context.py - slots and open positions</t>
+        </is>
+      </c>
+      <c r="D59" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E59" s="76" t="inlineStr">
+        <is>
+          <t>slots_used was never checked for sign: slots_total=0, slots_used=-1 gave slots_available = 1. OpenPosition validated nothing: a negative quantity counted a long as a short, zero dropped a held position from every total, a NaN or negative price corrupted notional.</t>
+        </is>
+      </c>
+      <c r="F59" s="76" t="inlineStr">
+        <is>
+          <t>Latent (RiskContext is built only in tests until E14-S09/E15-S13 wiring), but each is a fail-OPEN: check 7 passing on a book with no slots, and the sector / net-exposure caps reading more room than exists.</t>
+        </is>
+      </c>
+      <c r="G59" s="76" t="inlineStr">
+        <is>
+          <t>Slot counts must be non-negative ints. OpenPosition.__post_init__ refuses non-positive or non-int quantity, non-finite or non-positive prices, a blank sector (unknown stays None, which check 9 refuses), a non-Direction direction.</t>
+        </is>
+      </c>
+      <c r="H59" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_risk_framework.py::TestSlotCountsCannotInventCapacity, ::TestAnOpenPositionCannotLoosenTheCaps (12 refusals + the arithmetic + control). Mutations M5-M7 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-011</t>
+        </is>
+      </c>
+      <c r="B60" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C60" s="76" t="inlineStr">
+        <is>
+          <t>ingest/cleaning.py - outlier filter and volume check</t>
+        </is>
+      </c>
+      <c r="D60" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E60" s="76" t="inlineStr">
+        <is>
+          <t>The outlier filter compared each print with the last ACCEPTED one and only an accepted print moved that baseline. Probed: a genuine 3% move at the open accepted 0 of the next 199 prints; a bad first print rejected 0 of 99 good ones. The volume check compared across sessions: a pipeline living past midnight accepted 0 of 50 next-session ticks.</t>
+        </is>
+      </c>
+      <c r="F60" s="76" t="inlineStr">
+        <is>
+          <t>An instrument froze at a stale price for the rest of the session while the rejection count read as routine (looks_unhealthy aggregates the whole universe) - and the names that freeze are exactly the ones moving most. A silent wrong answer.</t>
+        </is>
+      </c>
+      <c r="G60" s="76" t="inlineStr">
+        <is>
+          <t>REBASELINE_CONFIRMATIONS = 3 consecutive prints at a new level, each within the bound of the one before, re-anchor the filter; one bad print still never lands, a run broken by an ordinary print earns no credit, the circuit band stays absolute; re-anchors are counted separately from rejections. Cumulative volume is compared only within one IST trading day.</t>
+        </is>
+      </c>
+      <c r="H60" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_ingest_cleaning.py::TestALevelThatPersistsIsReal (3 fixes + 5 controls), ::TestVolumeRestartsEverySession (incl. an IST-vs-UTC discriminating case). After the fix: 197/199, 97/99, 50/50. Mutations M14-M16 killed (M15 only after adding the alternating-print test).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-012</t>
+        </is>
+      </c>
+      <c r="B61" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C61" s="76" t="inlineStr">
+        <is>
+          <t>strategy/runtime.py + strategy/context.py - declared constraints</t>
+        </is>
+      </c>
+      <c r="D61" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E61" s="76" t="inlineStr">
+        <is>
+          <t>Four strategy declarations were parsed, validated and folded into the content hash, and read by nothing: Applicability.sectors, constraints.entry_window, min_bars_since_open, and max_entries_per_day - which defaults to 1 on EVERY strategy.</t>
+        </is>
+      </c>
+      <c r="F61" s="76" t="inlineStr">
+        <is>
+          <t>A strategy stopped out could re-enter the same symbol again and again in one day while its document said once; it traded outside its declared hours and sectors. The same 'configured limit binding nothing' defect E14-S10 fixed for the exposure caps.</t>
+        </is>
+      </c>
+      <c r="G61" s="76" t="inlineStr">
+        <is>
+          <t>StrategyEvaluator.applies_to enforces all four. EvalContext gained sector and entries_today; both 'unknown' values refuse (AUDIT-005's rule). The entry window is IST, start-inclusive, end-exclusive. Wiring (E15-S13) must supply entries_today from the order book.</t>
+        </is>
+      </c>
+      <c r="H61" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_strategy_runtime.py::TestDeclaredConstraintsBindTheRuntime (each binds, unknown refuses, boundary cases, a control that the strategy still fires). Mutations M27-M30 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-013</t>
+        </is>
+      </c>
+      <c r="B62" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C62" s="76" t="inlineStr">
+        <is>
+          <t>strategy/dsl.py - strategy documents as untrusted input</t>
+        </is>
+      </c>
+      <c r="D62" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E62" s="76" t="inlineStr">
+        <is>
+          <t>exit.stop only had to be 'an exit primitive', and r_multiple_target, trail_after_r and squareoff_deadline all are - so 'stop: r_multiple_target' compiled. 'int' params accepted floats (14.7 ran as 14 while the hash kept 14.7); NaN passed any unbounded param and raised InvalidOperation (not caught by compile_strategy) against a bound; 'str' params were unchecked; condition lists were capped only AFTER parsing; YAML anchors/aliases allowed (a YAML bomb); an exit primitive could be an entry condition.</t>
+        </is>
+      </c>
+      <c r="F62" s="76" t="inlineStr">
+        <is>
+          <t>Live orders were still protected (the sizer computes the executable stop from ATR) and the runtime refused an unevaluable stop at the first trigger - so a fail-closed at runtime, but the DSL's documented guarantee ('cannot express no stop loss') was false, and identical strategies could count as distinct trials, inflating the overfitting control's trial count.</t>
+        </is>
+      </c>
+      <c r="G62" s="76" t="inlineStr">
+        <is>
+          <t>PrimitiveSpec.exit_role; each exit slot requires its own role; entries may not use exit primitives; strict int, finite-only numbers, typed+bounded str, typed enum; per-group (12) and per-condition (16) caps at parse; entry_window parsed and validated; sectors/min_price bounded; YAML size cap 64 KiB and no anchors/aliases; compile_strategy also catches ArithmeticError. Runtime _int accepts an int only.</t>
+        </is>
+      </c>
+      <c r="H62" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_strategy_dsl.py::TestEveryExitSlotTakesItsOwnKindOfExit, ::TestParametersAreWhatTheyClaim, ::TestDeclaredConstraintsAreWellFormed, ::TestTheYamlLoaderIsBounded; tests/unit/test_strategy_runtime.py::TestAnIntegerParameterIsNeverTruncatedAtRuntime. Mutations M23-M26, M31, M32 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-014</t>
+        </is>
+      </c>
+      <c r="B63" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C63" s="76" t="inlineStr">
+        <is>
+          <t>broker/kite/trading.py + execution/gateway.py - rate limit after TX1</t>
+        </is>
+      </c>
+      <c r="D63" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E63" s="76" t="inlineStr">
+        <is>
+          <t>The Kite adapter takes an order token inside place_order - AFTER the gateway's SUBMITTING record - and its refusal was the limiter's own RuntimeError, outside the broker taxonomy. Kite's own 429 reached the gateway the same way.</t>
+        </is>
+      </c>
+      <c r="F63" s="76" t="inlineStr">
+        <is>
+          <t>The SIT-003 shape one layer down: a SUBMITTING row for an order that never left, which reconciliation hunts every cycle, and an exception type no caller handles.</t>
+        </is>
+      </c>
+      <c r="G63" s="76" t="inlineStr">
+        <is>
+          <t>The adapter translates RateLimitExceededError into RateLimitError on both the order and read paths. The gateway records a RateLimitError as REJECTED (so the stale signal can never be resubmitted) and raises its own RateLimitedError.</t>
+        </is>
+      </c>
+      <c r="H63" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_gateway.py::TestARateLimitAfterTheRecordIsRecordedAsRefused, ::TestTheAdapterSpeaksTheTaxonomy; integration tests updated to the taxonomy. Mutations M10, M11 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-015</t>
+        </is>
+      </c>
+      <c r="B64" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C64" s="76" t="inlineStr">
+        <is>
+          <t>broker/kite/market_data.py - instrument sync</t>
+        </is>
+      </c>
+      <c r="D64" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E64" s="76" t="inlineStr">
+        <is>
+          <t>The instrument sync stored tick_size 0.05 for any row missing a tick (or carrying 0) and lot_size 1 for any row missing one - the hardcoded fallback the trading adapter refuses by design, moved upstream where that refusal could not see it.</t>
+        </is>
+      </c>
+      <c r="F64" s="76" t="inlineStr">
+        <is>
+          <t>A stop snapped to a grid the exchange may reject is rejected, and a rejected stop is an emergency exit.</t>
+        </is>
+      </c>
+      <c r="G64" s="76" t="inlineStr">
+        <is>
+          <t>Both required via require_field; a row that cannot state its grid is skipped and logged, so a rising count says the dump's shape moved. A genuine 0.01 tick survives exactly.</t>
+        </is>
+      </c>
+      <c r="H64" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_broker_kite.py::...test_an_instrument_that_cannot_state_its_grid_is_skipped_not_defaulted. Mutation M13 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-016</t>
+        </is>
+      </c>
+      <c r="B65" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C65" s="76" t="inlineStr">
+        <is>
+          <t>ingest/kite_ws.py - feed staleness</t>
+        </is>
+      </c>
+      <c r="D65" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E65" s="76" t="inlineStr">
+        <is>
+          <t>A heartbeat set FeedStats.last_tick_at - the field documented as what the health gate reads.</t>
+        </is>
+      </c>
+      <c r="F65" s="76" t="inlineStr">
+        <is>
+          <t>A connection that stayed up while the subscribed ticks stopped flowing read as fresh every second.</t>
+        </is>
+      </c>
+      <c r="G65" s="76" t="inlineStr">
+        <is>
+          <t>Heartbeats set last_heartbeat_at; last_tick_at means data only.</t>
+        </is>
+      </c>
+      <c r="H65" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_ingest_feed.py::TestAHeartbeatIsNotData. Mutation M19 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-017</t>
+        </is>
+      </c>
+      <c r="B66" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C66" s="76" t="inlineStr">
+        <is>
+          <t>broker/kite/trading.py - null ids</t>
+        </is>
+      </c>
+      <c r="D66" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E66" s="76" t="inlineStr">
+        <is>
+          <t>place_order guarded with `if not str(result)`, and str(None) is 'None' (truthy). _to_order rendered a missing order_id or tradingsymbol as the string 'None' - which passes the symbol allowlist.</t>
+        </is>
+      </c>
+      <c r="F66" s="76" t="inlineStr">
+        <is>
+          <t>A null order id recorded as landed under broker order 'None'; an incomplete row adoptable by the recovery path.</t>
+        </is>
+      </c>
+      <c r="G66" s="76" t="inlineStr">
+        <is>
+          <t>A null or blank id is AmbiguousOrderError; order_id and tradingsymbol are required.</t>
+        </is>
+      </c>
+      <c r="H66" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_broker_kite.py::...test_a_null_order_id_is_ambiguous_not_broker_order_none, ::...test_an_order_row_without_its_identity_is_refused_not_named_none. Mutation M12 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-018</t>
+        </is>
+      </c>
+      <c r="B67" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C67" s="76" t="inlineStr">
+        <is>
+          <t>ingest/kite_protocol.py - frame splitting</t>
+        </is>
+      </c>
+      <c r="D67" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E67" s="76" t="inlineStr">
+        <is>
+          <t>split_frame refused a frame SHORTER than its declared packets but accepted one with trailing bytes, though its docstring promised to reject any whose lengths do not add up.</t>
+        </is>
+      </c>
+      <c r="F67" s="76" t="inlineStr">
+        <is>
+          <t>A misaligned read or a protocol change parsing as a good frame.</t>
+        </is>
+      </c>
+      <c r="G67" s="76" t="inlineStr">
+        <is>
+          <t>Bytes the packets do not account for raise ProtocolError.</t>
+        </is>
+      </c>
+      <c r="H67" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_ingest_protocol.py::...test_bytes_the_packets_do_not_account_for_are_refused (+ exact-frame control). Mutation M17 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-019</t>
+        </is>
+      </c>
+      <c r="B68" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C68" s="76" t="inlineStr">
+        <is>
+          <t>common/db/models.py + migrations - unbuilt indexes</t>
+        </is>
+      </c>
+      <c r="D68" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E68" s="76" t="inlineStr">
+        <is>
+          <t>ix_audit_reason, ix_trial_ts and ix_journal_date were declared from text() expressions alone, which attaches an Index to no table: not in the metadata, never created by create_all or any migration, invisible to Alembic's comparator. ix_audit_reason also filtered outcome = 'REJECT' while the engine writes 'rejected'.</t>
+        </is>
+      </c>
+      <c r="F68" s="76" t="inlineStr">
+        <is>
+          <t>Performance and observability only: the 'why isn't it trading?' query ran unindexed.</t>
+        </is>
+      </c>
+      <c r="G68" s="76" t="inlineStr">
+        <is>
+          <t>Bound to their mapped columns; migration c4e8a2d7f913 creates all three (non-unique; the decision_log hypertable accepts it); upgrade/downgrade/upgrade round-trip verified.</t>
+        </is>
+      </c>
+      <c r="H68" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_schema_matches_models.py::test_every_index_declared_in_the_models_is_in_the_metadata; test_datastore_scaffold round-trip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-020</t>
+        </is>
+      </c>
+      <c r="B69" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C69" s="76" t="inlineStr">
+        <is>
+          <t>execution/sizer.py - refusal message</t>
+        </is>
+      </c>
+      <c r="D69" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E69" s="76" t="inlineStr">
+        <is>
+          <t>When a short's R-multiple target landed at or below zero, the refusal said 'stop distance not less than the entry price'.</t>
+        </is>
+      </c>
+      <c r="F69" s="76" t="inlineStr">
+        <is>
+          <t>An operator sent to the wrong number.</t>
+        </is>
+      </c>
+      <c r="G69" s="76" t="inlineStr">
+        <is>
+          <t>The message names which bound failed.</t>
+        </is>
+      </c>
+      <c r="H69" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_sizer.py::...test_a_short_whose_target_lands_below_zero_says_so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-021</t>
+        </is>
+      </c>
+      <c r="B70" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C70" s="76" t="inlineStr">
+        <is>
+          <t>process - schema drift</t>
+        </is>
+      </c>
+      <c r="D70" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E70" s="76" t="inlineStr">
+        <is>
+          <t>Nothing compared the migrations with the models; uq_open_slot, uq_client_order and the CHECKs on orders/positions were assumed to exist because the models declare them.</t>
+        </is>
+      </c>
+      <c r="F70" s="76" t="inlineStr">
+        <is>
+          <t>None found - the migrated schema matches - but drift would have been invisible.</t>
+        </is>
+      </c>
+      <c r="G70" s="76" t="inlineStr">
+        <is>
+          <t>Alembic compare_metadata against a freshly migrated TimescaleDB, the enum-derived CHECKs asserted present by name, and a control that drops uq_open_slot inside a rolled-back transaction.</t>
+        </is>
+      </c>
+      <c r="H70" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_schema_matches_models.py (4 tests).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="76" t="inlineStr">
+        <is>
+          <t>DEP-004</t>
+        </is>
+      </c>
+      <c r="B71" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C71" s="76" t="inlineStr">
+        <is>
+          <t>Dependency supply chain - certifi</t>
+        </is>
+      </c>
+      <c r="D71" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E71" s="76" t="inlineStr">
+        <is>
+          <t>certifi 2026.7.22 still trusted the emSign ECC Root CA - G3, under which eight intermediates have compromised private keys (PYSEC-2026-4320 / GHSA-6q48-6c7w-9gw2).</t>
+        </is>
+      </c>
+      <c r="F71" s="76" t="inlineStr">
+        <is>
+          <t>certifi is the trust store for requests/httpx - every TLS connection to the broker. An on-path attacker with a compromised key could impersonate api.kite.trade.</t>
+        </is>
+      </c>
+      <c r="G71" s="76" t="inlineStr">
+        <is>
+          <t>constraints.txt certifi==2026.10.23 (&gt;= 2026.10.19, which restored only the unaffected emSign roots).</t>
+        </is>
+      </c>
+      <c r="H71" s="76" t="inlineStr">
+        <is>
+          <t>pip-audit clean on the bump; CI's audit step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="76" t="inlineStr">
+        <is>
+          <t>DEP-005</t>
+        </is>
+      </c>
+      <c r="B72" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C72" s="76" t="inlineStr">
+        <is>
+          <t>Dependency supply chain - filelock (dev tooling)</t>
+        </is>
+      </c>
+      <c r="D72" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E72" s="76" t="inlineStr">
+        <is>
+          <t>filelock 3.32.2: CVE-2026-112940, -112913, -112907 (local lock-file attacks in shared directories).</t>
+        </is>
+      </c>
+      <c r="F72" s="76" t="inlineStr">
+        <is>
+          <t>Reached only through CacheControl[filecache] under pip-audit; not in the runtime image.</t>
+        </is>
+      </c>
+      <c r="G72" s="76" t="inlineStr">
+        <is>
+          <t>constraints.txt filelock==4.2.4.</t>
+        </is>
+      </c>
+      <c r="H72" s="76" t="inlineStr">
+        <is>
+          <t>pip-audit clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="76" t="inlineStr">
+        <is>
+          <t>DEP-006</t>
+        </is>
+      </c>
+      <c r="B73" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C73" s="76" t="inlineStr">
+        <is>
+          <t>Build backend - setuptools</t>
+        </is>
+      </c>
+      <c r="D73" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E73" s="76" t="inlineStr">
+        <is>
+          <t>setuptools 83.0.0: GHSA-xmj3-9gf7-h52w (Windows path escape in the legacy wheel install path).</t>
+        </is>
+      </c>
+      <c r="F73" s="76" t="inlineStr">
+        <is>
+          <t>Build environment only; CI and the Dockerfile upgrade setuptools on every build.</t>
+        </is>
+      </c>
+      <c r="G73" s="76" t="inlineStr">
+        <is>
+          <t>Local venv upgraded to 84.2.1; the hygiene test's floor raised from 78.1.1 to 84.1.0.</t>
+        </is>
+      </c>
+      <c r="H73" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_dependency_hygiene.py::...test_the_locally_installed_build_backend_is_not_vulnerable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="76" t="inlineStr">
+        <is>
+          <t>DEP-007</t>
+        </is>
+      </c>
+      <c r="B74" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C74" s="76" t="inlineStr">
+        <is>
+          <t>Dependency supply chain - Twisted (via kiteconnect)</t>
+        </is>
+      </c>
+      <c r="D74" s="76" t="inlineStr">
+        <is>
+          <t>Accepted risk</t>
+        </is>
+      </c>
+      <c r="E74" s="76" t="inlineStr">
+        <is>
+          <t>Five more Twisted 26.4.0 advisories: CVE-2026-115774 (IMAP4 server, twisted.mail), -115775 (XMPP XML stream, twisted.words), -115776 (IRC server, twisted.words), -115778 (telnet, twisted.conch), -115877 (HTTP server header smuggling, twisted.web). Fixed only in 26.10.0rc1/rc2 on 27 Oct 2026.</t>
+        </is>
+      </c>
+      <c r="F74" s="76" t="inlineStr">
+        <is>
+          <t>None reachable: every one needs a Twisted SERVER of that protocol; this process imports none of twisted.mail, .words, .conch or .web. A pre-release is not pinned into a system that moves money when the code cannot run anyway.</t>
+        </is>
+      </c>
+      <c r="G74" s="76" t="inlineStr">
+        <is>
+          <t>Each ID ignored individually (never the package); ACCEPTED_ADVISORIES maps each to its subsystem and assessed version.</t>
+        </is>
+      </c>
+      <c r="H74" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_dependency_hygiene.py::TestTheAcceptedTwistedAdvisories - per-advisory subsystem probe, a control importing all five vulnerable modules, every audit site ignoring exactly the set, and a version pin that fails the build when Twisted moves (26.10.0 final will force removal).</t>
         </is>
       </c>
     </row>
@@ -30000,7 +30888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -30031,6 +30919,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="59">
       <c r="A4" s="82" t="inlineStr">
         <is>
@@ -30524,6 +31413,68 @@
       <c r="L11" s="76" t="inlineStr">
         <is>
           <t>None - fixed in the same session</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="76" t="inlineStr">
+        <is>
+          <t>SIT-008</t>
+        </is>
+      </c>
+      <c r="B12" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C12" s="76" t="inlineStr">
+        <is>
+          <t>E15-S12 (harness)</t>
+        </is>
+      </c>
+      <c r="D12" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="E12" s="76" t="inlineStr">
+        <is>
+          <t>tests/sit/test_e14_trading_session.py</t>
+        </is>
+      </c>
+      <c r="F12" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G12" s="76" t="inlineStr">
+        <is>
+          <t>Every gateway submission in the SIT suite paired a stored RiskDecision with a FRESHLY MINTED Recommendation - a different correlation id each time. 22 SIT scenarios failed with DecisionMismatchError the moment AUDIT-006 made the decision carry its identity.</t>
+        </is>
+      </c>
+      <c r="H12" s="76" t="inlineStr">
+        <is>
+          <t>Nothing could see it: a decision carried no identity, so any pairing 'worked'. The harness was correct about everything it asserted and still exercised the exact wiring defect AUDIT-006 closes.</t>
+        </is>
+      </c>
+      <c r="I12" s="76" t="inlineStr">
+        <is>
+          <t>Session.run kept the decision and threw away the recommendation it was evaluated with; submission sites re-minted one from the minute's timestamp.</t>
+        </is>
+      </c>
+      <c r="J12" s="76" t="inlineStr">
+        <is>
+          <t>Session.recommendations holds the recommendation each minute was evaluated with; all 11 submission sites use it.</t>
+        </is>
+      </c>
+      <c r="K12" s="76" t="inlineStr">
+        <is>
+          <t>The gateway's DecisionMismatchError itself, on every SIT submission (181 SIT passing).</t>
+        </is>
+      </c>
+      <c r="L12" s="76" t="inlineStr">
+        <is>
+          <t>None - fixed in the session.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -27762,7 +27762,7 @@
       </c>
       <c r="G149" s="76" t="inlineStr">
         <is>
-          <t>Full gate: 2,427 -&gt; 2,581 passed, 0 skipped, coverage 93% (flat); ruff, format, mypy, bandit clean; pip-audit clean with 6 assessed ignores. Mutation testing on the fixes: 33/33 mutations killed (32/33 first run; M32 survivor verified benign - anchors refused first - and closed with an alias-only test).</t>
+          <t>Full gate: 2,427 -&gt; 2,581 passed, 0 skipped, coverage 93% (flat); ruff, format, mypy, bandit clean; pip-audit clean with 6 assessed ignores. Mutation testing on the fixes: 33/33 mutations killed (32/33 first run; M32 survivor verified benign - anchors refused first - and closed with an alias-only test). DEV CI on 0418b2d then failed (lint scope, two advisories published that morning) - fixed and recorded as AUDIT-022, DEP-008, DEP-009.</t>
         </is>
       </c>
     </row>
@@ -27783,7 +27783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -30868,6 +30868,132 @@
       <c r="H74" s="76" t="inlineStr">
         <is>
           <t>tests/security/test_dependency_hygiene.py::TestTheAcceptedTwistedAdvisories - per-advisory subsystem probe, a control importing all five vulnerable modules, every audit site ignoring exactly the set, and a version pin that fails the build when Twisted moves (26.10.0 final will force removal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="76" t="inlineStr">
+        <is>
+          <t>DEP-008</t>
+        </is>
+      </c>
+      <c r="B75" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C75" s="76" t="inlineStr">
+        <is>
+          <t>Dependency supply chain - msgpack (via autobahn, CacheControl)</t>
+        </is>
+      </c>
+      <c r="D75" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E75" s="76" t="inlineStr">
+        <is>
+          <t>msgpack 1.2.1: CVE-2026-114613 - the C extension leaks a decoded map value when strict_map_key rejects a key; repeated malformed input grows memory without bound. Published between the local audit and the DEV CI run of 0418b2d on 27 Oct 2026.</t>
+        </is>
+      </c>
+      <c r="F75" s="76" t="inlineStr">
+        <is>
+          <t>Not reachable from the application (msgpack is never imported by it; autobahn's serializers and pip-audit's cache use it).</t>
+        </is>
+      </c>
+      <c r="G75" s="76" t="inlineStr">
+        <is>
+          <t>constraints.txt msgpack==1.2.4.</t>
+        </is>
+      </c>
+      <c r="H75" s="76" t="inlineStr">
+        <is>
+          <t>pip-audit clean in a reproduction of CI's environment (python:3.11-slim-bookworm, constraints + autobahn override).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="76" t="inlineStr">
+        <is>
+          <t>DEP-009</t>
+        </is>
+      </c>
+      <c r="B76" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C76" s="76" t="inlineStr">
+        <is>
+          <t>Dependency supply chain - Twisted DNS client (via kiteconnect)</t>
+        </is>
+      </c>
+      <c r="D76" s="76" t="inlineStr">
+        <is>
+          <t>Accepted risk</t>
+        </is>
+      </c>
+      <c r="E76" s="76" t="inlineStr">
+        <is>
+          <t>Twisted 26.4.0: CVE-2026-83813 - twisted.names.dns accepts a DNS response on the 16-bit transaction id alone (cache poisoning). Fixed only in 26.10.0rc1. Published within hours of the five DEP-007 advisories.</t>
+        </is>
+      </c>
+      <c r="F76" s="76" t="inlineStr">
+        <is>
+          <t>None reachable: the reactor resolves through the system resolver unless twisted.names is installed explicitly, nothing here installs it or runs the reactor, and twisted.names is never imported.</t>
+        </is>
+      </c>
+      <c r="G76" s="76" t="inlineStr">
+        <is>
+          <t>Ignored by ID (seventh entry in ACCEPTED_ADVISORIES, subsystem twisted.names); CI and make audit updated.</t>
+        </is>
+      </c>
+      <c r="H76" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_dependency_hygiene.py::TestTheAcceptedTwistedAdvisories - the subsystem probe and a control importing twisted.names.dns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-022</t>
+        </is>
+      </c>
+      <c r="B77" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C77" s="76" t="inlineStr">
+        <is>
+          <t>process - the local gate was not CI's gate</t>
+        </is>
+      </c>
+      <c r="D77" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E77" s="76" t="inlineStr">
+        <is>
+          <t>Two gaps let DEV CI fail on a commit whose local gate was green: the /sdlc skill's local lint was `ruff check src/ tests/ scripts/`, which skips migrations/ (CI runs `ruff check .`, and the new migration had an import-order error); and the local venv had drifted from constraints.txt on 17 packages, so local audits checked versions nothing ships.</t>
+        </is>
+      </c>
+      <c r="F77" s="76" t="inlineStr">
+        <is>
+          <t>A 'green' local gate that CI then fails - and an audit of the wrong dependency set, which is the worse half.</t>
+        </is>
+      </c>
+      <c r="G77" s="76" t="inlineStr">
+        <is>
+          <t>The skill now installs from constraints.txt plus the autobahn override and runs CI's exact `ruff check .` / `ruff format --check .`. CI-only audit findings are reproduced in python:3.11-slim-bookworm (job logs need admin rights).</t>
+        </is>
+      </c>
+      <c r="H77" s="76" t="inlineStr">
+        <is>
+          <t>Diagnosed by reproduction: the container audit found exactly the two advisories CI did. Local venv now matches constraints except autobahn (replaced by design) and uvloop (Linux-only).</t>
         </is>
       </c>
     </row>
@@ -30919,7 +31045,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="59">
       <c r="A4" s="82" t="inlineStr">
         <is>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -27762,7 +27762,7 @@
       </c>
       <c r="G149" s="76" t="inlineStr">
         <is>
-          <t>Full gate: 2,427 -&gt; 2,581 passed, 0 skipped, coverage 93% (flat); ruff, format, mypy, bandit clean; pip-audit clean with 6 assessed ignores. Mutation testing on the fixes: 33/33 mutations killed (32/33 first run; M32 survivor verified benign - anchors refused first - and closed with an alias-only test). DEV CI on 0418b2d then failed (lint scope, two advisories published that morning) - fixed and recorded as AUDIT-022, DEP-008, DEP-009.</t>
+          <t>Full gate: 2,427 -&gt; 2,581 passed, 0 skipped, coverage 93% (flat); ruff, format, mypy, bandit clean; pip-audit clean with 6 assessed ignores. Mutation testing on the fixes: 33/33 mutations killed (32/33 first run; M32 survivor verified benign - anchors refused first - and closed with an alias-only test). DEV CI on 0418b2d then failed (lint scope, two advisories published that morning) - fixed and recorded as AUDIT-022, DEP-008, DEP-009. PROMOTED AND RUN ON THE QA TREE, 27 Oct 2026: QA 6c04290 (DEV 6913103), CI green on DEV and QA. The whole suite run from a worktree of the QA branch (algotrader confirmed loaded from that tree): 2,581 passed, 0 failed - 2,567 in the first run plus 14 caplog tests that errored only because the run disabled pytest's logging plugin, re-run on the same tree with it enabled. 181 SIT scenarios among them. Documents/, scripts/tracker, .claude absent from QA.</t>
         </is>
       </c>
     </row>
@@ -27812,7 +27812,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -22227,7 +22227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J149"/>
+  <dimension ref="A1:J150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -27763,6 +27763,43 @@
       <c r="G149" s="76" t="inlineStr">
         <is>
           <t>Full gate: 2,427 -&gt; 2,581 passed, 0 skipped, coverage 93% (flat); ruff, format, mypy, bandit clean; pip-audit clean with 6 assessed ignores. Mutation testing on the fixes: 33/33 mutations killed (32/33 first run; M32 survivor verified benign - anchors refused first - and closed with an alias-only test). DEV CI on 0418b2d then failed (lint scope, two advisories published that morning) - fixed and recorded as AUDIT-022, DEP-008, DEP-009. PROMOTED AND RUN ON THE QA TREE, 27 Oct 2026: QA 6c04290 (DEV 6913103), CI green on DEV and QA. The whole suite run from a worktree of the QA branch (algotrader confirmed loaded from that tree): 2,581 passed, 0 failed - 2,567 in the first run plus 14 caplog tests that errored only because the run disabled pytest's logging plugin, re-run on the same tree with it enabled. 181 SIT scenarios among them. Documents/, scripts/tracker, .claude absent from QA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="76" t="inlineStr">
+        <is>
+          <t>QA-VER-02</t>
+        </is>
+      </c>
+      <c r="B150" s="76" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C150" s="76" t="inlineStr">
+        <is>
+          <t>Accuracy review of the /sdlc skill against the repository, CI and the tracker, 28 Oct 2026.</t>
+        </is>
+      </c>
+      <c r="D150" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E150" s="76" t="inlineStr">
+        <is>
+          <t>Every command, path and claim in .claude/skills/sdlc/SKILL.md checked against the repo. Inaccurate and corrected: (1) Rule 1 cited a PROD gate the promotion tool never runs (AUDIT-023); (2) `make audit`/`make test-safety`/`make doctor` - make is not installed on the development machine; direct commands given; (3) R2 'dependencies are Closed' - only E00/E01 are Closed and every E14/E15 story rightly started on QA-Success dependencies; R2 now QA-Success-or-Closed, with a status lifecycle table the skill never had; (4) promote.py strips Documents, scripts/tracker AND .claude, not Documents only; (5) the commit template hard-coded 'Claude Opus 5'; (6) the doctor gate exits 1 on any dev machine (no deployment secrets) so 'every gate green' could never pass - the expected vs blocking sections are now stated; (7) Phase 0's 'unpromoted work' query lists docs-only commits forever; the promote.py dry run is now the check; (8) the tracker artifact URL belongs to an earlier account and has been unreachable since 15 Oct 2026 - the refusal procedure is now written instead of a dead end; (9) 'tested in test_safety_invariants.py' - invariants 3 and 5 are tested in its neighbours. Missing and added: Docker and '0 skipped' as part of green (15 Oct: 332 skipped looked green), the constrained install, CI's exact lint scope, re-running the audit before push, reproducing CI-only failures in python:3.11-slim-bookworm (job logs need admin), the SIT worktree procedure, the caplog/-p no:logging pitfall, mutation-harness rules (byte-exact restore, nothing else running, wrong-reason survivors), the CI-only jobs (image build, gitleaks).</t>
+        </is>
+      </c>
+      <c r="F150" s="76" t="inlineStr">
+        <is>
+          <t>The verified parts: the String(28) example (exactly three check names exceed it), the E14-S01 dependency correction and the NSE holiday triangulation are as stated in the tracker and config; every referenced file exists; the SIT scenario list matches tests/sit. ENGINEERING_STANDARD.md had the same stale R2, audit command and make-based gate - corrected in step, since the skill defers to it on process.</t>
+        </is>
+      </c>
+      <c r="G150" s="76" t="inlineStr">
+        <is>
+          <t>Each corrected command was executed as written on 28 Oct 2026: the derived pip-audit line (7 ignored, 0 found), the SIT worktree procedure (181 passed on QA 6c04290, algotrader loaded from the worktree), promote.py refusing DEV-&gt;PROD, QA-&gt;PROD and DEV-&gt;main and passing the CI check on DEV's head, doctor (Configuration, Broker SDK, Market calendar, Strategies OK; Datastores FAIL as stated).</t>
         </is>
       </c>
     </row>
@@ -27783,7 +27820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -27812,6 +27849,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -30993,6 +31031,132 @@
       <c r="H77" s="76" t="inlineStr">
         <is>
           <t>Diagnosed by reproduction: the container audit found exactly the two advisories CI did. Local venv now matches constraints except autobahn (replaced by design) and uvloop (Linux-only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-023</t>
+        </is>
+      </c>
+      <c r="B78" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C78" s="76" t="inlineStr">
+        <is>
+          <t>scripts/promote.py - the PROD gate</t>
+        </is>
+      </c>
+      <c r="D78" s="76" t="inlineStr">
+        <is>
+          <t>Fixed (tool); branch protection is the owner's action</t>
+        </is>
+      </c>
+      <c r="E78" s="76" t="inlineStr">
+        <is>
+          <t>promote.py accepted any --from/--to: `--from DEV --to PROD` would have pushed DEV's whole tree (Documents, the lifecycle driver) straight to PROD, skipping QA. The /sdlc skill's first rule cited promote.yml's `exit 1` as the PROD gate - a workflow this script never runs - so the rule was held up by instruction text alone. Its docstring also named 'promoting a commit CI never saw' as a failure it prevents, and nothing in it consulted CI. GitHub branch protection is off on every branch (protected=false for PROD, QA, main, DEV, checked 28 Oct 2026).</t>
+        </is>
+      </c>
+      <c r="F78" s="76" t="inlineStr">
+        <is>
+          <t>A single mistyped argument would have put untested code and planning material on the branch that trades real capital, with nothing to stop it.</t>
+        </is>
+      </c>
+      <c r="G78" s="76" t="inlineStr">
+        <is>
+          <t>promote.py refuses every promotion but DEV-&gt;QA before any git command (two independent layers: an explicit PROD refusal and a DEV-&gt;QA allowlist), and refuses unless the CI workflow's latest run on the exact source commit completed successfully - an unreachable or rate-limited API refuses too. Branch protection on PROD is recommended to the owner: it is the only gate that also covers a hand-typed git push.</t>
+        </is>
+      </c>
+      <c r="H78" s="76" t="inlineStr">
+        <is>
+          <t>Code/tests/security/test_promotion_hygiene.py::TestTheScriptCannotPromoteToProd, ::TestOnlyACommitCiPassedIsPromoted. Mutation: 8/8 killed (6/8 first run; the two survivors were a test passing for the wrong reason - a fake git made the divergence check refuse first - fixed by a fixture where only the CI check can refuse).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-024</t>
+        </is>
+      </c>
+      <c r="B79" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C79" s="76" t="inlineStr">
+        <is>
+          <t>Code/Makefile - developer install and lint</t>
+        </is>
+      </c>
+      <c r="D79" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E79" s="76" t="inlineStr">
+        <is>
+          <t>`make install` installed `-e .[dev]` without `-c constraints.txt` and upgraded only pip - the root cause of the 17-package venv drift in AUDIT-022. `make lint` and `make fmt` covered `src tests` while CI lints `.`; `make check` was labelled 'everything CI runs' and was not. The hygiene tests checked CI and the Dockerfile install sites, never the Makefile.</t>
+        </is>
+      </c>
+      <c r="F79" s="76" t="inlineStr">
+        <is>
+          <t>Following the documented install produced an environment nothing ships; following the documented lint missed what CI catches.</t>
+        </is>
+      </c>
+      <c r="G79" s="76" t="inlineStr">
+        <is>
+          <t>make install = CI's three install steps; lint/fmt over `.`; check's label states what it covers. A hygiene test now holds the Makefile install to CI's.</t>
+        </is>
+      </c>
+      <c r="H79" s="76" t="inlineStr">
+        <is>
+          <t>Code/tests/security/test_dependency_hygiene.py::...test_make_install_builds_the_environment_ci_builds (verified to fail on the previous Makefile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-025</t>
+        </is>
+      </c>
+      <c r="B80" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C80" s="76" t="inlineStr">
+        <is>
+          <t>Code/scripts/doctor.py - interpreter advice</t>
+        </is>
+      </c>
+      <c r="D80" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E80" s="76" t="inlineStr">
+        <is>
+          <t>doctor.py warned on Python 3.11 with '3.12+ recommended', while CI, the runtime image and mypy all pin 3.11.</t>
+        </is>
+      </c>
+      <c r="F80" s="76" t="inlineStr">
+        <is>
+          <t>Advice that would move a developer onto an interpreter nothing ships, so their tests describe a different system.</t>
+        </is>
+      </c>
+      <c r="G80" s="76" t="inlineStr">
+        <is>
+          <t>OK on the shipped 3.11; a newer local interpreter warns that it tests what nothing ships.</t>
+        </is>
+      </c>
+      <c r="H80" s="76" t="inlineStr">
+        <is>
+          <t>Run on 28 Oct 2026: Environment section reports OK on 3.11.9.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -27799,7 +27799,7 @@
       </c>
       <c r="G150" s="76" t="inlineStr">
         <is>
-          <t>Each corrected command was executed as written on 28 Oct 2026: the derived pip-audit line (7 ignored, 0 found), the SIT worktree procedure (181 passed on QA 6c04290, algotrader loaded from the worktree), promote.py refusing DEV-&gt;PROD, QA-&gt;PROD and DEV-&gt;main and passing the CI check on DEV's head, doctor (Configuration, Broker SDK, Market calendar, Strategies OK; Datastores FAIL as stated).</t>
+          <t>Each corrected command was executed as written on 28 Oct 2026: the derived pip-audit line (7 ignored, 0 found), the SIT worktree procedure (181 passed on QA 6c04290, algotrader loaded from the worktree), promote.py refusing DEV-&gt;PROD, QA-&gt;PROD and DEV-&gt;main and passing the CI check on DEV's head, doctor (Configuration, Broker SDK, Market calendar, Strategies OK; Datastores FAIL as stated). PROMOTED AND RUN ON THE QA TREE, 28 Oct 2026: DEV 26e1d14 (CI Run 110 green) -&gt; QA c9aba2f (CI Run 111 green). The promotion went through the new promote.py: it first REFUSED while the GitHub API quota was exhausted by status polling (HTTP 403) - the fail-closed CI check working in practice - and promoted after the reset once it confirmed CI passed on 26e1d14. SIT + security on the QA tree via the skill's worktree procedure: 638 passed, 0 failed. Two process notes added to the skill from the run: watch CI on the public Actions page (no quota), and OneDrive marks worktree metadata read-only (remove from PowerShell).</t>
         </is>
       </c>
     </row>
@@ -27849,7 +27849,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4530,7 +4530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X205"/>
+  <dimension ref="A1:X206"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -4572,6 +4572,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -8034,7 +8035,8 @@
       <c r="W42" s="49" t="n"/>
       <c r="X42" s="75" t="inlineStr">
         <is>
-          <t>The deadline must be pinned at position OPEN and stored with the position, never recomputed at exit time from current classification. If NSE reclassifies a symbol during the day, a recomputed deadline could move LATER and put you past the broker's square-off. E15-S06 computes at open — make sure this story feeds that path, not the exit path.</t>
+          <t>The deadline must be pinned at position OPEN and stored with the position, never recomputed at exit time from current classification. If NSE reclassifies a symbol during the day, a recomputed deadline could move LATER and put you past the broker's square-off. E15-S06 computes at open — make sure this story feeds that path, not the exit path.
+FROM E15-S13 (28 Oct 2026): execution reads instrument_daily_status for the day (DailyStatusRepository.for_symbol): is_cas_stock sets each position's square-off deadline, and T2T/ASM/GSM/FNO_BAN each block (session_context.restrictions_from). A symbol with no row for the day is refused (eligibility unknown). NOTE the column defaults: is_cas_stock is NOT NULL server_default false, so a row written without the flag reads NON-CAS and gets the LATER deadline - this story must always write it explicitly.</t>
         </is>
       </c>
     </row>
@@ -14069,6 +14071,11 @@
       </c>
       <c r="V115" s="48" t="n"/>
       <c r="W115" s="49" t="n"/>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>FROM E15-S13 (28 Oct 2026): the consumer exists. Publish each Recommendation to stream:signals as an Envelope whose correlation_id EQUALS the payload's and whose payload is `rec.model_dump(mode="json")`; a mismatch, or any extra field, is dead-lettered. emitted_at is the moment of emission: execution refuses a signal older than execution.max_signal_age_seconds (default 60, hard cap 300). A VETO need not be filtered here - execution refuses it - but should not be sent.</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="30" customHeight="1" s="59">
       <c r="A116" s="38" t="inlineStr">
@@ -16148,7 +16155,8 @@
       <c r="W136" s="49" t="n"/>
       <c r="X136" s="75" t="inlineStr">
         <is>
-          <t>'Switching paper-&gt;live changes exactly one dependency injection' is a strong claim and deserves a STRUCTURAL test, the way the ReadOnlyGuard test works. Otherwise one stray `if mode == PAPER` in the risk path makes every paper result unrepresentative of live.</t>
+          <t>'Switching paper-&gt;live changes exactly one dependency injection' is a strong claim and deserves a STRUCTURAL test, the way the ReadOnlyGuard test works. Otherwise one stray `if mode == PAPER` in the risk path makes every paper result unrepresentative of live.
+FROM E15-S13 (28 Oct 2026): the execution service sends in PAPER and LIVE modes to WHATEVER placer it is given - it cannot tell a paper placer from Kite. This story's placer is what makes PAPER safe: the entrypoint must hand the gateway the paper placer in PAPER mode, and nothing else may. ALERT_ONLY and APPROVAL are refused by the service itself (AUDIT-027).</t>
         </is>
       </c>
     </row>
@@ -18774,6 +18782,11 @@
         </is>
       </c>
       <c r="W171" s="49" t="n"/>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>FROM E15-S13 (28 Oct 2026): the execution service asks SessionFacts.unhealthy_services(now=...) for the health roll-up; until this story provides it, NoProducerYet answers None and the engine rejects EVERY signal (HEALTH via RISK_ENGINE_FAULT). Implement it as a SessionFacts method returning a tuple of unhealthy service names - empty only when every service was checked.</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="30" customHeight="1" s="59">
       <c r="A172" s="38" t="inlineStr">
@@ -20249,7 +20262,8 @@
       <c r="W191" s="49" t="n"/>
       <c r="X191" s="75" t="inlineStr">
         <is>
-          <t>'Verify core has no internet access, by attempt' is the right test. Note the tension with E02-S01's auth callback and E17-S01's dashboard access — both want inbound reachability. Resolve the network design ONCE here rather than three times in three stories, or the answers will disagree.</t>
+          <t>'Verify core has no internet access, by attempt' is the right test. Note the tension with E02-S01's auth callback and E17-S01's dashboard access — both want inbound reachability. Resolve the network design ONCE here rather than three times in three stories, or the answers will disagree.
+FROM E15-S13 (28 Oct 2026): docker-compose runs `python -m algotrader.execution`, and no service has a __main__ yet. The execution entrypoint composes ExecutionService (execution/service.py) with: the Kite trading adapter (or E15-S10's paper placer in PAPER mode - AUDIT-027), a session per operation for the repositories, RepositoryContextStore, HaltController, AuditWriter.write as the audit sink, and RedisSignalSource; then `await service.run(source, stop)`. QA-VER-01 constraint 4 lands here too: reconciliation reads must not share the data token bucket with backfill.</t>
         </is>
       </c>
     </row>
@@ -21379,7 +21393,7 @@
       </c>
       <c r="E205" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F205" s="41" t="inlineStr">
@@ -21442,7 +21456,17 @@
       </c>
       <c r="V205" s="48" t="inlineStr">
         <is>
-          <t>RAISED 30 Sep 2026 by E15-S12. S04, S05, S09 and S12 each delivered a mechanism and deliberately left its caller; this story is the caller. Until it exists nothing registers an EntryPlan when an entry is sent, so in production every fill is still exited as unprotected.</t>
+          <t>RAISED 30 Sep 2026 by E15-S12. S04, S05, S09 and S12 each delivered a mechanism and deliberately left its caller; this story is the caller. Until it exists nothing registers an EntryPlan when an entry is sent, so in production every fill is still exited as unprotected.
+BUSINESS ANALYSIS, 28 Oct 2026 (/sdlc).
+DoR: R1 ok (P0, 5d, Safety-critical). R2 ok - E15-S12, E15-S09, E14-S07 all QA-Success. Task 5's E04-S05 (New) is a RUNTIME dependency, not a build one: the service reads instrument_daily_status, and until E04-S05 populates it every symbol's eligibility is unknown and the engine refuses. R3 no open blocker. R4 LLA 5.7, 8.3, 9.1 and the S12 design record read this session.
+VALUE: this is the story that makes E15 a system - without it every fill is exited as unprotected. What breaks if wrong: a filled entry exited (plan late), two entries in one slot, a restart exiting the book, a VETO traded, alert-only placing orders. Test depth set accordingly (mutation required).
+OUT OF SCOPE, recorded: (1) the process entrypoint - docker-compose runs `python -m algotrader.execution` and no service has a __main__ yet; credentials, the Kite session and the paper placer for PAPER mode belong there. (2) Producers for three risk inputs: service health (E20-S05), live ATR, per-share margin (adapter has no order_margins) - NoProducerYet answers them unknown, so production rejects every signal until they exist. (3) Correlations - answered empty, so a second position is refused. (4) EvalContext.entries_today/sector (QA-VER-01 constraint 2) belong to the strategy-side signal service, which consumes nothing from here. (5) Constraint 4 (reconciliation reads sharing the data bucket with backfill) is a composition decision for the entrypoint.
+AC REWRITTEN AS FALSIFIABLE: AC1 = a Recommendation published on stream:signals, consumed by the running service against the real adapter/Postgres/Redis, is submitted, and after the broker fills it the next cycle holds a ProtectedPosition under the signal's correlation with an SL-M stop for the filled quantity. AC2 = with the kill switch armed in Redis (or any rejection), no order row exists and the broker received nothing. AC3 = start() restores before the first cycle; a held position is in the book after the first cycle and no exit is sent; signals are refused until a cycle has succeeded.
+DELIVERED 28 Oct 2026: execution/service.py (ExecutionService, RedisSignalSource), execution/session_context.py (RiskContextBuilder, PendingEntries, PendingAwareSlots, NoProducerYet, RepositoryContextStore), execution/risk/factory.py (build_risk_engine - the only RiskEngine constructor in src, asserted by AST), ReconciliationLoop(guard=...), reconciliation forgets an ENTRY's plan when it writes SUBMIT_FAILED, InstrumentRepository.profile, PositionRepository.closed_since, ExecutionConfig.max_signal_age_seconds (hard cap MAX_SIGNAL_AGE_SECONDS=300).
+DECISIONS: one asyncio lock for signals and cycles (9.1 made structural); sent-not-booked entries count as held, slotted and exposed; plans registered BEFORE the broker call; unknown send outcomes keep the plan, definitive ones release it; duplicates (row exists or ledger unreadable) are refused, never re-evaluated; VETO, stale (&gt;60s default) and future-dated (&gt;5s) signals, alert_only and approval modes are refused before the engine and audited under stage EXECUTION; all four surveillance flags block (recorded assumption); a missing daily row assumes the earlier CAS deadline and leaves eligibility unknown.
+GATES: Full gate 28 Oct 2026: 2,731 passed, 0 failed, 0 skipped, coverage 93% (flat; service 95%, session_context 93%, factory 100%, reconciliation 96%); ruff check/format and mypy clean over the whole tree; bandit 0; pip-audit clean (7 accepted IDs); security suite 460 passed; doctor: Configuration/Broker SDK/Market calendar/Strategies OK (Datastores FAIL and Secrets/SEBI/Network WARN are the dev machine).
+MUTATION: 34 named mutations, 34 killed after QA-E15-32 (one test passing for the wrong reason fixed; one redundant release removed; one anchor corrected); sources byte-identical.
+SIT: Pending - SIT-21 (tests/sit/test_e15_execution_session.py: a whole day, a restart mid-session, a kill switch mid-session) passed on DEV; to run on the QA tree.</t>
         </is>
       </c>
       <c r="W205" s="49" t="n"/>
@@ -21458,6 +21482,94 @@
 4. RECONCILIATION READS SHARE THE DATA TOKEN BUCKET WITH BACKFILL. A backfill draining the bucket makes the 30-second reads fail, and three consecutive failures arm BROKER_DISCONNECTED. Either keep backfill out of the session or give reconciliation its own budget.</t>
         </is>
       </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="38" t="inlineStr">
+        <is>
+          <t>E15-S14</t>
+        </is>
+      </c>
+      <c r="B206" s="39" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="C206" s="40" t="inlineStr">
+        <is>
+          <t>EXECUTION &amp; POSITIONS</t>
+        </is>
+      </c>
+      <c r="D206" s="40" t="inlineStr">
+        <is>
+          <t>Live risk inputs for the execution service: ATR and per-share margin</t>
+        </is>
+      </c>
+      <c r="E206" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F206" s="41" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G206" s="39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H206" s="50" t="inlineStr">
+        <is>
+          <t>Safety-critical</t>
+        </is>
+      </c>
+      <c r="I206" s="39" t="inlineStr">
+        <is>
+          <t>FEAT</t>
+        </is>
+      </c>
+      <c r="J206" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K206" s="40" t="inlineStr">
+        <is>
+          <t>E15-S13</t>
+        </is>
+      </c>
+      <c r="L206" s="40" t="n"/>
+      <c r="M206" s="44" t="n"/>
+      <c r="N206" s="45" t="n"/>
+      <c r="O206" s="44" t="n"/>
+      <c r="P206" s="44" t="n"/>
+      <c r="Q206" s="44" t="n"/>
+      <c r="R206" s="39" t="n"/>
+      <c r="S206" s="48" t="inlineStr">
+        <is>
+          <t>As a trader, I want the execution service to know each candidate's live ATR and the broker's per-share margin, so that the risk engine can size and approve a real signal rather than refuse every one.</t>
+        </is>
+      </c>
+      <c r="T206" s="48" t="inlineStr">
+        <is>
+          <t>1. A SessionFacts.atr producer: the ATR the strategy runtime computes, exported per symbol with its as-of time (stale -&gt; None).
+2. A SessionFacts.margin_per_share producer: Kite order_margins for the candidate (MIS, MARKET, 1 share), behind the order-rate limiter.
+3. A SessionFacts.correlations producer: correlations_against() over daily closes from BarRepository.
+4. Wire all three in place of NoProducerYet.</t>
+        </is>
+      </c>
+      <c r="U206" s="48" t="inlineStr">
+        <is>
+          <t>AC1 (RED) With the producers wired, an approvable signal is approved and sized from the live ATR and margin.
+AC2 (RED) A stale ATR, an unanswered margin call, or an uncomputable correlation each still rejects, naming the input.
+AC3 (RED) A held symbol whose correlation is unknown still refuses a second position.</t>
+        </is>
+      </c>
+      <c r="V206" s="48" t="inlineStr">
+        <is>
+          <t>RAISED 28 Oct 2026 by E15-S13. The service, the context builder and NoProducerYet exist; these three inputs are the reason production rejects every signal today (with E20-S05's health roll-up).</t>
+        </is>
+      </c>
+      <c r="W206" s="49" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:W197"/>
@@ -22227,7 +22339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J150"/>
+  <dimension ref="A1:J154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -22255,7 +22367,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="82" t="inlineStr">
         <is>
@@ -27800,6 +27911,154 @@
       <c r="G150" s="76" t="inlineStr">
         <is>
           <t>Each corrected command was executed as written on 28 Oct 2026: the derived pip-audit line (7 ignored, 0 found), the SIT worktree procedure (181 passed on QA 6c04290, algotrader loaded from the worktree), promote.py refusing DEV-&gt;PROD, QA-&gt;PROD and DEV-&gt;main and passing the CI check on DEV's head, doctor (Configuration, Broker SDK, Market calendar, Strategies OK; Datastores FAIL as stated). PROMOTED AND RUN ON THE QA TREE, 28 Oct 2026: DEV 26e1d14 (CI Run 110 green) -&gt; QA c9aba2f (CI Run 111 green). The promotion went through the new promote.py: it first REFUSED while the GitHub API quota was exhausted by status polling (HTTP 403) - the fail-closed CI check working in practice - and promoted after the reset once it confirmed CI passed on 26e1d14. SIT + security on the QA tree via the skill's worktree procedure: 638 passed, 0 failed. Two process notes added to the skill from the run: watch CI on the public Actions page (no quota), and OneDrive marks worktree metadata read-only (remove from PowerShell).</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-29</t>
+        </is>
+      </c>
+      <c r="B151" s="76" t="inlineStr">
+        <is>
+          <t>E15-S13</t>
+        </is>
+      </c>
+      <c r="C151" s="76" t="inlineStr">
+        <is>
+          <t>An entry that never reached the broker held its plan - and now its slot - for the rest of the day</t>
+        </is>
+      </c>
+      <c r="D151" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E151" s="76" t="inlineStr">
+        <is>
+          <t>Reconciliation forgets a plan when the broker LISTS the entry as ended; an entry written SUBMIT_FAILED is listed nowhere, so its plan was never dropped. Harmless memory before this story; with plans now counted as pending slots it would have run the book one slot short until restart.</t>
+        </is>
+      </c>
+      <c r="F151" s="76" t="inlineStr">
+        <is>
+          <t>Found in design (Phase 3) by tracing every exit from 'pending'. Reconciliation now calls manager.forget when it writes SUBMIT_FAILED; a late landing finds no plan and is exited (S12 AC3, unchanged).</t>
+        </is>
+      </c>
+      <c r="G151" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_reconciliation.py::TestS13AnEntryThatNeverLandedReleasesItsPlan (4, incl. grace-window control and late landing). Mutation 'rec: SUBMIT_FAILED keeps the plan' killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-30</t>
+        </is>
+      </c>
+      <c r="B152" s="76" t="inlineStr">
+        <is>
+          <t>E15-S13</t>
+        </is>
+      </c>
+      <c r="C152" s="76" t="inlineStr">
+        <is>
+          <t>The pending set could be observed stale between cycles</t>
+        </is>
+      </c>
+      <c r="D152" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E152" s="76" t="inlineStr">
+        <is>
+          <t>PendingEntries was pruned only when a context was built, so after reconciliation booked a fill the set still reported the entry in flight to any other reader.</t>
+        </is>
+      </c>
+      <c r="F152" s="76" t="inlineStr">
+        <is>
+          <t>Found by the AC1 integration test asserting the booked entry was no longer pending. Every read now prunes first.</t>
+        </is>
+      </c>
+      <c r="G152" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_session_context.py::TestPendingEntries::test_every_read_prunes_first; tests/integration/test_execution_service_wiring.py AC1. Mutation 'ctx: reads do not prune' killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-31</t>
+        </is>
+      </c>
+      <c r="B153" s="76" t="inlineStr">
+        <is>
+          <t>E15-S13</t>
+        </is>
+      </c>
+      <c r="C153" s="76" t="inlineStr">
+        <is>
+          <t>The AC3 control asserted a failure the reconciler does not have</t>
+        </is>
+      </c>
+      <c r="D153" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Corrected (test)</t>
+        </is>
+      </c>
+      <c r="E153" s="76" t="inlineStr">
+        <is>
+          <t>The control expected a cycle on an empty book to exit a held position. With a working stop, step 5 counts the stop as cover and exits nothing.</t>
+        </is>
+      </c>
+      <c r="F153" s="76" t="inlineStr">
+        <is>
+          <t>The real cost of skipping the restore is quieter: the position never enters the book, so no time exit walks it and no risk context counts it as held. The control now asserts that, and a second control (no stop) shows the exit S12 constraint 2 describes.</t>
+        </is>
+      </c>
+      <c r="G153" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_execution_service_wiring.py::TestAc3RestartRestoresBeforeTheFirstCycle (5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-32</t>
+        </is>
+      </c>
+      <c r="B154" s="76" t="inlineStr">
+        <is>
+          <t>E15-S13</t>
+        </is>
+      </c>
+      <c r="C154" s="76" t="inlineStr">
+        <is>
+          <t>Mutation testing: a test passing for the wrong reason, and a release no test could observe</t>
+        </is>
+      </c>
+      <c r="D154" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E154" s="76" t="inlineStr">
+        <is>
+          <t>34 named mutations over service.py, session_context.py and the reconciliation changes. Two survived the first run. 'reads do not prune' (prune removed from slots()) survived because test_every_read_prunes_first asserted all four reads in sequence on one object - the first read pruned for the rest. 'release keeps the pending slot' survived because PendingEntries prunes from the plans on every read, so the explicit discard was unobservable. A third mutation never ran: ruff format had rewrapped its anchor line.</t>
+        </is>
+      </c>
+      <c r="F154" s="76" t="inlineStr">
+        <is>
+          <t>The prune test is now one read per case on a fresh set. PendingEntries.discard was removed - the plan is the one record of 'still in flight'. The anchor was corrected and the mutation run.</t>
+        </is>
+      </c>
+      <c r="G154" s="76" t="inlineStr">
+        <is>
+          <t>34/34 killed; sources byte-identical after every run. tests/unit/test_session_context.py::TestPendingEntries::test_every_read_prunes_first[len|contains|entries|slots].</t>
         </is>
       </c>
     </row>
@@ -27820,7 +28079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -31156,6 +31415,174 @@
       <c r="H80" s="76" t="inlineStr">
         <is>
           <t>Run on 28 Oct 2026: Environment section reports OK on 3.11.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-026</t>
+        </is>
+      </c>
+      <c r="B81" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C81" s="76" t="inlineStr">
+        <is>
+          <t>execution - AI veto</t>
+        </is>
+      </c>
+      <c r="D81" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E81" s="76" t="inlineStr">
+        <is>
+          <t>None of the fourteen risk checks reads Recommendation.ai_verdict. A VETO that reached stream:signals would have been evaluated on its numbers and traded.</t>
+        </is>
+      </c>
+      <c r="F81" s="76" t="inlineStr">
+        <is>
+          <t>The AI layer's explicit 'do not trade' would have bound nothing at the one place orders are made.</t>
+        </is>
+      </c>
+      <c r="G81" s="76" t="inlineStr">
+        <is>
+          <t>ExecutionService refuses a VETO before the engine (RejectReason.AI_VETO, audited). WEAK stays the engine's to judge.</t>
+        </is>
+      </c>
+      <c r="H81" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_execution_service.py::TestRefusedBeforeTheEngine::test_a_veto_is_refused (+ WEAK control). Mutation killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-027</t>
+        </is>
+      </c>
+      <c r="B82" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C82" s="76" t="inlineStr">
+        <is>
+          <t>execution - system mode</t>
+        </is>
+      </c>
+      <c r="D82" s="76" t="inlineStr">
+        <is>
+          <t>Fixed (service); PAPER placer is the entrypoint's</t>
+        </is>
+      </c>
+      <c r="E82" s="76" t="inlineStr">
+        <is>
+          <t>system.mode was enforced nowhere. ARCHITECTURE_RESEARCH / INDIA_FEATURES define alert-only as 'no orders' and approval as 'system proposes, you confirm'; an execution service wired in either mode would have sent orders.</t>
+        </is>
+      </c>
+      <c r="F82" s="76" t="inlineStr">
+        <is>
+          <t>The staged rollout's first two safety stages would have been fiction.</t>
+        </is>
+      </c>
+      <c r="G82" s="76" t="inlineStr">
+        <is>
+          <t>Only PAPER and LIVE send; ALERT_ONLY and APPROVAL refuse every signal (no reason code - a working mode is not a fault). PAPER still sends to whatever placer it is given: the entrypoint must hand it a paper placer - recorded as a hard constraint on that story.</t>
+        </is>
+      </c>
+      <c r="H82" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_execution_service.py::...test_a_mode_that_places_no_orders_places_none (both modes), ::test_live_mode_sends_too. Mutation killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-028</t>
+        </is>
+      </c>
+      <c r="B83" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C83" s="76" t="inlineStr">
+        <is>
+          <t>execution - decision_log as a sink</t>
+        </is>
+      </c>
+      <c r="D83" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E83" s="76" t="inlineStr">
+        <is>
+          <t>The first draft wrote broker and database exception TEXT into SignalResult.detail and ContextUnavailableError, both of which reach decision_log - the sink REC-002/REC-003 established the logging layer's redaction never sees.</t>
+        </is>
+      </c>
+      <c r="F83" s="76" t="inlineStr">
+        <is>
+          <t>A broker error echoing a request parameter, or a driver error naming a DSN, would have been persisted unredacted in the audit chain.</t>
+        </is>
+      </c>
+      <c r="G83" s="76" t="inlineStr">
+        <is>
+          <t>The audit detail carries the exception TYPE only; the text goes to the redacted log.</t>
+        </is>
+      </c>
+      <c r="H83" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_execution_service.py::TestNothingSecretReachesTheAuditTable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-029</t>
+        </is>
+      </c>
+      <c r="B84" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C84" s="76" t="inlineStr">
+        <is>
+          <t>execution - stream input (STRIDE)</t>
+        </is>
+      </c>
+      <c r="D84" s="76" t="inlineStr">
+        <is>
+          <t>Assessed</t>
+        </is>
+      </c>
+      <c r="E84" s="76" t="inlineStr">
+        <is>
+          <t>stream:signals is writable by anything on the core network. S: the engine is the gate for every message; a payload that is not a Recommendation (extra fields forbidden - a 'quantity' is refused) or whose envelope and payload disagree on correlation is dead-lettered. T: redelivery is harmless - an existing order row refuses re-evaluation. R: every outcome is audited (engine rows + stage EXECUTION). I: details are one_safe_line and exception types only. D: the stream is maxlen-bounded and handling is serial. E: no payload value selects a code path.</t>
+        </is>
+      </c>
+      <c r="F84" s="76" t="inlineStr">
+        <is>
+          <t>Residual: a process with Redis write access can submit well-formed signals; Redis is reachable only on the internal network (LLA 10.3).</t>
+        </is>
+      </c>
+      <c r="G84" s="76" t="inlineStr">
+        <is>
+          <t>None needed beyond the above.</t>
+        </is>
+      </c>
+      <c r="H84" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_execution_service.py::TestTheStream; tests/integration/test_execution_service_wiring.py::...test_a_malformed_entry_is_dead_lettered_and_acknowledged.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -21393,7 +21393,7 @@
       </c>
       <c r="E205" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F205" s="41" t="inlineStr">
@@ -21464,9 +21464,9 @@
 AC REWRITTEN AS FALSIFIABLE: AC1 = a Recommendation published on stream:signals, consumed by the running service against the real adapter/Postgres/Redis, is submitted, and after the broker fills it the next cycle holds a ProtectedPosition under the signal's correlation with an SL-M stop for the filled quantity. AC2 = with the kill switch armed in Redis (or any rejection), no order row exists and the broker received nothing. AC3 = start() restores before the first cycle; a held position is in the book after the first cycle and no exit is sent; signals are refused until a cycle has succeeded.
 DELIVERED 28 Oct 2026: execution/service.py (ExecutionService, RedisSignalSource), execution/session_context.py (RiskContextBuilder, PendingEntries, PendingAwareSlots, NoProducerYet, RepositoryContextStore), execution/risk/factory.py (build_risk_engine - the only RiskEngine constructor in src, asserted by AST), ReconciliationLoop(guard=...), reconciliation forgets an ENTRY's plan when it writes SUBMIT_FAILED, InstrumentRepository.profile, PositionRepository.closed_since, ExecutionConfig.max_signal_age_seconds (hard cap MAX_SIGNAL_AGE_SECONDS=300).
 DECISIONS: one asyncio lock for signals and cycles (9.1 made structural); sent-not-booked entries count as held, slotted and exposed; plans registered BEFORE the broker call; unknown send outcomes keep the plan, definitive ones release it; duplicates (row exists or ledger unreadable) are refused, never re-evaluated; VETO, stale (&gt;60s default) and future-dated (&gt;5s) signals, alert_only and approval modes are refused before the engine and audited under stage EXECUTION; all four surveillance flags block (recorded assumption); a missing daily row assumes the earlier CAS deadline and leaves eligibility unknown.
-GATES: Full gate 28 Oct 2026: 2,731 passed, 0 failed, 0 skipped, coverage 93% (flat; service 95%, session_context 93%, factory 100%, reconciliation 96%); ruff check/format and mypy clean over the whole tree; bandit 0; pip-audit clean (7 accepted IDs); security suite 460 passed; doctor: Configuration/Broker SDK/Market calendar/Strategies OK (Datastores FAIL and Secrets/SEBI/Network WARN are the dev machine).
+GATES: Full gate 28 Oct 2026: 2,731 passed, 0 failed, 0 skipped, coverage 93% (flat; service 95%, session_context 93%, factory 100%, reconciliation 96%); ruff check/format and mypy clean over the whole tree; bandit 0; pip-audit clean (7 accepted IDs), re-run before push; security suite 460 passed; gitleaks clean on the pushed range; doctor: Configuration/Broker SDK/Market calendar/Strategies OK (Datastores FAIL and Secrets/SEBI/Network WARN are the dev machine). CI: DEV Run 114 FAILED (gitleaks, QA-E15-33) -&gt; fixed in 83cd00b -&gt; DEV Run 115 green; promoted DEV 83cd00b -&gt; QA 12c42cf via promote.py (CI check passed, no divergence, Documents/scripts/tracker/.claude stripped and verified absent); QA Run 116 green.
 MUTATION: 34 named mutations, 34 killed after QA-E15-32 (one test passing for the wrong reason fixed; one redundant release removed; one anchor corrected); sources byte-identical.
-SIT: Pending - SIT-21 (tests/sit/test_e15_execution_session.py: a whole day, a restart mid-session, a kill switch mid-session) passed on DEV; to run on the QA tree.</t>
+SIT: SIT on the QA tree (worktree at origin/QA 12c42cf, algotrader imported from the worktree), whole suite because the change spans components: 2,731 passed, 0 failed, 0 skipped. SIT-21 (tests/sit/test_e15_execution_session.py) walks a whole day through the real stack - pre-open, both no-trade windows, a duplicate delivery, a missing daily row, a VETO, a stale signal, a held symbol - and asserts every signal ends exactly one audited way, every entry is protected by one stop, nothing is exited, no halt; plus a restart mid-session (book kept, nothing placed, next signal gets slot 2) and a kill switch mid-session (new entries refused, protection untouched). No SIT defects.</t>
         </is>
       </c>
       <c r="W205" s="49" t="n"/>
@@ -22339,7 +22339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J154"/>
+  <dimension ref="A1:J155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -22367,6 +22367,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="82" t="inlineStr">
         <is>
@@ -28059,6 +28060,43 @@
       <c r="G154" s="76" t="inlineStr">
         <is>
           <t>34/34 killed; sources byte-identical after every run. tests/unit/test_session_context.py::TestPendingEntries::test_every_read_prunes_first[len|contains|entries|slots].</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-33</t>
+        </is>
+      </c>
+      <c r="B155" s="76" t="inlineStr">
+        <is>
+          <t>E15-S13</t>
+        </is>
+      </c>
+      <c r="C155" s="76" t="inlineStr">
+        <is>
+          <t>CI's secret scan failed a commit every local gate had passed</t>
+        </is>
+      </c>
+      <c r="D155" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E155" s="76" t="inlineStr">
+        <is>
+          <t>DEV CI Run 114 (b14532c) failed its Security job: gitleaks generic-api-key, twice, on a test fixture written as one literal ('api_key=... access_token=...') in TestNothingSecretReachesTheAuditTable. Fake values, nothing to rotate. The local Phase 7 gate runs bandit, pip-audit and the security suite - not gitleaks - so it could not see it: AUDIT-022's 'the local gate is not CI's gate', one job over.</t>
+        </is>
+      </c>
+      <c r="F155" s="76" t="inlineStr">
+        <is>
+          <t>Reproduced locally with the gitleaks container (2 findings, same rule and line). Fixtures assembled at runtime with a comment, the convention test_log_redaction.py already uses (83cd00b); the unpushed range then scanned clean, and CI Run 115 passed - which also confirmed the action judges each push on its own, so b14532c stays in history without a force-push. The /sdlc skill's Phase 7 now runs gitleaks on the unpushed range.</t>
+        </is>
+      </c>
+      <c r="G155" s="76" t="inlineStr">
+        <is>
+          <t>CI Run 115 (DEV 83cd00b) green; local gitleaks over every file this story added: no leaks found.</t>
         </is>
       </c>
     </row>
@@ -28108,6 +28146,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4568,7 +4568,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: BACKLOG.md · 189 stories across 24 epics · Set Status from the dropdown in column E. Yellow-tinted columns (M–Q, W) are yours to fill in. Tasks/Acceptance are wrapped — widen a row or click a cell to read the full text.</t>
+          <t>Source: BACKLOG.md · 202 stories across 24 epics (189 from BACKLOG.md, 13 raised since) · Set Status from the dropdown in column E. Yellow-tinted columns (M–Q, W) are yours to fill in. Tasks/Acceptance are wrapped — widen a row or click a cell to read the full text.</t>
         </is>
       </c>
     </row>
@@ -7614,7 +7614,11 @@
       </c>
       <c r="T37" s="48" t="n"/>
       <c r="U37" s="48" t="n"/>
-      <c r="V37" s="48" t="n"/>
+      <c r="V37" s="48" t="inlineStr">
+        <is>
+          <t>TRACKER RECONCILED AGAINST THE CODE, 28 Oct 2026: Status unchanged (New). common/db/retention.py archives BARS (ohlcv) to Parquet (E01-S06); nothing archives ticks.</t>
+        </is>
+      </c>
       <c r="W37" s="49" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1" s="59">
@@ -8143,7 +8147,7 @@
       </c>
       <c r="E44" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F44" s="41" t="inlineStr">
@@ -8205,7 +8209,8 @@
       </c>
       <c r="V44" s="48" t="inlineStr">
         <is>
-          <t>DATED, 27 Oct 2026: config/nse_holidays.yaml covers 2026 only. MarketCalendar fails CLOSED on an uncovered year (HolidayDataError), so from 1 Jan 2027 the system refuses to trade until the 2027 list is added. NSE publishes it in December; add it, triangulated against two publications as the 2026 list was, before the last trading day of 2026.</t>
+          <t>DATED, 27 Oct 2026: config/nse_holidays.yaml covers 2026 only. MarketCalendar fails CLOSED on an uncovered year (HolidayDataError), so from 1 Jan 2027 the system refuses to trade until the 2027 list is added. NSE publishes it in December; add it, triangulated against two publications as the 2026 list was, before the last trading day of 2026.
+TRACKER RECONCILED AGAINST THE CODE, 28 Oct 2026: Was New; the work was done on 24 Aug 2026 and never recorded. config/nse_holidays.yaml transcribes NSE's 2026 list (21 dates), verified_against_nse_circular: true, covers_years: [2026]; the Muhurat Sunday session is modelled in common/calendar.py; doctor.py reports the list verified. DELIVERED IN PART - remaining: (1) the 2027 list before the last trading day of 2026 (the calendar fails closed on an uncovered year, see the dated note above); (2) the runbook reminder (E23-S06, unbuilt); (3) automated fetch was 'consider' and is not built.</t>
         </is>
       </c>
       <c r="W44" s="49" t="n"/>
@@ -9117,7 +9122,8 @@
       <c r="V54" s="48" t="inlineStr">
         <is>
           <t>EMA, SMA, RSI, MACD, ATR, Bollinger, VWAP, VolumeRatio - all matched to TA-Lib within 1e-4. MACD needed a real fix found by that comparison: TA-Lib seeds BOTH its EMAs at the same bar (the slow period's start), not each at its own. Composing two independent EMAs read -18.75 where TA-Lib read -20.11 on a 200-bar series - a 7% error on a line whose CROSSINGS are the signal. Bollinger uses population not sample stddev (2.6% apart at n=20). VWAP is session-anchored and ignores synthetic bars. VolumeRatio excludes the current bar so a 10x spike does not damp itself.
-NOT DONE: ADX. Listed in the story, deferred - it is the only one with no consumer yet.</t>
+NOT DONE: ADX. Listed in the story, deferred - it is the only one with no consumer yet.
+TRACKER RECONCILED AGAINST THE CODE, 28 Oct 2026: Status confirmed (Development Completed): still no ADX in indicators/ (engine.py, framework.py, levels.py).</t>
         </is>
       </c>
       <c r="W54" s="49" t="n"/>
@@ -12832,7 +12838,11 @@
         </is>
       </c>
       <c r="U100" s="48" t="n"/>
-      <c r="V100" s="48" t="n"/>
+      <c r="V100" s="48" t="inlineStr">
+        <is>
+          <t>TRACKER RECONCILED AGAINST THE CODE, 28 Oct 2026: Status unchanged (New). The strategy and strategy_trial tables exist (E01 schema) and strategy documents compile from config/strategies (scripts/validate_strategies.py), but there is no repository, no persistence of a StrategyDocument and no load-on-startup.</t>
+        </is>
+      </c>
       <c r="W100" s="49" t="n"/>
     </row>
     <row r="101" ht="30" customHeight="1" s="59">
@@ -18436,7 +18446,7 @@
       </c>
       <c r="E167" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F167" s="53" t="inlineStr">
@@ -18477,7 +18487,8 @@
       <c r="U167" s="48" t="n"/>
       <c r="V167" s="48" t="inlineStr">
         <is>
-          <t>Latency histograms per stage · data quality counters · AI metrics including cache hit ratio · trading counters · risk gauges · health.</t>
+          <t>Latency histograms per stage · data quality counters · AI metrics including cache hit ratio · trading counters · risk gauges · health.
+TRACKER RECONCILED AGAINST THE CODE, 28 Oct 2026: Was New. common/metrics.py registers 13 Prometheus metrics: signals_approved/rejected_total, risk_check_errors_total, risk_evaluation_seconds, positions_opened_total, partial_fills_total, naked_positions_total, unprotectable_fills_total, stop_attach_failures_total, unknown_positions_total, reconciliation_cycles/drift/read_failures_total. DELIVERED IN PART - remaining: per-stage latency histograms (only the risk evaluation has one), data-quality counters, AI metrics incl. cache hit ratio, health.</t>
         </is>
       </c>
       <c r="W167" s="49" t="n"/>
@@ -18852,7 +18863,8 @@
       <c r="U172" s="48" t="n"/>
       <c r="V172" s="48" t="inlineStr">
         <is>
-          <t>Correlation ID binding across all services.</t>
+          <t>Correlation ID binding across all services.
+TRACKER RECONCILED AGAINST THE CODE, 28 Oct 2026: Status unchanged (New). common/logging.py provides bind_correlation() (E00-S05), but nothing in src calls it: no service binds a correlation id yet.</t>
         </is>
       </c>
       <c r="W172" s="49" t="n"/>
@@ -18957,7 +18969,7 @@
       </c>
       <c r="E174" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F174" s="41" t="inlineStr">
@@ -18998,7 +19010,8 @@
       <c r="U174" s="48" t="n"/>
       <c r="V174" s="48" t="inlineStr">
         <is>
-          <t>Compare actual egress IP against config; refuse to start on mismatch in live mode.</t>
+          <t>Compare actual egress IP against config; refuse to start on mismatch in live mode.
+TRACKER RECONCILED AGAINST THE CODE, 28 Oct 2026: Was New. AppConfig refuses to load in LIVE mode without system.static_ip; scripts/doctor.py:check_egress_ip compares the actual egress IP with EXPECTED_EGRESS_IP (warns when unset). DELIVERED IN PART - remaining: 'refuse to START on mismatch' belongs to a service entrypoint, and none exists yet (E23-S03).</t>
         </is>
       </c>
       <c r="W174" s="49" t="n"/>
@@ -19411,7 +19424,7 @@
       </c>
       <c r="E180" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F180" s="53" t="inlineStr">
@@ -19456,7 +19469,8 @@
       <c r="U180" s="48" t="n"/>
       <c r="V180" s="48" t="inlineStr">
         <is>
-          <t>Verify the hash chain end to end; detect any retroactive modification.</t>
+          <t>Verify the hash chain end to end; detect any retroactive modification.
+TRACKER RECONCILED AGAINST THE CODE, 28 Oct 2026: Was New. common/audit.py:verify_chain verifies the hash chain end to end and detects retroactive modification (built under E01-S05; tests/integration/test_audit_chain.py incl. hypothesis tampering cases). DELIVERED IN PART - remaining: the operator-facing utility (a command or script that runs it and reports) and a schedule; neither exists.</t>
         </is>
       </c>
       <c r="W180" s="49" t="n"/>
@@ -19535,7 +19549,11 @@
         </is>
       </c>
       <c r="U181" s="48" t="n"/>
-      <c r="V181" s="48" t="n"/>
+      <c r="V181" s="48" t="inlineStr">
+        <is>
+          <t>TRACKER RECONCILED AGAINST THE CODE, 28 Oct 2026: Status unchanged (New). Task 1 exists, built under E14-S07: tests/unit/test_sizer.py's hypothesis property that sizing never rounds up (risk never exceeds budget). Tasks 2-5 (slot count, approved-has-stop, square-off before the broker's deadline, monotonic clamps) have no property tests.</t>
+        </is>
+      </c>
       <c r="W181" s="49" t="n"/>
     </row>
     <row r="182" ht="30" customHeight="1" s="59">
@@ -19561,7 +19579,7 @@
       </c>
       <c r="E182" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F182" s="53" t="inlineStr">
@@ -19602,7 +19620,8 @@
       <c r="U182" s="48" t="n"/>
       <c r="V182" s="48" t="inlineStr">
         <is>
-          <t>Testcontainers for Redis and Postgres; every inter-service contract exercised.</t>
+          <t>Testcontainers for Redis and Postgres; every inter-service contract exercised.
+TRACKER RECONCILED AGAINST THE CODE, 28 Oct 2026: Was New. The Testcontainers harness for Postgres and Redis exists (tests/conftest.py) with 21 integration files (~9,800 lines) - persistence, audit chain, broker rate limit, gateway, order state, protective stop, positions, reconciliation, slots, tick-to-trigger, the execution service - and CI runs them on every push. DELIVERED IN PART - remaining: the contracts of services not built yet (signal engine, AI, pre-market, macro, notifier, API).</t>
         </is>
       </c>
       <c r="W182" s="49" t="n"/>
@@ -19675,7 +19694,8 @@
       <c r="U183" s="48" t="n"/>
       <c r="V183" s="48" t="inlineStr">
         <is>
-          <t>Replay a recorded session through the full pipeline; assert deterministic outputs; regression on every change.</t>
+          <t>Replay a recorded session through the full pipeline; assert deterministic outputs; regression on every change.
+TRACKER RECONCILED AGAINST THE CODE, 28 Oct 2026: Status unchanged (New). tests/replay contains only __init__.py.</t>
         </is>
       </c>
       <c r="W183" s="49" t="n"/>
@@ -19753,7 +19773,8 @@
       </c>
       <c r="V184" s="48" t="inlineStr">
         <is>
-          <t>All nine scenarios from LOW_LEVEL_ARCHITECTURE §12.3 — kill each service, Redis restart, WebSocket drop, AI outage, broker 500, clock jump, disk full, duplicate tick flood.</t>
+          <t>All nine scenarios from LOW_LEVEL_ARCHITECTURE §12.3 — kill each service, Redis restart, WebSocket drop, AI outage, broker 500, clock jump, disk full, duplicate tick flood.
+TRACKER RECONCILED AGAINST THE CODE, 28 Oct 2026: Status unchanged (New). tests/chaos contains only __init__.py; degraded-dependency scenarios live in tests/sit instead.</t>
         </is>
       </c>
       <c r="W184" s="49" t="n"/>
@@ -19964,7 +19985,8 @@
       <c r="U187" s="48" t="n"/>
       <c r="V187" s="48" t="inlineStr">
         <is>
-          <t>100% line coverage gate on `execution/risk_engine.py` and `execution/sizer.py`.</t>
+          <t>100% line coverage gate on `execution/risk_engine.py` and `execution/sizer.py`.
+TRACKER RECONCILED AGAINST THE CODE, 28 Oct 2026: Status unchanged (New) - no coverage gate exists anywhere (no fail_under in pyproject, Makefile or ci.yml). Today the modules this story means are covered: execution/risk/checks/* 100%, factory 100%, framework 99%, sizer 100% (full gate, 28 Oct 2026) - nothing keeps them there. CORRECTION to the scope: the story names execution/risk_engine.py, which does not exist - the engine is execution/risk/ (framework.py, checks/, factory.py). pyproject's [tool.coverage.paths] 'risk' entry names the same missing file and is not an enforcement mechanism ([paths] maps source locations when combining data files).</t>
         </is>
       </c>
       <c r="W187" s="49" t="n"/>
@@ -20359,7 +20381,7 @@
       </c>
       <c r="E193" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F193" s="53" t="inlineStr">
@@ -20400,7 +20422,8 @@
       <c r="U193" s="48" t="n"/>
       <c r="V193" s="48" t="inlineStr">
         <is>
-          <t>`make check` on every PR; gitleaks; pip-audit; safety-invariant tests as a required check on `QA` and `PROD`.</t>
+          <t>`make check` on every PR; gitleaks; pip-audit; safety-invariant tests as a required check on `QA` and `PROD`.
+TRACKER RECONCILED AGAINST THE CODE, 28 Oct 2026: Was New. .github/workflows/ci.yml runs on push and pull_request to DEV/QA/PROD/main: lint/format/types (make check's commands), tests incl. tests/security (the safety invariants), gitleaks, pip-audit with assessed ignores, a container image build, and a CI-gate job; scripts/promote.py refuses a DEV-&gt;QA promotion unless CI passed on the commit. DELIVERED IN PART - remaining: 'a required check on QA and PROD' needs GitHub branch protection, which is off on every branch (checked 28 Oct 2026) - the owner's action, and recommended.</t>
         </is>
       </c>
       <c r="W193" s="49" t="n"/>
@@ -22367,7 +22390,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="82" t="inlineStr">
         <is>
@@ -28146,7 +28168,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -15710,7 +15710,7 @@
       </c>
       <c r="E132" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F132" s="41" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="K132" s="40" t="inlineStr">
         <is>
-          <t>E15-S05, E04-S05</t>
+          <t>E15-S05</t>
         </is>
       </c>
       <c r="L132" s="40" t="n"/>
@@ -15770,7 +15770,20 @@
 • 🔴 No position survives its deadline in a full-session replay</t>
         </is>
       </c>
-      <c r="V132" s="48" t="n"/>
+      <c r="V132" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+BUSINESS ANALYSIS, 28 Oct 2026 (/sdlc, E15-S06).
+DoR: R1 ok (P0, 1.5d, Safety-critical). R2 CORRECTED: E04-S05 is a RUNTIME dependency, not a build one - the deadline is computed and stored at position open (constraint 1), from the CAS flag E15-S13 reads off instrument_daily_status, and the timer only acts on the stored value; E04-S05 populates that flag. Dependencies set to E15-S05. R3 no blocker. R4 LLA 5.8, the five inherited constraints, positions/reconciliation/protective_stop code read this session.
+VALUE: invariant 5's time exit. What breaks if wrong: a position force-closed by the broker; two exits for one position (account short); a held position never exited.
+OUT OF SCOPE, recorded: exit precedence beyond 'a triggered stop is the exit' (E15-S07); reducing quantity on partial exits (E15-S08 - a stop that part-fills then cancels is exited for the remainder and HALTS as not held); alert transports (E19); the process entrypoint (E23-S03).
+DECISIONS: (1) Task 2's Redis sorted set NOT built - a second copy of the deadline, and a missed add is a position with no time exit; the sweep reads the book. LLA 5.8 rewritten. (2) Constraint 4: the timer SHARES the SQUAREOFF key - unused for every position it acts on, no migration of order_intent_enum, no second exit key. (3) Constraint 5: cancel the stop and send nothing until the broker shows it terminal (CANCEL PENDING maps to OPEN = live, so the reconciler cannot add an exit in the gap either). (4) Constraints 2-3: ExitingPosition gains reason; reconciliation closes with it (TIME / UNPROTECTED). (5) Build concern 1: one-second loop + backstop sweep after every cycle and reconnect + stall detection (squareoff_timer_stalls_total). (6) Build concern 2: the exit is MARKET with market_protection (asserted at the Kite payload). (7) Every exit min(book, broker): see AUDIT-030. (8) A halt never stops the timer.
+RESIDUALS, recorded: after a restart mid time-exit the close may read UNPROTECTED (the reason is in memory); if a stop's cancel stays pending past the in-sweep settle (~1s) and a cycle runs after it lands, the reconciler exits it (one exit, labelled UNPROTECTED); a position booked in the same cycle whose stop AND emergency exit both die could read held 0 from the cycle's positions snapshot and halt (fail closed).
+GATES: Full gate 28 Oct 2026, one pass: ruff check/format and mypy clean (STATIC EXIT CODE 0); 2,798 passed, 0 failed, 0 skipped (PYTEST EXIT CODE 0, written by the run itself); coverage 93% flat (squareoff 94%, service 96%, reconciliation 96%, positions 97%, trading models 98%); bandit exit 0; pip-audit exit 0 (7 accepted IDs), re-run before push; security suite 460 passed; doctor: only Datastores FAIL (dev machine). Two earlier runs were NOT green and are recorded: 14 failures reported through a pipe as exit 0 (QA-E15-37), and a mypy failure after the _is_the_exit refactor (fixed with TypeGuard).
+MUTATION: 30 named mutations over squareoff.py, the reconciler guard, positions.py, service.py and the Position validator: 30 killed, sources byte-identical (first run 26/29 + 2 never ran: QA-E15-38).
+SIT: Pending - SIT-21 (updated: every position now leaves at its deadline, closed TIME) and SIT-22 (a day with three positions and two deadlines, a restart after the deadline, a kill switch mid-session, yesterday's stale row) pass on DEV; to run on the QA tree.</t>
+        </is>
+      </c>
       <c r="W132" s="49" t="n"/>
       <c r="X132" s="75" t="inlineStr">
         <is>
@@ -15857,6 +15870,11 @@
         </is>
       </c>
       <c r="W133" s="49" t="n"/>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>FROM E15-S06 (28 Oct 2026): the timer already encodes two precedence rules - a halt never stops a time exit, and a stop that has triggered (any fill) IS the exit, so the timer does not race it. Exit precedence must keep both.</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="30" customHeight="1" s="59">
       <c r="A134" s="38" t="inlineStr">
@@ -15934,7 +15952,8 @@
         <is>
           <t>CONSTRAINT INHERITED FROM E15-S12 (30 Sep 2026).
 1. A PARTIAL stop or exit fill leaves the position HELD at its original quantity - confirm_exit does not reduce it. Reducing the book on a partial exit is this story's.
-2. Only FINISHED entries are booked, so a booked position cannot grow today. If this story ever books a working entry, the stop must be resized as it grows, or the later shares have no stop.</t>
+2. Only FINISHED entries are booked, so a booked position cannot grow today. If this story ever books a working entry, the stop must be resized as it grows, or the later shares have no stop.
+FROM E15-S06 (28 Oct 2026): a stop that part-fills and is then cancelled leaves the book at the full quantity; step 4 and the timer exit what the broker holds and HALT (POSITION_NOT_HELD), because the book cannot be reduced yet. This story's partial exits should reduce the book instead, so that case stops halting.</t>
         </is>
       </c>
     </row>
@@ -21237,11 +21256,7 @@
           <t>E14-S09, E15 (order gateway)</t>
         </is>
       </c>
-      <c r="L203" s="40" t="inlineStr">
-        <is>
-          <t>No order path exists to cancel or close through</t>
-        </is>
-      </c>
+      <c r="L203" s="40" t="n"/>
       <c r="M203" s="44" t="n"/>
       <c r="N203" s="45" t="n"/>
       <c r="O203" s="44" t="n"/>
@@ -21269,7 +21284,11 @@
         </is>
       </c>
       <c r="W203" s="49" t="n"/>
-      <c r="X203" s="75" t="n"/>
+      <c r="X203" s="75" t="inlineStr">
+        <is>
+          <t>CORRECTED 28 Oct 2026: 'Blocked by: No order path exists to cancel or close through' is no longer true - OrderGateway.cancel (E15-S12) and submit_exit exist, and the square-off timer (E15-S06) closes through exactly that path. The remaining dependency is the operator transport (E14-S12 / E19).</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="38" t="inlineStr">
@@ -22362,7 +22381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J155"/>
+  <dimension ref="A1:J160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -22390,6 +22409,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="82" t="inlineStr">
         <is>
@@ -28119,6 +28139,191 @@
       <c r="G155" s="76" t="inlineStr">
         <is>
           <t>CI Run 115 (DEV 83cd00b) green; local gitleaks over every file this story added: no leaks found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-34</t>
+        </is>
+      </c>
+      <c r="B156" s="76" t="inlineStr">
+        <is>
+          <t>E15-S06</t>
+        </is>
+      </c>
+      <c r="C156" s="76" t="inlineStr">
+        <is>
+          <t>Reconciliation's step-4 tests exited positions the broker did not hold</t>
+        </is>
+      </c>
+      <c r="D156" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Corrected (tests)</t>
+        </is>
+      </c>
+      <c r="E156" s="76" t="inlineStr">
+        <is>
+          <t>Ten step-4 tests booked positions with an empty broker - a state no session produces - so the exits they asserted were sized from the book alone. Under the AUDIT-030 guard nine failed (correctly: a not-held position now halts). The tenth, test_a_failed_exit_leaves_the_label_alone, kept passing for the WRONG reason: the not-held halt stopped it before the failing exit it exists to test.</t>
+        </is>
+      </c>
+      <c r="F156" s="76" t="inlineStr">
+        <is>
+          <t>A _held_all fixture gives each booked position the entry that bought it and the broker holding it produced; all ten run through it.</t>
+        </is>
+      </c>
+      <c r="G156" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_reconciliation.py - 131 passed; the guard's own tests in TestS06OnlyWhatTheBrokerHoldsIsExited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-35</t>
+        </is>
+      </c>
+      <c r="B157" s="76" t="inlineStr">
+        <is>
+          <t>E15-S06</t>
+        </is>
+      </c>
+      <c r="C157" s="76" t="inlineStr">
+        <is>
+          <t>A stop that filled just before the deadline would have halted the day</t>
+        </is>
+      </c>
+      <c r="D157" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed (design review)</t>
+        </is>
+      </c>
+      <c r="E157" s="76" t="inlineStr">
+        <is>
+          <t>The first draft checked the broker's holding before the stop. A stop filling moments before the deadline leaves the broker flat while the book still holds the position (reconciliation closes it within a cycle), so the not-held guard would have halted the session on an ordinary stop-out.</t>
+        </is>
+      </c>
+      <c r="F157" s="76" t="inlineStr">
+        <is>
+          <t>Found in self-review. The stop is read first; any fill means it is the exit.</t>
+        </is>
+      </c>
+      <c r="G157" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_squareoff.py::TestOnlyWhatTheBrokerHoldsIsExited::test_a_stop_that_filled_before_the_deadline_is_not_a_missing_position; mutation 'held checked before the stop' killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-36</t>
+        </is>
+      </c>
+      <c r="B158" s="76" t="inlineStr">
+        <is>
+          <t>E15-S06</t>
+        </is>
+      </c>
+      <c r="C158" s="76" t="inlineStr">
+        <is>
+          <t>A not-held position would have been re-asked every second</t>
+        </is>
+      </c>
+      <c r="D158" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed (design review)</t>
+        </is>
+      </c>
+      <c r="E158" s="76" t="inlineStr">
+        <is>
+          <t>The draft timer re-read the broker's positions and orderbook for a not-held position on every one-second sweep, and re-armed the halt (a CRITICAL line) each time - two broker calls a second, indefinitely, from the data budget reconciliation needs (QA-VER-01 constraint 4).</t>
+        </is>
+      </c>
+      <c r="F158" s="76" t="inlineStr">
+        <is>
+          <t>Once recorded not-held, the timer skips the position; the halt is armed once here and re-armed every cycle by reconciliation.</t>
+        </is>
+      </c>
+      <c r="G158" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_squareoff.py::...test_it_is_not_re_asked_every_second; mutation killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-37</t>
+        </is>
+      </c>
+      <c r="B159" s="76" t="inlineStr">
+        <is>
+          <t>E15-S06</t>
+        </is>
+      </c>
+      <c r="C159" s="76" t="inlineStr">
+        <is>
+          <t>14 failures were reported as exit code 0</t>
+        </is>
+      </c>
+      <c r="D159" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Process fixed</t>
+        </is>
+      </c>
+      <c r="E159" s="76" t="inlineStr">
+        <is>
+          <t>Adding the Position deadline validator failed 14 tests in test_trading_models.py, whose fixture built positions from the wall clock plus five hours. The full-suite run piped pytest into sort | uniq, so the reported exit code was uniq's - 0 - and the session called the fixture 'fixed' on the strength of a one-file re-run. The owner caught it.</t>
+        </is>
+      </c>
+      <c r="F159" s="76" t="inlineStr">
+        <is>
+          <t>The fixture is pinned to a trading morning. The /sdlc skill's Phase 8 and CLAUDE.md now require pytest's own exit code ($? straight after it, or PIPESTATUS) and a whole-suite run before 'fixed'.</t>
+        </is>
+      </c>
+      <c r="G159" s="76" t="inlineStr">
+        <is>
+          <t>Full gate: 2,797 passed, PYTEST EXIT CODE 0 written by the run itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-38</t>
+        </is>
+      </c>
+      <c r="B160" s="76" t="inlineStr">
+        <is>
+          <t>E15-S06</t>
+        </is>
+      </c>
+      <c r="C160" s="76" t="inlineStr">
+        <is>
+          <t>Mutation testing: a test passing for the wrong reason hid a gap in the stop rule</t>
+        </is>
+      </c>
+      <c r="D160" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E160" s="76" t="inlineStr">
+        <is>
+          <t>Mutation 'a stop filling on cancel is exited again' (delete the post-cancel filling check) SURVIVED. Why: a stop that FILLED also reads as live, so the next check sent nothing either, and the test asserted only 'no exit'. Verifying the survivor exposed the real gap: the rule 'any fill means the stop is the exit' was wrong for a stop that part-filled and was then CANCELLED - terminal, selling nothing more, with the remainder unprotected - which the timer left for reconciliation a cycle later. Separately, two model mutations never ran: trading.py's working copy is CRLF and the harness anchors were LF.</t>
+        </is>
+      </c>
+      <c r="F160" s="76" t="inlineStr">
+        <is>
+          <t>The stop is the exit only if it has filled AND is still live (_is_the_exit); a cancelled part-filled stop now has the held remainder exited at once (and halts, E15-S08). The test asserts the recorded REASON (STOP_FILLING, not CANCELLING). The harness matches each file's line endings.</t>
+        </is>
+      </c>
+      <c r="G160" s="76" t="inlineStr">
+        <is>
+          <t>30 named mutations, 30 killed; sources byte-identical. tests/unit/test_squareoff.py::...test_a_stop_cancelled_part_filled_is_not_the_exit.</t>
         </is>
       </c>
     </row>
@@ -28139,7 +28344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -28168,6 +28373,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -31643,6 +31849,132 @@
       <c r="H84" s="76" t="inlineStr">
         <is>
           <t>tests/unit/test_execution_service.py::TestTheStream; tests/integration/test_execution_service_wiring.py::...test_a_malformed_entry_is_dead_lettered_and_acknowledged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-030</t>
+        </is>
+      </c>
+      <c r="B85" s="76" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C85" s="76" t="inlineStr">
+        <is>
+          <t>execution/reconciliation.py step 4 (E15-S09 code) - exiting what the broker does not hold</t>
+        </is>
+      </c>
+      <c r="D85" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E85" s="76" t="inlineStr">
+        <is>
+          <t>Step 4 exited any booked position whose stop was not live, sized from the BOOK. A positions row left OPEN after the broker closed the position outside our view - its own MIS square-off at 15:20 while the service was down, a stop that filled unseen - is restored the next session as an UnverifiedPosition with no live stop, and step 4 sent a MARKET exit for it.</t>
+        </is>
+      </c>
+      <c r="F85" s="76" t="inlineStr">
+        <is>
+          <t>A MARKET SELL of shares the account did not hold: an unintended naked short, opened at the first cycle of the morning, with every control reporting a routine exit. The square-off timer adds the same exit path, so it had to be closed here.</t>
+        </is>
+      </c>
+      <c r="G85" s="76" t="inlineStr">
+        <is>
+          <t>held_by_broker() reads the broker's MIS/NSE net quantity in the position's direction; step 4 and the timer exit min(book, broker). A holding the broker lacks sends NOTHING and halts (new HaltReason.POSITION_NOT_HELD -&gt; kill switch; drift NOT_HELD; alerted once, re-armed every cycle); a partial one exits what is held and halts.</t>
+        </is>
+      </c>
+      <c r="H85" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_reconciliation.py::TestS06OnlyWhatTheBrokerHoldsIsExited (6, incl. delivery shares and the short sign); tests/integration/test_execution_service_wiring.py::TestS06TheTimeExitForReal::test_yesterdays_open_row_is_not_sold_this_morning; SIT-22 test_yesterdays_open_row_halts_the_morning_and_nothing_is_sold_all_day. Mutations killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-031</t>
+        </is>
+      </c>
+      <c r="B86" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C86" s="76" t="inlineStr">
+        <is>
+          <t>common/models/trading.py Position - the deadline the timer trusts</t>
+        </is>
+      </c>
+      <c r="D86" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E86" s="76" t="inlineStr">
+        <is>
+          <t>Position accepted any squareoff_deadline. The timer computes nothing and acts on the stored value (E15-S05 constraint 1), so a row edited by hand or corrupted to read next week would be held past every square-off with the timer reporting nothing due.</t>
+        </is>
+      </c>
+      <c r="F86" s="76" t="inlineStr">
+        <is>
+          <t>A position silently without its time exit - invariant 5 - until the broker force-closed it.</t>
+        </is>
+      </c>
+      <c r="G86" s="76" t="inlineStr">
+        <is>
+          <t>A model validator refuses a deadline off the position's opening IST day or after 15:30 (the rule RiskContext already applies). A bad row now fails the restore, and the service does not start.</t>
+        </is>
+      </c>
+      <c r="H86" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_trading_models.py::TestADeadlineIsIntraday (4, incl. an IST-vs-UTC discriminating case). Mutations 'any deadline accepted' and 'the UTC day' killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-032</t>
+        </is>
+      </c>
+      <c r="B87" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C87" s="76" t="inlineStr">
+        <is>
+          <t>execution/squareoff.py - STRIDE</t>
+        </is>
+      </c>
+      <c r="D87" s="76" t="inlineStr">
+        <is>
+          <t>Assessed / Fixed</t>
+        </is>
+      </c>
+      <c r="E87" s="76" t="inlineStr">
+        <is>
+          <t>S: acts only on the book and broker reads; the deadline is validated at construction (AUDIT-031). T: never two working exits (cancel, then send only once terminal). R: every action audited under stage SQUAREOFF, once per position and kind; closes by reconciliation. I: details carry quantities, times and exception TYPES only. D: broker reads only for due positions; not-held positions skipped (QA-E15-36); the cancel settle is bounded (5 reads); the once-only record set was unbounded over a long-lived process - now pruned to the book. E: no input selects a code path.</t>
+        </is>
+      </c>
+      <c r="F87" s="76" t="inlineStr">
+        <is>
+          <t>Residuals recorded on E15-S06.</t>
+        </is>
+      </c>
+      <c r="G87" s="76" t="inlineStr">
+        <is>
+          <t>Record set pruned to the book.</t>
+        </is>
+      </c>
+      <c r="H87" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_squareoff.py::TestItsMemoryIsBounded; mutation 'memory never pruned' killed.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -15710,7 +15710,7 @@
       </c>
       <c r="E132" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F132" s="41" t="inlineStr">
@@ -15779,9 +15779,9 @@
 OUT OF SCOPE, recorded: exit precedence beyond 'a triggered stop is the exit' (E15-S07); reducing quantity on partial exits (E15-S08 - a stop that part-fills then cancels is exited for the remainder and HALTS as not held); alert transports (E19); the process entrypoint (E23-S03).
 DECISIONS: (1) Task 2's Redis sorted set NOT built - a second copy of the deadline, and a missed add is a position with no time exit; the sweep reads the book. LLA 5.8 rewritten. (2) Constraint 4: the timer SHARES the SQUAREOFF key - unused for every position it acts on, no migration of order_intent_enum, no second exit key. (3) Constraint 5: cancel the stop and send nothing until the broker shows it terminal (CANCEL PENDING maps to OPEN = live, so the reconciler cannot add an exit in the gap either). (4) Constraints 2-3: ExitingPosition gains reason; reconciliation closes with it (TIME / UNPROTECTED). (5) Build concern 1: one-second loop + backstop sweep after every cycle and reconnect + stall detection (squareoff_timer_stalls_total). (6) Build concern 2: the exit is MARKET with market_protection (asserted at the Kite payload). (7) Every exit min(book, broker): see AUDIT-030. (8) A halt never stops the timer.
 RESIDUALS, recorded: after a restart mid time-exit the close may read UNPROTECTED (the reason is in memory); if a stop's cancel stays pending past the in-sweep settle (~1s) and a cycle runs after it lands, the reconciler exits it (one exit, labelled UNPROTECTED); a position booked in the same cycle whose stop AND emergency exit both die could read held 0 from the cycle's positions snapshot and halt (fail closed).
-GATES: Full gate 28 Oct 2026, one pass: ruff check/format and mypy clean (STATIC EXIT CODE 0); 2,798 passed, 0 failed, 0 skipped (PYTEST EXIT CODE 0, written by the run itself); coverage 93% flat (squareoff 94%, service 96%, reconciliation 96%, positions 97%, trading models 98%); bandit exit 0; pip-audit exit 0 (7 accepted IDs), re-run before push; security suite 460 passed; doctor: only Datastores FAIL (dev machine). Two earlier runs were NOT green and are recorded: 14 failures reported through a pipe as exit 0 (QA-E15-37), and a mypy failure after the _is_the_exit refactor (fixed with TypeGuard).
+GATES: Full gate 28 Oct 2026, one pass: ruff check/format and mypy clean (STATIC EXIT CODE 0); 2,798 passed, 0 failed, 0 skipped (PYTEST EXIT CODE 0, written by the run itself); coverage 93% flat; bandit exit 0; pip-audit exit 0 (7 accepted IDs), re-run before push; gitleaks clean on the pushed range; security suite 460 passed; doctor: only Datastores FAIL (dev machine). Two earlier runs were NOT green and are recorded: 14 failures reported through a pipe as exit 0 (QA-E15-37), and a mypy failure after the _is_the_exit refactor (fixed with TypeGuard). CI: DEV Run 119 green (4c1ab92); promoted DEV 4c1ab92 -&gt; QA a9c971b via promote.py (exit 0; CI check passed, no divergence, stripped paths verified absent); QA Run 120 green.
 MUTATION: 30 named mutations over squareoff.py, the reconciler guard, positions.py, service.py and the Position validator: 30 killed, sources byte-identical (first run 26/29 + 2 never ran: QA-E15-38).
-SIT: Pending - SIT-21 (updated: every position now leaves at its deadline, closed TIME) and SIT-22 (a day with three positions and two deadlines, a restart after the deadline, a kill switch mid-session, yesterday's stale row) pass on DEV; to run on the QA tree.</t>
+SIT: SIT on the QA tree (worktree at origin/QA a9c971b, algotrader imported from the worktree), whole suite because the change spans components: 2,798 passed, 0 failed, 0 skipped, PYTEST EXIT CODE 0. SIT-22 walks the real stack (Postgres, Redis, Kite payloads): three positions across two deadlines each exit IN their deadline's minute, never with a stop and an exit both working, all closed TIME, flat at the close; a restart at 15:17 after a 15:15 deadline squares off at once, once, for what was held, closed TIME; a kill switch at 14:00 leaves the time exits untouched; yesterday's OPEN row halts the morning (POSITION_NOT_HELD) and nothing is sold all day. SIT-21 updated: every position now leaves at its deadline. No SIT defects.</t>
         </is>
       </c>
       <c r="W132" s="49" t="n"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -7172,7 +7172,8 @@
       <c r="W32" s="49" t="n"/>
       <c r="X32" s="75" t="inlineStr">
         <is>
-          <t>NSE replaced the legacy bhavcopy with the UDiFF format and moved the URL. A fetcher written against the old path will 404, or worse fetch a stale mirror. Pin the exact source and assert on the header row, not just on HTTP 200. Also: bhavcopy is UNADJUSTED, so this must land before E03-S02 computes factors, never after.</t>
+          <t>NSE replaced the legacy bhavcopy with the UDiFF format and moved the URL. A fetcher written against the old path will 404, or worse fetch a stale mirror. Pin the exact source and assert on the header row, not just on HTTP 200. Also: bhavcopy is UNADJUSTED, so this must land before E03-S02 computes factors, never after.
+FROM E15-S14 (29 Oct 2026): correlations are computed from DAILY closes in ohlcv (timeframe 1d) and need every candidate's and held name's series to END ON THE PREVIOUS SESSION; a series that stops earlier makes its correlation unknown, and the guard then refuses any second position.</t>
         </is>
       </c>
     </row>
@@ -13849,7 +13850,8 @@
       <c r="W112" s="49" t="n"/>
       <c r="X112" s="75" t="inlineStr">
         <is>
-          <t>SEQUENCING BUG: this story is Phase 4 but depends on E12-S01 (strategy registry), which is Phase 5. Phase 4 cannot complete as currently sequenced. Either pull E12-S01 forward into Phase 4 or move this story into Phase 5.</t>
+          <t>SEQUENCING BUG: this story is Phase 4 but depends on E12-S01 (strategy registry), which is Phase 5. Phase 4 cannot complete as currently sequenced. Either pull E12-S01 forward into Phase 4 or move this story into Phase 5.
+FROM E15-S14 (29 Oct 2026): the execution service sizes every signal from the ATR this loop PUBLISHES. After folding each sealed bar into a symbol's IndicatorSet, call indicators.publish.publish_indicator_state BEFORE emitting any signal evaluated on that bar. Execution refuses a state older than one bar + 30s, not ready (warming or a feed gap), or on another timeframe than the signal's strategy declares - a signal that overtakes its own bar's state is refused.</t>
         </is>
       </c>
     </row>
@@ -16185,7 +16187,8 @@
       <c r="X136" s="75" t="inlineStr">
         <is>
           <t>'Switching paper-&gt;live changes exactly one dependency injection' is a strong claim and deserves a STRUCTURAL test, the way the ReadOnlyGuard test works. Otherwise one stray `if mode == PAPER` in the risk path makes every paper result unrepresentative of live.
-FROM E15-S13 (28 Oct 2026): the execution service sends in PAPER and LIVE modes to WHATEVER placer it is given - it cannot tell a paper placer from Kite. This story's placer is what makes PAPER safe: the entrypoint must hand the gateway the paper placer in PAPER mode, and nothing else may. ALERT_ONLY and APPROVAL are refused by the service itself (AUDIT-027).</t>
+FROM E15-S13 (28 Oct 2026): the execution service sends in PAPER and LIVE modes to WHATEVER placer it is given - it cannot tell a paper placer from Kite. This story's placer is what makes PAPER safe: the entrypoint must hand the gateway the paper placer in PAPER mode, and nothing else may. ALERT_ONLY and APPROVAL are refused by the service itself (AUDIT-027).
+FROM E15-S14 (29 Oct 2026): the paper broker must answer KiteTradingAdapter.margin_required(symbol, side=..., quantity=1) -&gt; Decimal - LiveSessionFacts' margin producer calls it in PAPER mode exactly as in LIVE. Zero or an error refuses the signal.</t>
         </is>
       </c>
     </row>
@@ -18814,7 +18817,8 @@
       <c r="W171" s="49" t="n"/>
       <c r="X171" t="inlineStr">
         <is>
-          <t>FROM E15-S13 (28 Oct 2026): the execution service asks SessionFacts.unhealthy_services(now=...) for the health roll-up; until this story provides it, NoProducerYet answers None and the engine rejects EVERY signal (HEALTH via RISK_ENGINE_FAULT). Implement it as a SessionFacts method returning a tuple of unhealthy service names - empty only when every service was checked.</t>
+          <t>FROM E15-S13 (28 Oct 2026): the execution service asks SessionFacts.unhealthy_services(now=...) for the health roll-up; until this story provides it, NoProducerYet answers None and the engine rejects EVERY signal (HEALTH via RISK_ENGINE_FAULT). Implement it as a SessionFacts method returning a tuple of unhealthy service names - empty only when every service was checked.
+FROM E15-S14 (29 Oct 2026): health is now the only live input without a producer. LiveSessionFacts takes it as `health` - an object with unhealthy_services(now=...) -&gt; tuple[str, ...] | None.</t>
         </is>
       </c>
     </row>
@@ -20304,7 +20308,8 @@
       <c r="X191" s="75" t="inlineStr">
         <is>
           <t>'Verify core has no internet access, by attempt' is the right test. Note the tension with E02-S01's auth callback and E17-S01's dashboard access — both want inbound reachability. Resolve the network design ONCE here rather than three times in three stories, or the answers will disagree.
-FROM E15-S13 (28 Oct 2026): docker-compose runs `python -m algotrader.execution`, and no service has a __main__ yet. The execution entrypoint composes ExecutionService (execution/service.py) with: the Kite trading adapter (or E15-S10's paper placer in PAPER mode - AUDIT-027), a session per operation for the repositories, RepositoryContextStore, HaltController, AuditWriter.write as the audit sink, and RedisSignalSource; then `await service.run(source, stop)`. QA-VER-01 constraint 4 lands here too: reconciliation reads must not share the data token bucket with backfill.</t>
+FROM E15-S13 (28 Oct 2026): docker-compose runs `python -m algotrader.execution`, and no service has a __main__ yet. The execution entrypoint composes ExecutionService (execution/service.py) with: the Kite trading adapter (or E15-S10's paper placer in PAPER mode - AUDIT-027), a session per operation for the repositories, RepositoryContextStore, HaltController, AuditWriter.write as the audit sink, and RedisSignalSource; then `await service.run(source, stop)`. QA-VER-01 constraint 4 lands here too: reconciliation reads must not share the data token bucket with backfill.
+FROM E15-S14 (29 Oct 2026): compose the service's facts as LiveSessionFacts(health=NoProducerYet() until E20-S05, atr=PublishedATR(redis, timeframes=strategy_timeframes(&lt;the strategy documents the strategy side loads&gt;)), margin=BrokerMarginPerShare(&lt;the trading adapter, or the paper one&gt;), correlations=DailyCloseCorrelations(BarRepository(...), calendar=...)).</t>
         </is>
       </c>
     </row>
@@ -21548,7 +21553,7 @@
       </c>
       <c r="E206" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F206" s="41" t="inlineStr">
@@ -21601,14 +21606,25 @@
       </c>
       <c r="U206" s="48" t="inlineStr">
         <is>
-          <t>AC1 (RED) With the producers wired, an approvable signal is approved and sized from the live ATR and margin.
-AC2 (RED) A stale ATR, an unanswered margin call, or an uncomputable correlation each still rejects, naming the input.
-AC3 (RED) A held symbol whose correlation is unknown still refuses a second position.</t>
+          <t>AC1 (RED) With the producers wired - ATR from the state the real IndicatorSet publishes to Redis, margin from the Kite adapter's /margins/orders answer, correlations from daily closes in Postgres - an approvable signal is SUBMITTED, and its quantity is the sizer's from that ATR and margin (the risk budget over 1.5 x ATR; and the margin clamp when the broker's per-share margin is dear).
+AC2 (RED) Each of these rejects, places nothing, and the rejection detail names the input: no published state; a state more than one bar + 30s old; a signal from a strategy the service was not given; a margin call that fails; a zero margin.
+AC3 (RED) With a position held, a candidate whose daily history is missing, or does not end on the previous session, is refused (RISK_ENGINE_FAULT, naming the held symbol); the control - both histories current and uncorrelated - takes the second position.</t>
         </is>
       </c>
       <c r="V206" s="48" t="inlineStr">
         <is>
-          <t>RAISED 28 Oct 2026 by E15-S13. The service, the context builder and NoProducerYet exist; these three inputs are the reason production rejects every signal today (with E20-S05's health roll-up).</t>
+          <t>RAISED 28 Oct 2026 by E15-S13. The service, the context builder and NoProducerYet exist; these three inputs are the reason production rejects every signal today (with E20-S05's health roll-up).
+BUSINESS ANALYSIS, 29 Oct 2026 (/sdlc, E15-S14).
+DoR: R1 ok (P0, 2d, Safety-critical). R2 ok - E15-S13 QA-Success. R3 no blocker covers it (B8 blocks the daily-bar SOURCE, E03-S01, not this story). R4 LLA 4.1/4.3/5.7/8.3, session_context, sizer, correlation, the Kite adapter and the indicator engine read this session.
+VALUE: the inputs every approval is sized from. What breaks if wrong: a position sized from a stale or another strategy's ATR (every size wrong by the same factor, all day); a margin guessed low; two names that are one bet read as unrelated; margin lookups starving an exit order.
+TASK CORRECTIONS, recorded: (1) Task 1's ATR cannot be computed from Postgres - live bars reach it only after the session (LLA 4.1) - so the strategy side PUBLISHES its state (IndicatorSet.published -&gt; indicators/publish.py -&gt; state:indicator, an IndicatorSnapshot with as_of and ready) and execution reads it. (2) Task 2 said 'behind the order-rate limiter'; that would let a burst of margin lookups refuse an exit order. It is a read and takes a DATA token (KiteTradingAdapter.margin_required, asserted by a token-counting test).
+DECISIONS: ATR on the signal's own strategy's timeframe (strategy_timeframes from the strategy documents; an unknown strategy has no ATR); refused if absent, not ready, describing another key, dated &gt;5s ahead, or older than one bar + 30s. Margin: one share, NSE/MIS/MARKET, the signal's side, 5s bound (it runs under the lock the square-off timer takes), &lt;=0 is unknown. Correlations: daily closes, today's bar excluded, each pair ALIGNED ON COMMON DATES (correlations_against pairs by position - QA-E15-41), unknown for a series not ending on the previous session. SessionFacts.atr gains strategy_id and margin_per_share gains direction. Health stays NoProducerYet (E20-S05); LiveSessionFacts composes the four.
+OUT OF SCOPE, recorded: the health roll-up (E20-S05); calling the publisher from the strategy loop (E13-S01, concern written); the paper broker's margin (E15-S10, concern written); daily-bar ingestion (E03-S01, concern written); composing it at the entrypoint (E23-S03, concern written).
+RESIDUALS, recorded: margin is asked for every signal that reaches the context build, including ones a check then rejects (one read per signal); a 1h strategy's last bar of the day reports an as_of after 15:30 (no entry is possible then); the sizing ATR is atr_14 on the strategy's timeframe - a strategy wanting another needs the mapping from its stop primitive; the 30s grace is a judgement. In production every input is still unknown until E13-S01 publishes and E03 fills daily bars, and health until E20-S05.
+FOUND MID-STORY: autobahn CVE-2026-116579 (published 28 Oct 21:10 UTC) turned the dependency audit red; FIXED by moving every install site to 26.10.2, in its own commit (AUDIT-033).
+GATES: Full gate 29 Oct 2026, one pass after the venv repair (the first run failed to COLLECT: the autobahn replacement had been interrupted, pytest exit 2 - not a code failure, recorded in b96b167): 2,879 passed, 0 failed, 0 skipped, PYTEST EXIT 0, coverage 93% (flat; live_inputs 94%, publish 100%, session_context 93%); ruff check/format and mypy clean over the whole tree; bandit 0; pip-audit 0 with the 7 accepted IDs, re-run before push; security suite 461 passed; gitleaks clean on the 2 pushed commits; ops/Dockerfile image built and imports kiteconnect under autobahn 26.10.2; doctor: Configuration/Broker SDK/Market calendar/Strategies OK (Datastores FAIL and Secrets/SEBI/Network WARN are the dev machine). CI: DEV Run 122 green on 251c5ac (with b96b167 autobahn); promoted DEV 251c5ac -&gt; QA 29c06e7 via promote.py (CI check passed, no divergence, Documents/scripts/tracker/.claude stripped and verified absent); QA Run 123 green on 29c06e7.
+MUTATION: 28 named mutations across live_inputs, the Kite margin read, IndicatorSet.published/restore, the publisher and the context builder: 28 killed, sources byte-identical.
+SIT: SIT on the QA tree (detached worktree at origin/QA 29c06e7, algotrader imported from the worktree), whole suite because the change spans broker, indicators and execution: 2,879 passed, 0 failed, 0 skipped, PYTEST EXIT 0. SIT-23 (tests/sit/test_e15_execution_session.py) walks a day with the live producers wired - the strategy side publishing state each 5m bar, a TCS feed gap 11:00-12:00 then a re-warm, the margin desk down 13:00-13:10, HDFCBANK with no daily history - and asserts every signal ends one audited way: INFY, TCS (after the re-warm) and WIPRO (after the outage) submitted and sized from the published ATR; HDFCBANK refused naming the held INFY (correlation unknown); TCS during the gap refused naming its ATR; WIPRO during the outage refused naming its per-share margin; every entry protected by one stop, squared off once at its deadline and closed TIME; no halt. No SIT defects.</t>
         </is>
       </c>
       <c r="W206" s="49" t="n"/>
@@ -21712,6 +21728,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -22140,7 +22157,8 @@
 It is a fetch-RELIABILITY problem, not a wall. The data is public; the difficulty is that the site is hostile to automation and changes shape without notice. Kite's instrument dump does NOT help - it carries token, symbol, tick size, lot size and segment, with no series, ASM, GSM, T2T or ban field (verified against the API docs).
 MITIGATIONS: jugaad-data (actively maintained, with caching specifically to avoid being blocked); nsefin for corporate actions, which is also E03-S02's missing feed; BSE as a fallback since ~90% of NSE equities are dual-listed; Zerodha's consolidated scrip sheet as a cross-check only (no SLA). The India-hosted VPS already required by constraint C1 sidesteps the geo-restriction.
 WHY IT IS SURVIVABLE: the fetch runs at 05:30, hours before the open, so a failure has a long runway for a retry, a fallback source or a manual override. E04-S01's acceptance criterion already says a fetch failure blocks the trading day rather than proceeding blind - the right posture: a bad fetch costs a trading day, not money.
-ACTION: spend an hour proving NSE reachability from the target environment before writing fetchers. That assumption sits under 8 stories and roughly 10 days of work.</t>
+ACTION: spend an hour proving NSE reachability from the target environment before writing fetchers. That assumption sits under 8 stories and roughly 10 days of work.
+OBSERVED 29 Oct 2026 (E15-S14 orientation): scripts/check_data_reachability.py from the development host (egress 14.96.14.58, an APNIC address) - NSE home 403 and the NSE ASM list an HTML interstitial, while the NSE bhavcopy archive, the NSE F&amp;O ban list, BSE and the Kite instruments dump all answered. If that host is in India, 'NSE blocks only overseas access' is incomplete and the India VPS may not resolve B8 by itself. Not concluded here; re-run on the VPS as planned.</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J160"/>
+  <dimension ref="A1:J163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -28324,6 +28342,117 @@
       <c r="G160" s="76" t="inlineStr">
         <is>
           <t>30 named mutations, 30 killed; sources byte-identical. tests/unit/test_squareoff.py::...test_a_stop_cancelled_part_filled_is_not_the_exit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-39</t>
+        </is>
+      </c>
+      <c r="B161" s="76" t="inlineStr">
+        <is>
+          <t>E15-S14</t>
+        </is>
+      </c>
+      <c r="C161" s="76" t="inlineStr">
+        <is>
+          <t>The first ATR design read a day-old number all session</t>
+        </is>
+      </c>
+      <c r="D161" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed (design review)</t>
+        </is>
+      </c>
+      <c r="E161" s="76" t="inlineStr">
+        <is>
+          <t>The first design computed the ATR in execution from the bars in Postgres - self-contained and testable today. LLA 4.1 puts live bars in Redis streams during the session and flushes them to Postgres afterwards, so that ATR would be yesterday's for the whole session and every signal would be refused (or, with intraday backfill, sized off a stale range).</t>
+        </is>
+      </c>
+      <c r="F161" s="76" t="inlineStr">
+        <is>
+          <t>The strategy side publishes its own state (IndicatorSet.published, indicators/publish.py) to state:indicator with as_of and ready; execution reads the one for the signal's strategy and refuses anything older than one bar + 30s.</t>
+        </is>
+      </c>
+      <c r="G161" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_live_inputs.py::TestReadAtr, ::TestPublishedAtr::test_what_the_writer_publishes_the_reader_reads; integration TestS14Ac2...::test_a_stale_atr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-40</t>
+        </is>
+      </c>
+      <c r="B162" s="76" t="inlineStr">
+        <is>
+          <t>E15-S14</t>
+        </is>
+      </c>
+      <c r="C162" s="76" t="inlineStr">
+        <is>
+          <t>The story's task put margin lookups on the order-rate limiter</t>
+        </is>
+      </c>
+      <c r="D162" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Corrected (story)</t>
+        </is>
+      </c>
+      <c r="E162" s="76" t="inlineStr">
+        <is>
+          <t>Task 2 read 'Kite order_margins ... behind the order-rate limiter'. The order bucket is 3/s with a burst of 3 and exists so that nothing can starve an order; a margin lookup per signal there could refuse a stop or a time exit in the same second.</t>
+        </is>
+      </c>
+      <c r="F162" s="76" t="inlineStr">
+        <is>
+          <t>margin_required goes through the adapter's read path and takes a DATA token. The task is corrected on the story with the reason.</t>
+        </is>
+      </c>
+      <c r="G162" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_live_inputs.py::TestMarginRequired::test_it_takes_a_data_token_never_an_order_token; mutation 'margin on the order bucket' killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-41</t>
+        </is>
+      </c>
+      <c r="B163" s="76" t="inlineStr">
+        <is>
+          <t>E15-S14</t>
+        </is>
+      </c>
+      <c r="C163" s="76" t="inlineStr">
+        <is>
+          <t>correlations_against pairs returns by position, not by date</t>
+        </is>
+      </c>
+      <c r="D163" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed (producer)</t>
+        </is>
+      </c>
+      <c r="E163" s="76" t="inlineStr">
+        <is>
+          <t>correlations_against (E14-S04) pairs the tail of each series by POSITION, which is right only when both cover the same sessions. A name that did not trade for three sessions mid-window paired every older return with the wrong day's: a pair at 0.98 read below 0.7, i.e. one bet read as two.</t>
+        </is>
+      </c>
+      <c r="F163" s="76" t="inlineStr">
+        <is>
+          <t>The producer aligns each pair on the dates both traded before calling it (daily_correlations). correlations_against is unchanged; its callers are now the producer and tests.</t>
+        </is>
+      </c>
+      <c r="G163" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_live_inputs.py::TestDailyCorrelations::test_pairs_are_aligned_on_common_dates (asserts the by-position reading is &lt; 0.7 and the aligned one &gt; 0.9); mutation 'paired by position' killed.</t>
         </is>
       </c>
     </row>
@@ -28344,7 +28473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -31975,6 +32104,90 @@
       <c r="H87" s="76" t="inlineStr">
         <is>
           <t>tests/unit/test_squareoff.py::TestItsMemoryIsBounded; mutation 'memory never pruned' killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-033</t>
+        </is>
+      </c>
+      <c r="B88" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C88" s="76" t="inlineStr">
+        <is>
+          <t>dependency autobahn 26.7.1 - CVE-2026-116579 / GHSA-pjh6-c8mg-3x7m</t>
+        </is>
+      </c>
+      <c r="D88" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E88" s="76" t="inlineStr">
+        <is>
+          <t>Published 28 Oct 2026 21:10 UTC; the dependency audit went red mid-story. permessage-brotli inflates a whole frame before maxMessagePayloadSize is checked, so one 421-byte frame costs an autobahn SERVER ~545 MiB.</t>
+        </is>
+      </c>
+      <c r="F88" s="76" t="inlineStr">
+        <is>
+          <t>Unreachable here: this system runs no autobahn server, enables no WebSocket compression extension, and never constructs a KiteTicker (autobahn is present only because kiteconnect imports its ticker module).</t>
+        </is>
+      </c>
+      <c r="G88" s="76" t="inlineStr">
+        <is>
+          <t>Fixed anyway, because a fix exists: every install site (ci.yml x3, ops/Dockerfile, Makefile, docs) moves to 26.10.2; requirements (cryptography&gt;=50, cbor2&gt;=6.1, txaio&gt;=25.12.2) already met by constraints.txt. kiteconnect 5.2.1 verified under it (imports, login URL, market_protection/algo_id, ticker import), locally and inside the built runtime image.</t>
+        </is>
+      </c>
+      <c r="H88" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_dependency_hygiene.py::TestAutobahnIsNotTheVulnerableVersion::test_the_installed_autobahn_carries_the_brotli_fix (BROTLI_FIX_AUTOBAHN = 26.10.1); pip-audit clean with the same 7 accepted IDs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-034</t>
+        </is>
+      </c>
+      <c r="B89" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C89" s="76" t="inlineStr">
+        <is>
+          <t>execution/live_inputs.py, indicators/publish.py, KiteTradingAdapter.margin_required - STRIDE</t>
+        </is>
+      </c>
+      <c r="D89" s="76" t="inlineStr">
+        <is>
+          <t>Assessed</t>
+        </is>
+      </c>
+      <c r="E89" s="76" t="inlineStr">
+        <is>
+          <t>S: the published state must match its key (symbol, timeframe), be ready, not be from the future, and be at most one bar + 30s old. A tampered ATR cannot breach the per-trade risk bound: quantity x stop &lt;= budget holds for ANY ATR, a vanishing ATR sizes a zero-width stop (refused) and a huge one puts the stop past the entry (refused). T: the state is validated by IndicatorSnapshot (NaN/inf refused, probed); -0 refused by the reader; the margin total must be one finite row for the symbol asked. R: every refusal names the input in decision_log; the producer logs why. I: logs go through one_safe_line; the audit detail carries the RiskContextError message, never broker text. D: per signal one Redis GET, one broker read (5s bound, data bucket) and one DB query; the timer waits at most one signal for the lock. E: strategy_id selects a timeframe by dict lookup (unknown -&gt; None); the symbol reaches a Redis key only through keys._safe.</t>
+        </is>
+      </c>
+      <c r="F89" s="76" t="inlineStr">
+        <is>
+          <t>Residuals recorded on E15-S14.</t>
+        </is>
+      </c>
+      <c r="G89" s="76" t="inlineStr">
+        <is>
+          <t>None required beyond the story.</t>
+        </is>
+      </c>
+      <c r="H89" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_live_inputs.py (67), integration TestS14* (10), SIT-23; mutation 28/28.</t>
         </is>
       </c>
     </row>
